--- a/Översikt SVALÖV.xlsx
+++ b/Översikt SVALÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45910</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 15475-2024</t>
+          <t>A 38522-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45401</v>
+        <v>45884</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.7</v>
+        <v>2.6</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -848,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -857,10 +857,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -869,146 +869,146 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Skogsknipprot
+Stor häxört</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 38522-2025 artfynd.xlsx", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 38522-2025 karta.png", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 38522-2025 georefererad karta.tif", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 38522-2025 FSC-klagomål.docx", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 38522-2025 FSC-klagomål mail.docx", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 38522-2025 tillsynsbegäran.docx", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 38522-2025 tillsynsbegäran mail.docx", "A 38522-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 15475-2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45401</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SVALÖV</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>1</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Ask
 Strutbräken</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15475-2024 artfynd.xlsx", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15475-2024 karta.png", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15475-2024 georefererad karta.tif", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15475-2024 FSC-klagomål.docx", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15475-2024 FSC-klagomål mail.docx", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15475-2024 tillsynsbegäran.docx", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15475-2024 tillsynsbegäran mail.docx", "A 15475-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 38522-2025</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45884</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SVALÖV</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Skogsknipprot
-Stor häxört</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 38522-2025 artfynd.xlsx", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 38522-2025 karta.png", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 38522-2025 georefererad karta.tif", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 38522-2025 FSC-klagomål.docx", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 38522-2025 FSC-klagomål mail.docx", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 38522-2025 tillsynsbegäran.docx", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 38522-2025 tillsynsbegäran mail.docx", "A 38522-2025")</f>
         <v/>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
         <v>45645</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 15456-2024</t>
+          <t>A 11170-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45401</v>
+        <v>44987</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1187,46 +1187,46 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Lundticka</t>
+          <t>Korndådra</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15456-2024 artfynd.xlsx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11170-2023 artfynd.xlsx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15456-2024 karta.png", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11170-2023 karta.png", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15456-2024 georefererad karta.tif", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11170-2023 georefererad karta.tif", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15456-2024 FSC-klagomål.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11170-2023 FSC-klagomål.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15456-2024 FSC-klagomål mail.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11170-2023 FSC-klagomål mail.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15456-2024 tillsynsbegäran.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11170-2023 tillsynsbegäran.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15456-2024 tillsynsbegäran mail.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11170-2023 tillsynsbegäran mail.docx", "A 11170-2023")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 1577-2024</t>
+          <t>A 15456-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45306</v>
+        <v>45401</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1256,20 +1256,20 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>21.2</v>
+        <v>2.5</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
@@ -1280,10 +1280,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1296,42 +1296,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Lundticka</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15456-2024 artfynd.xlsx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15456-2024 karta.png", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15456-2024 georefererad karta.tif", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15456-2024 FSC-klagomål.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15456-2024 FSC-klagomål mail.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15456-2024 tillsynsbegäran.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15456-2024 tillsynsbegäran mail.docx", "A 15456-2024")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 20125-2024</t>
+          <t>A 54127-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45434</v>
+        <v>45964</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1361,17 +1361,17 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.7</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
@@ -1385,7 +1385,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1397,46 +1397,50 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 20125-2024 artfynd.xlsx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 54127-2025 artfynd.xlsx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 20125-2024 karta.png", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 54127-2025 karta.png", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 20125-2024 georefererad karta.tif", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 54127-2025 georefererad karta.tif", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 20125-2024 FSC-klagomål.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 54127-2025 FSC-klagomål.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 20125-2024 FSC-klagomål mail.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 54127-2025 FSC-klagomål mail.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 20125-2024 tillsynsbegäran.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 54127-2025 tillsynsbegäran.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 20125-2024 tillsynsbegäran mail.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 54127-2025 tillsynsbegäran mail.docx", "A 54127-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/fåglar/A 54127-2025 prioriterade fågelarter.docx", "A 54127-2025")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 11672-2024</t>
+          <t>A 20125-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1450,10 +1454,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45373</v>
+        <v>45434</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1466,16 +1470,16 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>13.9</v>
+        <v>5.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1490,7 +1494,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1502,39 +1506,39 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11672-2024 artfynd.xlsx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 20125-2024 artfynd.xlsx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11672-2024 karta.png", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 20125-2024 karta.png", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11672-2024 georefererad karta.tif", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 20125-2024 georefererad karta.tif", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11672-2024 FSC-klagomål.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 20125-2024 FSC-klagomål.docx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11672-2024 FSC-klagomål mail.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 20125-2024 FSC-klagomål mail.docx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11672-2024 tillsynsbegäran.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 20125-2024 tillsynsbegäran.docx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11672-2024 tillsynsbegäran mail.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 20125-2024 tillsynsbegäran mail.docx", "A 20125-2024")</f>
         <v/>
       </c>
     </row>
@@ -1558,7 +1562,7 @@
         <v>45225</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1646,7 +1650,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 11170-2023</t>
+          <t>A 11672-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1660,10 +1664,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44987</v>
+        <v>45373</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1676,7 +1680,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.9</v>
+        <v>13.9</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1685,13 +1689,13 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1703,7 +1707,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1716,42 +1720,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Korndådra</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11170-2023 artfynd.xlsx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11672-2024 artfynd.xlsx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11170-2023 karta.png", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11672-2024 karta.png", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11170-2023 georefererad karta.tif", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11672-2024 georefererad karta.tif", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11170-2023 FSC-klagomål.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11672-2024 FSC-klagomål.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11170-2023 FSC-klagomål mail.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11672-2024 FSC-klagomål mail.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11170-2023 tillsynsbegäran.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11672-2024 tillsynsbegäran.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11170-2023 tillsynsbegäran mail.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11672-2024 tillsynsbegäran mail.docx", "A 11672-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 54127-2025</t>
+          <t>A 1577-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1765,10 +1769,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45964</v>
+        <v>45306</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1781,7 +1785,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>21.2</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1790,7 +1794,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1805,7 +1809,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1817,43 +1821,39 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 54127-2025 artfynd.xlsx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 54127-2025 karta.png", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 54127-2025 georefererad karta.tif", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 54127-2025 FSC-klagomål.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 54127-2025 FSC-klagomål mail.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 54127-2025 tillsynsbegäran.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 54127-2025 tillsynsbegäran mail.docx", "A 54127-2025")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/fåglar/A 54127-2025 prioriterade fågelarter.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
         <v>45351</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>45218</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>44763</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44598</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44483</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44847</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44501</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>44831</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>44854</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 13245-2024</t>
+          <t>A 49032-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2595,10 +2595,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45386</v>
+        <v>44860</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>13</v>
+        <v>3.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 21774-2024</t>
+          <t>A 35911-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45442</v>
+        <v>45148</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 35587-2024</t>
+          <t>A 9716-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45531</v>
+        <v>44617</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2800,7 +2800,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 16667-2023</t>
+          <t>A 11101-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2814,10 +2814,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45030</v>
+        <v>44986</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 22794-2024</t>
+          <t>A 1592-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45448</v>
+        <v>45306</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 6365-2026</t>
+          <t>A 11177-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46051</v>
+        <v>44987</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3019,7 +3019,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 22063-2025</t>
+          <t>A 23747-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45785</v>
+        <v>45793</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3092,7 +3092,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 8332-2025</t>
+          <t>A 24513-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3106,10 +3106,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45708</v>
+        <v>45798</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3165,7 +3165,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 14543-2024</t>
+          <t>A 27310-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45394</v>
+        <v>45096</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3238,7 +3238,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 17980-2025</t>
+          <t>A 10209-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45761</v>
+        <v>44986</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3311,7 +3311,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 19282-2025</t>
+          <t>A 42706-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3321,14 +3321,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45769</v>
+        <v>45908</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3384,7 +3384,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 20170-2024</t>
+          <t>A 43425-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45434</v>
+        <v>45911</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 42706-2025</t>
+          <t>A 22063-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45908</v>
+        <v>45785</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 43425-2025</t>
+          <t>A 5068-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45911</v>
+        <v>46049</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3603,7 +3603,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 62403-2022</t>
+          <t>A 59266-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44923</v>
+        <v>45988</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3676,7 +3676,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 37907-2025</t>
+          <t>A 22262-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45880</v>
+        <v>45070</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3705,13 +3705,8 @@
           <t>SVALÖV</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>5.7</v>
+        <v>1.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3754,7 +3749,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 40470-2025</t>
+          <t>A 17980-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3764,14 +3759,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45895</v>
+        <v>45761</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3784,7 +3779,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.1</v>
+        <v>3.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3827,7 +3822,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 15157-2023</t>
+          <t>A 6335-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3841,10 +3836,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45016</v>
+        <v>44600</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3857,7 +3852,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3900,7 +3895,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 47139-2025</t>
+          <t>A 16667-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3914,10 +3909,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45929</v>
+        <v>45030</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3930,7 +3925,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3973,7 +3968,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 11491-2023</t>
+          <t>A 19282-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3983,14 +3978,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44991</v>
+        <v>45769</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4003,7 +3998,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4046,7 +4041,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 10209-2023</t>
+          <t>A 6365-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4060,10 +4055,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44986</v>
+        <v>46051</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4076,7 +4071,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4119,7 +4114,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 14533-2026</t>
+          <t>A 47139-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4133,10 +4128,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46100</v>
+        <v>45929</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4149,7 +4144,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4192,7 +4187,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 44107-2023</t>
+          <t>A 1920-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4206,10 +4201,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45188</v>
+        <v>45671</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4265,7 +4260,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 15747-2026</t>
+          <t>A 37907-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4279,10 +4274,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46107</v>
+        <v>45880</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4294,8 +4289,13 @@
           <t>SVALÖV</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>5.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 43294-2025</t>
+          <t>A 40470-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4348,14 +4348,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45910</v>
+        <v>45895</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.6</v>
+        <v>0.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 3430-2026</t>
+          <t>A 8332-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46042</v>
+        <v>45708</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5.7</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 22262-2023</t>
+          <t>A 44112-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45070</v>
+        <v>45188</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 18926-2026</t>
+          <t>A 11491-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46127</v>
+        <v>44991</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 49032-2022</t>
+          <t>A 11922-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44860</v>
+        <v>44993</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 43466-2025</t>
+          <t>A 14533-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45911</v>
+        <v>46100</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 43004-2025</t>
+          <t>A 15747-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45909</v>
+        <v>46107</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 18121-2025</t>
+          <t>A 3430-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45761</v>
+        <v>46042</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.7</v>
+        <v>5.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 34810-2023</t>
+          <t>A 43294-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45141</v>
+        <v>45910</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>7</v>
+        <v>2.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 62201-2025</t>
+          <t>A 18926-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46006</v>
+        <v>46127</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>22.1</v>
+        <v>1.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 5068-2026</t>
+          <t>A 34810-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46049</v>
+        <v>45141</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 59266-2025</t>
+          <t>A 43466-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5155,10 +5155,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45988</v>
+        <v>45911</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.8</v>
+        <v>4.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 6335-2022</t>
+          <t>A 62201-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44600</v>
+        <v>46006</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4</v>
+        <v>22.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 10196-2025</t>
+          <t>A 43004-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45719</v>
+        <v>45909</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 44112-2023</t>
+          <t>A 35587-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45188</v>
+        <v>45531</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 35911-2023</t>
+          <t>A 8924-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45148</v>
+        <v>44974</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.9</v>
+        <v>6.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 42588-2023</t>
+          <t>A 1901-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45176</v>
+        <v>45671</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5579,7 +5579,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 1901-2025</t>
+          <t>A 22794-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45671</v>
+        <v>45448</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 1920-2025</t>
+          <t>A 32620-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45671</v>
+        <v>45111</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5725,7 +5725,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 43736-2023</t>
+          <t>A 18438-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45182</v>
+        <v>46127</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5798,7 +5798,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 9716-2022</t>
+          <t>A 44196-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44617</v>
+        <v>45573</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5871,7 +5871,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 18438-2026</t>
+          <t>A 24286-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46127</v>
+        <v>46169</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5944,7 +5944,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 24286-2026</t>
+          <t>A 17731-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5954,14 +5954,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46169</v>
+        <v>45758</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6034,7 +6034,7 @@
         <v>45987</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 25522-2026</t>
+          <t>A 14543-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6104,10 +6104,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46177</v>
+        <v>45394</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>8.5</v>
+        <v>0.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6163,7 +6163,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 37354-2022</t>
+          <t>A 25522-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44806</v>
+        <v>46177</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.4</v>
+        <v>8.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 5190-2024</t>
+          <t>A 13273-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6250,10 +6250,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45330</v>
+        <v>45386</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.1</v>
+        <v>12.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 17731-2025</t>
+          <t>A 29337-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6319,14 +6319,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45758</v>
+        <v>46202</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6382,7 +6382,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 22792-2024</t>
+          <t>A 25832-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6396,10 +6396,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45448</v>
+        <v>46178</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.5</v>
+        <v>7.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6455,7 +6455,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 25832-2026</t>
+          <t>A 30202-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6469,10 +6469,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46178</v>
+        <v>46206</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>7.8</v>
+        <v>5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6528,7 +6528,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 4964-2022</t>
+          <t>A 30535-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44593</v>
+        <v>46210</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6601,7 +6601,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 11177-2023</t>
+          <t>A 22792-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44987</v>
+        <v>45448</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6674,7 +6674,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 16215-2022</t>
+          <t>A 14546-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6688,10 +6688,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44670</v>
+        <v>45394</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6747,7 +6747,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 29337-2026</t>
+          <t>A 18121-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6761,10 +6761,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46202</v>
+        <v>45761</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6820,7 +6820,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 61620-2022</t>
+          <t>A 16215-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6834,10 +6834,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44910</v>
+        <v>44670</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6893,7 +6893,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 30535-2026</t>
+          <t>A 13787-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46210</v>
+        <v>46097</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6966,7 +6966,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 30202-2026</t>
+          <t>A 13791-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6980,10 +6980,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46206</v>
+        <v>46097</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 8924-2023</t>
+          <t>A 27380-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44974</v>
+        <v>46189</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>6.8</v>
+        <v>1.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7112,7 +7112,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 497-2023</t>
+          <t>A 15487-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44930</v>
+        <v>45747</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7185,7 +7185,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 11633-2024</t>
+          <t>A 4964-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7199,10 +7199,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45373</v>
+        <v>44593</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4.9</v>
+        <v>1.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7258,7 +7258,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 11922-2023</t>
+          <t>A 37354-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44993</v>
+        <v>44806</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7331,7 +7331,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 14546-2024</t>
+          <t>A 11633-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7345,10 +7345,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45394</v>
+        <v>45373</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>4.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7404,7 +7404,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 32620-2023</t>
+          <t>A 20170-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7418,10 +7418,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45111</v>
+        <v>45434</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7477,7 +7477,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 1592-2024</t>
+          <t>A 61620-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7491,10 +7491,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45306</v>
+        <v>44910</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7550,7 +7550,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 4149-2022</t>
+          <t>A 5190-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7560,14 +7560,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44588</v>
+        <v>45330</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7623,7 +7623,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 15487-2025</t>
+          <t>A 21774-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7637,10 +7637,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45747</v>
+        <v>45442</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7696,7 +7696,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 13787-2026</t>
+          <t>A 62403-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46097</v>
+        <v>44923</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7769,7 +7769,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 13791-2026</t>
+          <t>A 43736-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46097</v>
+        <v>45182</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7842,7 +7842,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 27380-2026</t>
+          <t>A 42588-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7856,10 +7856,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46189</v>
+        <v>45176</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7915,7 +7915,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 11101-2023</t>
+          <t>A 15157-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7929,10 +7929,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44986</v>
+        <v>45016</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7988,7 +7988,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 5184-2024</t>
+          <t>A 497-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8002,10 +8002,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45330</v>
+        <v>44930</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8061,7 +8061,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 13273-2024</t>
+          <t>A 5184-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8075,10 +8075,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45386</v>
+        <v>45330</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>12.4</v>
+        <v>2.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8134,7 +8134,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 44196-2024</t>
+          <t>A 44107-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45573</v>
+        <v>45188</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8207,7 +8207,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 21556-2025</t>
+          <t>A 10196-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8221,10 +8221,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45782</v>
+        <v>45719</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8280,7 +8280,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 21541-2025</t>
+          <t>A 4149-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8290,14 +8290,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45782</v>
+        <v>44588</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8353,7 +8353,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 21814-2025</t>
+          <t>A 13245-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8367,10 +8367,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45783</v>
+        <v>45386</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.4</v>
+        <v>13</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 20047-2024</t>
+          <t>A 21814-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45434</v>
+        <v>45783</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8499,7 +8499,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 34808-2024</t>
+          <t>A 21541-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45526</v>
+        <v>45782</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8572,7 +8572,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 5167-2024</t>
+          <t>A 21556-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45330</v>
+        <v>45782</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>6.5</v>
+        <v>1.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8645,7 +8645,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 23747-2025</t>
+          <t>A 20047-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8659,10 +8659,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45793</v>
+        <v>45434</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8718,7 +8718,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 24513-2025</t>
+          <t>A 34808-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8732,10 +8732,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45798</v>
+        <v>45526</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.4</v>
+        <v>3.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8791,7 +8791,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 27310-2023</t>
+          <t>A 5167-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45096</v>
+        <v>45330</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8881,7 +8881,7 @@
         <v>45854</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>

--- a/Översikt SVALÖV.xlsx
+++ b/Översikt SVALÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45910</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 38522-2025</t>
+          <t>A 15475-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45884</v>
+        <v>45401</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -833,14 +833,14 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
@@ -848,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -857,10 +857,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -869,146 +869,146 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15475-2024 artfynd.xlsx", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15475-2024 karta.png", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15475-2024 georefererad karta.tif", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15475-2024 FSC-klagomål.docx", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15475-2024 FSC-klagomål mail.docx", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15475-2024 tillsynsbegäran.docx", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15475-2024 tillsynsbegäran mail.docx", "A 15475-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 38522-2025</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SVALÖV</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Skogsknipprot
 Stor häxört</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 38522-2025 artfynd.xlsx", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 38522-2025 karta.png", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 38522-2025 georefererad karta.tif", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 38522-2025 FSC-klagomål.docx", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 38522-2025 FSC-klagomål mail.docx", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 38522-2025 tillsynsbegäran.docx", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 38522-2025 tillsynsbegäran mail.docx", "A 38522-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 15475-2024</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45401</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SVALÖV</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15475-2024 artfynd.xlsx", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15475-2024 karta.png", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15475-2024 georefererad karta.tif", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15475-2024 FSC-klagomål.docx", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15475-2024 FSC-klagomål mail.docx", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15475-2024 tillsynsbegäran.docx", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15475-2024 tillsynsbegäran mail.docx", "A 15475-2024")</f>
         <v/>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
         <v>45645</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 11170-2023</t>
+          <t>A 15456-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44987</v>
+        <v>45401</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1187,46 +1187,46 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Korndådra</t>
+          <t>Lundticka</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11170-2023 artfynd.xlsx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15456-2024 artfynd.xlsx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11170-2023 karta.png", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15456-2024 karta.png", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11170-2023 georefererad karta.tif", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15456-2024 georefererad karta.tif", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11170-2023 FSC-klagomål.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15456-2024 FSC-klagomål.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11170-2023 FSC-klagomål mail.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15456-2024 FSC-klagomål mail.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11170-2023 tillsynsbegäran.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15456-2024 tillsynsbegäran.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11170-2023 tillsynsbegäran mail.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15456-2024 tillsynsbegäran mail.docx", "A 15456-2024")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 15456-2024</t>
+          <t>A 11170-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45401</v>
+        <v>44987</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1268,10 +1268,10 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
         <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1292,46 +1292,46 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Lundticka</t>
+          <t>Korndådra</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15456-2024 artfynd.xlsx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11170-2023 artfynd.xlsx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15456-2024 karta.png", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11170-2023 karta.png", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15456-2024 georefererad karta.tif", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11170-2023 georefererad karta.tif", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15456-2024 FSC-klagomål.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11170-2023 FSC-klagomål.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15456-2024 FSC-klagomål mail.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11170-2023 FSC-klagomål mail.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15456-2024 tillsynsbegäran.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11170-2023 tillsynsbegäran.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15456-2024 tillsynsbegäran mail.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11170-2023 tillsynsbegäran mail.docx", "A 11170-2023")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 54127-2025</t>
+          <t>A 1577-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45964</v>
+        <v>45306</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>21.2</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1370,7 +1370,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1397,43 +1397,39 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 54127-2025 artfynd.xlsx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 54127-2025 karta.png", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 54127-2025 georefererad karta.tif", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 54127-2025 FSC-klagomål.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 54127-2025 FSC-klagomål mail.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 54127-2025 tillsynsbegäran.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 54127-2025 tillsynsbegäran mail.docx", "A 54127-2025")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/fåglar/A 54127-2025 prioriterade fågelarter.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
     </row>
@@ -1457,7 +1453,7 @@
         <v>45434</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1545,7 +1541,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 52664-2023</t>
+          <t>A 11672-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1559,10 +1555,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45225</v>
+        <v>45373</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1575,31 +1571,31 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>6.4</v>
+        <v>13.9</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1611,46 +1607,46 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 52664-2023 artfynd.xlsx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11672-2024 artfynd.xlsx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 52664-2023 karta.png", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11672-2024 karta.png", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 52664-2023 georefererad karta.tif", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11672-2024 georefererad karta.tif", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 52664-2023 FSC-klagomål.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11672-2024 FSC-klagomål.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 52664-2023 FSC-klagomål mail.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11672-2024 FSC-klagomål mail.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 52664-2023 tillsynsbegäran.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11672-2024 tillsynsbegäran.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 52664-2023 tillsynsbegäran mail.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11672-2024 tillsynsbegäran mail.docx", "A 11672-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 11672-2024</t>
+          <t>A 52664-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1664,10 +1660,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45373</v>
+        <v>45225</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1680,16 +1676,16 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>13.9</v>
+        <v>6.4</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1704,7 +1700,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1716,46 +1712,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11672-2024 artfynd.xlsx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 52664-2023 artfynd.xlsx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11672-2024 karta.png", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 52664-2023 karta.png", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11672-2024 georefererad karta.tif", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 52664-2023 georefererad karta.tif", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11672-2024 FSC-klagomål.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 52664-2023 FSC-klagomål.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11672-2024 FSC-klagomål mail.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 52664-2023 FSC-klagomål mail.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11672-2024 tillsynsbegäran.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 52664-2023 tillsynsbegäran.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11672-2024 tillsynsbegäran mail.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 52664-2023 tillsynsbegäran mail.docx", "A 52664-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 1577-2024</t>
+          <t>A 54127-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1769,10 +1765,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45306</v>
+        <v>45964</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1785,7 +1781,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>21.2</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1794,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1809,7 +1805,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1821,39 +1817,43 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 54127-2025 artfynd.xlsx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 54127-2025 karta.png", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 54127-2025 georefererad karta.tif", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 54127-2025 FSC-klagomål.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 54127-2025 FSC-klagomål mail.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 54127-2025 tillsynsbegäran.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 54127-2025 tillsynsbegäran mail.docx", "A 54127-2025")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/fåglar/A 54127-2025 prioriterade fågelarter.docx", "A 54127-2025")</f>
         <v/>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
         <v>45351</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>45218</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>44763</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44598</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44483</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44847</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44501</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>44831</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>44854</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 49032-2022</t>
+          <t>A 13245-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2595,10 +2595,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44860</v>
+        <v>45386</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.7</v>
+        <v>13</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 35911-2023</t>
+          <t>A 37907-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45148</v>
+        <v>45880</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2683,8 +2683,13 @@
           <t>SVALÖV</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>5.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2727,7 +2732,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 9716-2022</t>
+          <t>A 40470-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2737,14 +2742,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44617</v>
+        <v>45895</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2757,7 +2762,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2800,7 +2805,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 11101-2023</t>
+          <t>A 21774-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2814,10 +2819,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44986</v>
+        <v>45442</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2830,7 +2835,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2873,7 +2878,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 1592-2024</t>
+          <t>A 37354-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2887,10 +2892,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45306</v>
+        <v>44806</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2903,7 +2908,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2946,7 +2951,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 11177-2023</t>
+          <t>A 5190-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2960,10 +2965,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44987</v>
+        <v>45330</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2976,7 +2981,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3019,7 +3024,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 23747-2025</t>
+          <t>A 17731-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3029,14 +3034,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45793</v>
+        <v>45758</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3049,7 +3054,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3092,7 +3097,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 24513-2025</t>
+          <t>A 22794-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3106,10 +3111,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45798</v>
+        <v>45448</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3122,7 +3127,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.4</v>
+        <v>3.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3165,7 +3170,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 27310-2023</t>
+          <t>A 35587-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3179,10 +3184,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45096</v>
+        <v>45531</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3195,7 +3200,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3238,7 +3243,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 10209-2023</t>
+          <t>A 14533-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3252,10 +3257,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44986</v>
+        <v>46100</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3328,7 +3333,7 @@
         <v>45908</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3401,7 +3406,7 @@
         <v>45911</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3457,7 +3462,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 22063-2025</t>
+          <t>A 15747-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3471,10 +3476,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45785</v>
+        <v>46107</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3487,7 +3492,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3530,7 +3535,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 5068-2026</t>
+          <t>A 16667-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3544,10 +3549,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46049</v>
+        <v>45030</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3560,7 +3565,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3603,7 +3608,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 59266-2025</t>
+          <t>A 3430-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3617,10 +3622,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45988</v>
+        <v>46042</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3633,7 +3638,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.8</v>
+        <v>5.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3676,7 +3681,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 22262-2023</t>
+          <t>A 22792-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3690,10 +3695,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45070</v>
+        <v>45448</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3706,7 +3711,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3749,7 +3754,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 17980-2025</t>
+          <t>A 47139-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3763,10 +3768,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45761</v>
+        <v>45929</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3779,7 +3784,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3822,7 +3827,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 6335-2022</t>
+          <t>A 18926-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3836,10 +3841,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44600</v>
+        <v>46127</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3852,7 +3857,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3895,7 +3900,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 16667-2023</t>
+          <t>A 8332-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3909,10 +3914,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45030</v>
+        <v>45708</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3925,7 +3930,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3968,7 +3973,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 19282-2025</t>
+          <t>A 14543-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3978,14 +3983,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45769</v>
+        <v>45394</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3998,7 +4003,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4041,7 +4046,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 6365-2026</t>
+          <t>A 34810-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4055,10 +4060,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46051</v>
+        <v>45141</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4071,7 +4076,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.9</v>
+        <v>7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4114,7 +4119,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 47139-2025</t>
+          <t>A 20170-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4128,10 +4133,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45929</v>
+        <v>45434</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4144,7 +4149,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4187,7 +4192,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 1920-2025</t>
+          <t>A 62403-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4201,10 +4206,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45671</v>
+        <v>44923</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4217,7 +4222,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4260,7 +4265,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 37907-2025</t>
+          <t>A 43294-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4274,10 +4279,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45880</v>
+        <v>45910</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4289,13 +4294,8 @@
           <t>SVALÖV</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>5.7</v>
+        <v>2.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 40470-2025</t>
+          <t>A 62201-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4348,14 +4348,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45895</v>
+        <v>46006</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.1</v>
+        <v>22.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 8332-2025</t>
+          <t>A 4964-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45708</v>
+        <v>44593</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 44112-2023</t>
+          <t>A 15157-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45188</v>
+        <v>45016</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>44991</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 11922-2023</t>
+          <t>A 11177-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44993</v>
+        <v>44987</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 14533-2026</t>
+          <t>A 16215-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46100</v>
+        <v>44670</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 15747-2026</t>
+          <t>A 61620-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46107</v>
+        <v>44910</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 3430-2026</t>
+          <t>A 43466-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46042</v>
+        <v>45911</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 43294-2025</t>
+          <t>A 10209-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45910</v>
+        <v>44986</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 18926-2026</t>
+          <t>A 43004-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46127</v>
+        <v>45909</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 34810-2023</t>
+          <t>A 44107-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45141</v>
+        <v>45188</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>7</v>
+        <v>2.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 43466-2025</t>
+          <t>A 22262-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5155,10 +5155,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45911</v>
+        <v>45070</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 62201-2025</t>
+          <t>A 18438-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46006</v>
+        <v>46127</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>22.1</v>
+        <v>1.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 43004-2025</t>
+          <t>A 49032-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45909</v>
+        <v>44860</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 35587-2024</t>
+          <t>A 24286-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45531</v>
+        <v>46169</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 8924-2023</t>
+          <t>A 58970-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44974</v>
+        <v>45987</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>6.8</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 1901-2025</t>
+          <t>A 8924-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45671</v>
+        <v>44974</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5579,7 +5579,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 22794-2024</t>
+          <t>A 5068-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45448</v>
+        <v>46049</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 32620-2023</t>
+          <t>A 25522-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45111</v>
+        <v>46177</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.4</v>
+        <v>8.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5725,7 +5725,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 18438-2026</t>
+          <t>A 18121-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46127</v>
+        <v>45761</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5798,7 +5798,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 44196-2024</t>
+          <t>A 59266-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45573</v>
+        <v>45988</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 24286-2026</t>
+          <t>A 6365-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46169</v>
+        <v>46051</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5944,7 +5944,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 17731-2025</t>
+          <t>A 497-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5954,14 +5954,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45758</v>
+        <v>44930</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 58970-2025</t>
+          <t>A 11633-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45987</v>
+        <v>45373</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>4.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6090,7 +6090,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 14543-2024</t>
+          <t>A 11922-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6104,10 +6104,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45394</v>
+        <v>44993</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6163,7 +6163,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 25522-2026</t>
+          <t>A 6335-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46177</v>
+        <v>44600</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>8.5</v>
+        <v>4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 13273-2024</t>
+          <t>A 25832-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6250,10 +6250,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45386</v>
+        <v>46178</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>12.4</v>
+        <v>7.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 29337-2026</t>
+          <t>A 14546-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6323,10 +6323,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46202</v>
+        <v>45394</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6382,7 +6382,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 25832-2026</t>
+          <t>A 32620-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6396,10 +6396,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46178</v>
+        <v>45111</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>7.8</v>
+        <v>1.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6455,7 +6455,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 30202-2026</t>
+          <t>A 29337-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6469,10 +6469,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46206</v>
+        <v>46202</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6528,7 +6528,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 30535-2026</t>
+          <t>A 10196-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46210</v>
+        <v>45719</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6601,7 +6601,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 22792-2024</t>
+          <t>A 30535-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45448</v>
+        <v>46210</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6674,7 +6674,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 14546-2024</t>
+          <t>A 30202-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6688,10 +6688,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45394</v>
+        <v>46206</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6747,7 +6747,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 18121-2025</t>
+          <t>A 44112-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6761,10 +6761,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45761</v>
+        <v>45188</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6820,7 +6820,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 16215-2022</t>
+          <t>A 35911-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6834,10 +6834,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44670</v>
+        <v>45148</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6893,7 +6893,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 13787-2026</t>
+          <t>A 42588-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46097</v>
+        <v>45176</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6966,7 +6966,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 13791-2026</t>
+          <t>A 1901-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6980,10 +6980,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46097</v>
+        <v>45671</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>4.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 27380-2026</t>
+          <t>A 1920-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46189</v>
+        <v>45671</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7112,7 +7112,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 15487-2025</t>
+          <t>A 43736-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45747</v>
+        <v>45182</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7185,7 +7185,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 4964-2022</t>
+          <t>A 9716-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7199,10 +7199,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44593</v>
+        <v>44617</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7258,7 +7258,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 37354-2022</t>
+          <t>A 1592-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44806</v>
+        <v>45306</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7331,7 +7331,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 11633-2024</t>
+          <t>A 4149-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7341,14 +7341,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45373</v>
+        <v>44588</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.9</v>
+        <v>1.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7404,7 +7404,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 20170-2024</t>
+          <t>A 15487-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7418,10 +7418,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45434</v>
+        <v>45747</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7477,7 +7477,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 61620-2022</t>
+          <t>A 11101-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7491,10 +7491,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44910</v>
+        <v>44986</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 5190-2024</t>
+          <t>A 5184-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7567,7 +7567,7 @@
         <v>45330</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7623,7 +7623,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 21774-2024</t>
+          <t>A 13273-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7637,10 +7637,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45442</v>
+        <v>45386</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.6</v>
+        <v>12.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7696,7 +7696,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 62403-2022</t>
+          <t>A 44196-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44923</v>
+        <v>45573</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7769,7 +7769,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 43736-2023</t>
+          <t>A 13791-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45182</v>
+        <v>46097</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7842,7 +7842,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 42588-2023</t>
+          <t>A 21556-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7856,10 +7856,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45176</v>
+        <v>45782</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7915,7 +7915,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 15157-2023</t>
+          <t>A 21541-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7929,10 +7929,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45016</v>
+        <v>45782</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7988,7 +7988,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 497-2023</t>
+          <t>A 27380-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8002,10 +8002,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44930</v>
+        <v>46189</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8061,7 +8061,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 5184-2024</t>
+          <t>A 21814-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8075,10 +8075,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45330</v>
+        <v>45783</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8134,7 +8134,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 44107-2023</t>
+          <t>A 13787-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45188</v>
+        <v>46097</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8207,7 +8207,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 10196-2025</t>
+          <t>A 20047-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8221,10 +8221,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45719</v>
+        <v>45434</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8280,7 +8280,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 4149-2022</t>
+          <t>A 34808-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8290,14 +8290,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44588</v>
+        <v>45526</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8353,7 +8353,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 13245-2024</t>
+          <t>A 5167-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8367,10 +8367,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45386</v>
+        <v>45330</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>13</v>
+        <v>6.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 21814-2025</t>
+          <t>A 23747-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45783</v>
+        <v>45793</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8499,7 +8499,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 21541-2025</t>
+          <t>A 24513-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45782</v>
+        <v>45798</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.1</v>
+        <v>0.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8572,7 +8572,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 21556-2025</t>
+          <t>A 27310-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45782</v>
+        <v>45096</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8645,7 +8645,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 20047-2024</t>
+          <t>A 22063-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8659,10 +8659,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45434</v>
+        <v>45785</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8718,7 +8718,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 34808-2024</t>
+          <t>A 17980-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8732,10 +8732,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45526</v>
+        <v>45761</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8791,7 +8791,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 5167-2024</t>
+          <t>A 19282-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8801,14 +8801,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45330</v>
+        <v>45769</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>6.5</v>
+        <v>0.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8881,7 +8881,7 @@
         <v>45854</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>

--- a/Översikt SVALÖV.xlsx
+++ b/Översikt SVALÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45910</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 15475-2024</t>
+          <t>A 38522-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45401</v>
+        <v>45884</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.7</v>
+        <v>2.6</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -848,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -857,10 +857,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -869,146 +869,146 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Skogsknipprot
+Stor häxört</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 38522-2025 artfynd.xlsx", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 38522-2025 karta.png", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 38522-2025 georefererad karta.tif", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 38522-2025 FSC-klagomål.docx", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 38522-2025 FSC-klagomål mail.docx", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 38522-2025 tillsynsbegäran.docx", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 38522-2025 tillsynsbegäran mail.docx", "A 38522-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 15475-2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45401</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SVALÖV</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>1</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Ask
 Strutbräken</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15475-2024 artfynd.xlsx", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15475-2024 karta.png", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15475-2024 georefererad karta.tif", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15475-2024 FSC-klagomål.docx", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15475-2024 FSC-klagomål mail.docx", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15475-2024 tillsynsbegäran.docx", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15475-2024 tillsynsbegäran mail.docx", "A 15475-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 38522-2025</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45884</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SVALÖV</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Skogsknipprot
-Stor häxört</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 38522-2025 artfynd.xlsx", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 38522-2025 karta.png", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 38522-2025 georefererad karta.tif", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 38522-2025 FSC-klagomål.docx", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 38522-2025 FSC-klagomål mail.docx", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 38522-2025 tillsynsbegäran.docx", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 38522-2025 tillsynsbegäran mail.docx", "A 38522-2025")</f>
         <v/>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
         <v>45645</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 15456-2024</t>
+          <t>A 11170-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45401</v>
+        <v>44987</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1187,46 +1187,46 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Lundticka</t>
+          <t>Korndådra</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15456-2024 artfynd.xlsx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11170-2023 artfynd.xlsx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15456-2024 karta.png", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11170-2023 karta.png", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15456-2024 georefererad karta.tif", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11170-2023 georefererad karta.tif", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15456-2024 FSC-klagomål.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11170-2023 FSC-klagomål.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15456-2024 FSC-klagomål mail.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11170-2023 FSC-klagomål mail.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15456-2024 tillsynsbegäran.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11170-2023 tillsynsbegäran.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15456-2024 tillsynsbegäran mail.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11170-2023 tillsynsbegäran mail.docx", "A 11170-2023")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 11170-2023</t>
+          <t>A 15456-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44987</v>
+        <v>45401</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1268,10 +1268,10 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1292,46 +1292,46 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Korndådra</t>
+          <t>Lundticka</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11170-2023 artfynd.xlsx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15456-2024 artfynd.xlsx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11170-2023 karta.png", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15456-2024 karta.png", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11170-2023 georefererad karta.tif", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15456-2024 georefererad karta.tif", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11170-2023 FSC-klagomål.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15456-2024 FSC-klagomål.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11170-2023 FSC-klagomål mail.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15456-2024 FSC-klagomål mail.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11170-2023 tillsynsbegäran.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15456-2024 tillsynsbegäran.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11170-2023 tillsynsbegäran mail.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15456-2024 tillsynsbegäran mail.docx", "A 15456-2024")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 1577-2024</t>
+          <t>A 20125-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45306</v>
+        <v>45434</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>21.2</v>
+        <v>5.7</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1401,42 +1401,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 20125-2024 artfynd.xlsx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 20125-2024 karta.png", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 20125-2024 georefererad karta.tif", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 20125-2024 FSC-klagomål.docx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 20125-2024 FSC-klagomål mail.docx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 20125-2024 tillsynsbegäran.docx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 20125-2024 tillsynsbegäran mail.docx", "A 20125-2024")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 20125-2024</t>
+          <t>A 52664-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45434</v>
+        <v>45225</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
@@ -1506,35 +1506,35 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 20125-2024 artfynd.xlsx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 52664-2023 artfynd.xlsx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 20125-2024 karta.png", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 52664-2023 karta.png", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 20125-2024 georefererad karta.tif", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 52664-2023 georefererad karta.tif", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 20125-2024 FSC-klagomål.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 52664-2023 FSC-klagomål.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 20125-2024 FSC-klagomål mail.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 52664-2023 FSC-klagomål mail.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 20125-2024 tillsynsbegäran.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 52664-2023 tillsynsbegäran.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 20125-2024 tillsynsbegäran mail.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 52664-2023 tillsynsbegäran mail.docx", "A 52664-2023")</f>
         <v/>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
         <v>45373</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 52664-2023</t>
+          <t>A 54127-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1660,10 +1660,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45225</v>
+        <v>45964</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1676,17 +1676,17 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>6.4</v>
+        <v>1.3</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
       </c>
       <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
@@ -1700,7 +1700,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1712,46 +1712,50 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 52664-2023 artfynd.xlsx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 54127-2025 artfynd.xlsx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 52664-2023 karta.png", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 54127-2025 karta.png", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 52664-2023 georefererad karta.tif", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 54127-2025 georefererad karta.tif", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 52664-2023 FSC-klagomål.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 54127-2025 FSC-klagomål.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 52664-2023 FSC-klagomål mail.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 54127-2025 FSC-klagomål mail.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 52664-2023 tillsynsbegäran.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 54127-2025 tillsynsbegäran.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 52664-2023 tillsynsbegäran mail.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 54127-2025 tillsynsbegäran mail.docx", "A 54127-2025")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/fåglar/A 54127-2025 prioriterade fågelarter.docx", "A 54127-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 54127-2025</t>
+          <t>A 1577-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1765,10 +1769,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45964</v>
+        <v>45306</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1781,7 +1785,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>21.2</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1790,7 +1794,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1805,7 +1809,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1817,43 +1821,39 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 54127-2025 artfynd.xlsx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 54127-2025 karta.png", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 54127-2025 georefererad karta.tif", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 54127-2025 FSC-klagomål.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 54127-2025 FSC-klagomål mail.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 54127-2025 tillsynsbegäran.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 54127-2025 tillsynsbegäran mail.docx", "A 54127-2025")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/fåglar/A 54127-2025 prioriterade fågelarter.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
         <v>45351</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>45218</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>44763</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44598</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44483</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44847</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44501</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>44831</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>44854</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 13245-2024</t>
+          <t>A 49032-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2595,10 +2595,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45386</v>
+        <v>44860</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>13</v>
+        <v>3.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 37907-2025</t>
+          <t>A 35911-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45880</v>
+        <v>45148</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2683,13 +2683,8 @@
           <t>SVALÖV</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>5.7</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2732,7 +2727,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 40470-2025</t>
+          <t>A 11101-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2742,14 +2737,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45895</v>
+        <v>44986</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2762,7 +2757,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2805,7 +2800,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 21774-2024</t>
+          <t>A 9716-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2819,10 +2814,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45442</v>
+        <v>44617</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2835,7 +2830,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2878,7 +2873,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 37354-2022</t>
+          <t>A 11177-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2892,10 +2887,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44806</v>
+        <v>44987</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2908,7 +2903,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2951,7 +2946,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 5190-2024</t>
+          <t>A 1592-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2965,10 +2960,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45330</v>
+        <v>45306</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2981,7 +2976,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3024,7 +3019,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 17731-2025</t>
+          <t>A 10209-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3034,14 +3029,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45758</v>
+        <v>44986</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3054,7 +3049,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3097,7 +3092,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 22794-2024</t>
+          <t>A 24513-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3111,10 +3106,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45448</v>
+        <v>45798</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3127,7 +3122,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.8</v>
+        <v>0.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3170,7 +3165,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 35587-2024</t>
+          <t>A 27310-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3184,10 +3179,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45531</v>
+        <v>45096</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3200,7 +3195,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3243,7 +3238,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 14533-2026</t>
+          <t>A 22262-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3257,10 +3252,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46100</v>
+        <v>45070</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3273,7 +3268,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3316,7 +3311,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 42706-2025</t>
+          <t>A 6335-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3330,10 +3325,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45908</v>
+        <v>44600</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3346,7 +3341,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3389,7 +3384,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 43425-2025</t>
+          <t>A 16667-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3403,10 +3398,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45911</v>
+        <v>45030</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3419,7 +3414,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3462,7 +3457,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 15747-2026</t>
+          <t>A 42706-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3476,10 +3471,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46107</v>
+        <v>45908</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3492,7 +3487,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3535,7 +3530,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 16667-2023</t>
+          <t>A 22063-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3549,10 +3544,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45030</v>
+        <v>45785</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3565,7 +3560,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3608,7 +3603,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 3430-2026</t>
+          <t>A 43425-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3622,10 +3617,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46042</v>
+        <v>45911</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3638,7 +3633,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>5.7</v>
+        <v>2.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3681,7 +3676,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 22792-2024</t>
+          <t>A 17980-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3695,10 +3690,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45448</v>
+        <v>45761</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3711,7 +3706,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3754,7 +3749,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 47139-2025</t>
+          <t>A 1920-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3768,10 +3763,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45929</v>
+        <v>45671</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3784,7 +3779,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3827,7 +3822,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 18926-2026</t>
+          <t>A 19282-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3837,14 +3832,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46127</v>
+        <v>45769</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3857,7 +3852,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3917,7 +3912,7 @@
         <v>45708</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3973,7 +3968,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 14543-2024</t>
+          <t>A 47139-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3987,10 +3982,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45394</v>
+        <v>45929</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4003,7 +3998,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4046,7 +4041,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 34810-2023</t>
+          <t>A 44112-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4060,10 +4055,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45141</v>
+        <v>45188</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4076,7 +4071,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>7</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4119,7 +4114,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 20170-2024</t>
+          <t>A 37907-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4133,10 +4128,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45434</v>
+        <v>45880</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4148,8 +4143,13 @@
           <t>SVALÖV</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>5.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 62403-2022</t>
+          <t>A 40470-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4202,14 +4202,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44923</v>
+        <v>45895</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.2</v>
+        <v>0.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 43294-2025</t>
+          <t>A 11491-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45910</v>
+        <v>44991</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 62201-2025</t>
+          <t>A 5068-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46006</v>
+        <v>46049</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>22.1</v>
+        <v>3.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 4964-2022</t>
+          <t>A 11922-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44593</v>
+        <v>44993</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 15157-2023</t>
+          <t>A 59266-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45016</v>
+        <v>45988</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 11491-2023</t>
+          <t>A 43294-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44991</v>
+        <v>45910</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 11177-2023</t>
+          <t>A 6365-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44987</v>
+        <v>46051</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 16215-2022</t>
+          <t>A 43466-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44670</v>
+        <v>45911</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 61620-2022</t>
+          <t>A 43004-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44910</v>
+        <v>45909</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 43466-2025</t>
+          <t>A 35587-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45911</v>
+        <v>45531</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.5</v>
+        <v>1.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 10209-2023</t>
+          <t>A 8924-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44986</v>
+        <v>44974</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.2</v>
+        <v>6.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 43004-2025</t>
+          <t>A 1901-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45909</v>
+        <v>45671</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 44107-2023</t>
+          <t>A 14533-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45188</v>
+        <v>46100</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 22262-2023</t>
+          <t>A 22794-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5155,10 +5155,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45070</v>
+        <v>45448</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 18438-2026</t>
+          <t>A 15747-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46127</v>
+        <v>46107</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 49032-2022</t>
+          <t>A 32620-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44860</v>
+        <v>45111</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 24286-2026</t>
+          <t>A 3430-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46169</v>
+        <v>46042</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.9</v>
+        <v>5.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 58970-2025</t>
+          <t>A 44196-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45987</v>
+        <v>45573</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 8924-2023</t>
+          <t>A 17731-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5516,14 +5516,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44974</v>
+        <v>45758</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>6.8</v>
+        <v>0.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5579,7 +5579,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 5068-2026</t>
+          <t>A 14543-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46049</v>
+        <v>45394</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 25522-2026</t>
+          <t>A 18926-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46177</v>
+        <v>46127</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>8.5</v>
+        <v>1.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5725,7 +5725,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 18121-2025</t>
+          <t>A 13273-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45761</v>
+        <v>45386</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.7</v>
+        <v>12.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5798,7 +5798,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 59266-2025</t>
+          <t>A 22792-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45988</v>
+        <v>45448</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5871,7 +5871,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 6365-2026</t>
+          <t>A 34810-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46051</v>
+        <v>45141</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.9</v>
+        <v>7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5944,7 +5944,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 497-2023</t>
+          <t>A 14546-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5958,10 +5958,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44930</v>
+        <v>45394</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6017,7 +6017,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 11633-2024</t>
+          <t>A 62201-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45373</v>
+        <v>46006</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.9</v>
+        <v>22.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6090,7 +6090,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 11922-2023</t>
+          <t>A 18121-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6104,10 +6104,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44993</v>
+        <v>45761</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6163,7 +6163,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 6335-2022</t>
+          <t>A 16215-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44600</v>
+        <v>44670</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 25832-2026</t>
+          <t>A 15487-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6250,10 +6250,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46178</v>
+        <v>45747</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>7.8</v>
+        <v>0.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 14546-2024</t>
+          <t>A 4964-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6323,10 +6323,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45394</v>
+        <v>44593</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6382,7 +6382,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 32620-2023</t>
+          <t>A 37354-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6396,10 +6396,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45111</v>
+        <v>44806</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 29337-2026</t>
+          <t>A 11633-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6469,10 +6469,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46202</v>
+        <v>45373</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2</v>
+        <v>4.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6528,7 +6528,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 10196-2025</t>
+          <t>A 18438-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45719</v>
+        <v>46127</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6601,7 +6601,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 30535-2026</t>
+          <t>A 24286-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46210</v>
+        <v>46169</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6674,7 +6674,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 30202-2026</t>
+          <t>A 58970-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6688,10 +6688,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46206</v>
+        <v>45987</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6747,7 +6747,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 44112-2023</t>
+          <t>A 25522-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6761,10 +6761,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45188</v>
+        <v>46177</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.5</v>
+        <v>8.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6820,7 +6820,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 35911-2023</t>
+          <t>A 20170-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6834,10 +6834,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45148</v>
+        <v>45434</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6893,7 +6893,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 42588-2023</t>
+          <t>A 29337-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45176</v>
+        <v>46202</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6966,7 +6966,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 1901-2025</t>
+          <t>A 25832-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6980,10 +6980,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45671</v>
+        <v>46178</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 1920-2025</t>
+          <t>A 61620-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45671</v>
+        <v>44910</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7112,7 +7112,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 43736-2023</t>
+          <t>A 5190-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45182</v>
+        <v>45330</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7185,7 +7185,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 9716-2022</t>
+          <t>A 30202-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7199,10 +7199,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44617</v>
+        <v>46206</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7258,7 +7258,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 1592-2024</t>
+          <t>A 21774-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45306</v>
+        <v>45442</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7331,7 +7331,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 4149-2022</t>
+          <t>A 62403-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7341,14 +7341,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44588</v>
+        <v>44923</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7404,7 +7404,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 15487-2025</t>
+          <t>A 30535-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7418,10 +7418,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45747</v>
+        <v>46210</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7477,7 +7477,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 11101-2023</t>
+          <t>A 43736-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7491,10 +7491,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44986</v>
+        <v>45182</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7550,7 +7550,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 5184-2024</t>
+          <t>A 42588-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7564,10 +7564,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45330</v>
+        <v>45176</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7623,7 +7623,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 13273-2024</t>
+          <t>A 15157-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7637,10 +7637,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45386</v>
+        <v>45016</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>12.4</v>
+        <v>2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7696,7 +7696,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 44196-2024</t>
+          <t>A 497-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45573</v>
+        <v>44930</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7769,7 +7769,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 13791-2026</t>
+          <t>A 5184-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46097</v>
+        <v>45330</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7842,7 +7842,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 21556-2025</t>
+          <t>A 44107-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7856,10 +7856,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45782</v>
+        <v>45188</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7915,7 +7915,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 21541-2025</t>
+          <t>A 10196-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7929,10 +7929,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45782</v>
+        <v>45719</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7988,7 +7988,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 27380-2026</t>
+          <t>A 4149-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7998,14 +7998,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46189</v>
+        <v>44588</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8061,7 +8061,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 21814-2025</t>
+          <t>A 13245-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8075,10 +8075,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45783</v>
+        <v>45386</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.4</v>
+        <v>13</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8134,7 +8134,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 13787-2026</t>
+          <t>A 13791-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8151,7 +8151,7 @@
         <v>46097</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8207,7 +8207,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 20047-2024</t>
+          <t>A 13787-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8221,10 +8221,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45434</v>
+        <v>46097</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8280,7 +8280,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 34808-2024</t>
+          <t>A 27380-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8294,10 +8294,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45526</v>
+        <v>46189</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8353,7 +8353,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 5167-2024</t>
+          <t>A 21814-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8367,10 +8367,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45330</v>
+        <v>45783</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>6.5</v>
+        <v>2.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 23747-2025</t>
+          <t>A 21541-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45793</v>
+        <v>45782</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8499,7 +8499,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 24513-2025</t>
+          <t>A 21556-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45798</v>
+        <v>45782</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8572,7 +8572,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 27310-2023</t>
+          <t>A 20047-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45096</v>
+        <v>45434</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8645,7 +8645,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 22063-2025</t>
+          <t>A 34808-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8659,10 +8659,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45785</v>
+        <v>45526</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8718,7 +8718,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 17980-2025</t>
+          <t>A 5167-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8732,10 +8732,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45761</v>
+        <v>45330</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3.4</v>
+        <v>6.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8791,7 +8791,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 19282-2025</t>
+          <t>A 23747-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8801,14 +8801,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45769</v>
+        <v>45793</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8881,7 +8881,7 @@
         <v>45854</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>

--- a/Översikt SVALÖV.xlsx
+++ b/Översikt SVALÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45910</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 38522-2025</t>
+          <t>A 15475-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45884</v>
+        <v>45401</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -833,14 +833,14 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
@@ -848,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -857,10 +857,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -869,146 +869,146 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15475-2024 artfynd.xlsx", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15475-2024 karta.png", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15475-2024 georefererad karta.tif", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15475-2024 FSC-klagomål.docx", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15475-2024 FSC-klagomål mail.docx", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15475-2024 tillsynsbegäran.docx", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15475-2024 tillsynsbegäran mail.docx", "A 15475-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 38522-2025</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SVALÖV</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Skogsknipprot
 Stor häxört</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 38522-2025 artfynd.xlsx", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 38522-2025 karta.png", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 38522-2025 georefererad karta.tif", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 38522-2025 FSC-klagomål.docx", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 38522-2025 FSC-klagomål mail.docx", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 38522-2025 tillsynsbegäran.docx", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 38522-2025 tillsynsbegäran mail.docx", "A 38522-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 15475-2024</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45401</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SVALÖV</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15475-2024 artfynd.xlsx", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15475-2024 karta.png", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15475-2024 georefererad karta.tif", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15475-2024 FSC-klagomål.docx", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15475-2024 FSC-klagomål mail.docx", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15475-2024 tillsynsbegäran.docx", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15475-2024 tillsynsbegäran mail.docx", "A 15475-2024")</f>
         <v/>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
         <v>45645</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 11170-2023</t>
+          <t>A 15456-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44987</v>
+        <v>45401</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1187,46 +1187,46 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Korndådra</t>
+          <t>Lundticka</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11170-2023 artfynd.xlsx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15456-2024 artfynd.xlsx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11170-2023 karta.png", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15456-2024 karta.png", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11170-2023 georefererad karta.tif", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15456-2024 georefererad karta.tif", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11170-2023 FSC-klagomål.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15456-2024 FSC-klagomål.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11170-2023 FSC-klagomål mail.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15456-2024 FSC-klagomål mail.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11170-2023 tillsynsbegäran.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15456-2024 tillsynsbegäran.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11170-2023 tillsynsbegäran mail.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15456-2024 tillsynsbegäran mail.docx", "A 15456-2024")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 15456-2024</t>
+          <t>A 1577-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45401</v>
+        <v>45306</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.5</v>
+        <v>21.2</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1268,7 +1268,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1280,10 +1280,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1296,35 +1296,35 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Lundticka</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15456-2024 artfynd.xlsx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15456-2024 karta.png", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15456-2024 georefererad karta.tif", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15456-2024 FSC-klagomål.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15456-2024 FSC-klagomål mail.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15456-2024 tillsynsbegäran.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15456-2024 tillsynsbegäran mail.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
         <v>45434</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 52664-2023</t>
+          <t>A 11672-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45225</v>
+        <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1466,31 +1466,31 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>6.4</v>
+        <v>13.9</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1502,46 +1502,46 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 52664-2023 artfynd.xlsx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11672-2024 artfynd.xlsx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 52664-2023 karta.png", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11672-2024 karta.png", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 52664-2023 georefererad karta.tif", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11672-2024 georefererad karta.tif", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 52664-2023 FSC-klagomål.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11672-2024 FSC-klagomål.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 52664-2023 FSC-klagomål mail.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11672-2024 FSC-klagomål mail.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 52664-2023 tillsynsbegäran.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11672-2024 tillsynsbegäran.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 52664-2023 tillsynsbegäran mail.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11672-2024 tillsynsbegäran mail.docx", "A 11672-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 11672-2024</t>
+          <t>A 52664-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45373</v>
+        <v>45225</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1571,16 +1571,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>13.9</v>
+        <v>6.4</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1595,7 +1595,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1607,39 +1607,39 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11672-2024 artfynd.xlsx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 52664-2023 artfynd.xlsx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11672-2024 karta.png", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 52664-2023 karta.png", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11672-2024 georefererad karta.tif", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 52664-2023 georefererad karta.tif", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11672-2024 FSC-klagomål.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 52664-2023 FSC-klagomål.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11672-2024 FSC-klagomål mail.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 52664-2023 FSC-klagomål mail.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11672-2024 tillsynsbegäran.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 52664-2023 tillsynsbegäran.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11672-2024 tillsynsbegäran mail.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 52664-2023 tillsynsbegäran mail.docx", "A 52664-2023")</f>
         <v/>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
         <v>45964</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 1577-2024</t>
+          <t>A 11170-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45306</v>
+        <v>44987</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1785,23 +1785,23 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>21.2</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
@@ -1809,10 +1809,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1821,39 +1821,39 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Korndådra</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11170-2023 artfynd.xlsx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11170-2023 karta.png", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11170-2023 georefererad karta.tif", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11170-2023 FSC-klagomål.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11170-2023 FSC-klagomål mail.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11170-2023 tillsynsbegäran.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11170-2023 tillsynsbegäran mail.docx", "A 11170-2023")</f>
         <v/>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
         <v>45351</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>45218</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>44763</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44598</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44483</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44847</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44501</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>44831</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>44854</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 49032-2022</t>
+          <t>A 13245-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2595,10 +2595,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44860</v>
+        <v>45386</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.7</v>
+        <v>13</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 35911-2023</t>
+          <t>A 21774-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45148</v>
+        <v>45442</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 11101-2023</t>
+          <t>A 35587-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44986</v>
+        <v>45531</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2800,7 +2800,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 9716-2022</t>
+          <t>A 22794-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2814,10 +2814,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44617</v>
+        <v>45448</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 11177-2023</t>
+          <t>A 16667-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44987</v>
+        <v>45030</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 1592-2024</t>
+          <t>A 6365-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45306</v>
+        <v>46051</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3019,7 +3019,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 10209-2023</t>
+          <t>A 8332-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44986</v>
+        <v>45708</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3092,7 +3092,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 24513-2025</t>
+          <t>A 14543-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3106,10 +3106,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45798</v>
+        <v>45394</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3165,7 +3165,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 27310-2023</t>
+          <t>A 22063-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45096</v>
+        <v>45785</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3238,7 +3238,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 22262-2023</t>
+          <t>A 20170-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45070</v>
+        <v>45434</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3311,7 +3311,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 6335-2022</t>
+          <t>A 17980-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44600</v>
+        <v>45761</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3384,7 +3384,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 16667-2023</t>
+          <t>A 19282-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3394,14 +3394,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45030</v>
+        <v>45769</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 42706-2025</t>
+          <t>A 14533-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45908</v>
+        <v>46100</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 22063-2025</t>
+          <t>A 62403-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45785</v>
+        <v>44923</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3603,7 +3603,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 43425-2025</t>
+          <t>A 15747-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45911</v>
+        <v>46107</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3676,7 +3676,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 17980-2025</t>
+          <t>A 3430-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45761</v>
+        <v>46042</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 1920-2025</t>
+          <t>A 15157-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45671</v>
+        <v>45016</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 19282-2025</t>
+          <t>A 11491-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3832,14 +3832,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45769</v>
+        <v>44991</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3895,7 +3895,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 8332-2025</t>
+          <t>A 37907-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45708</v>
+        <v>45880</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3924,8 +3924,13 @@
           <t>SVALÖV</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>5.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3968,7 +3973,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 47139-2025</t>
+          <t>A 40470-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3978,14 +3983,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45929</v>
+        <v>45895</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3998,7 +4003,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4041,7 +4046,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 44112-2023</t>
+          <t>A 18926-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4055,10 +4060,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45188</v>
+        <v>46127</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4071,7 +4076,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4114,7 +4119,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 37907-2025</t>
+          <t>A 10209-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4128,10 +4133,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45880</v>
+        <v>44986</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4143,13 +4148,8 @@
           <t>SVALÖV</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>5.7</v>
+        <v>1.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 40470-2025</t>
+          <t>A 42706-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4202,14 +4202,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45895</v>
+        <v>45908</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 11491-2023</t>
+          <t>A 43425-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44991</v>
+        <v>45911</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 5068-2026</t>
+          <t>A 34810-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46049</v>
+        <v>45141</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 11922-2023</t>
+          <t>A 44107-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44993</v>
+        <v>45188</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 59266-2025</t>
+          <t>A 62201-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45988</v>
+        <v>46006</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.8</v>
+        <v>22.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 43294-2025</t>
+          <t>A 22262-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45910</v>
+        <v>45070</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 6365-2026</t>
+          <t>A 49032-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46051</v>
+        <v>44860</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 43466-2025</t>
+          <t>A 47139-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45911</v>
+        <v>45929</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 43004-2025</t>
+          <t>A 18121-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45909</v>
+        <v>45761</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 35587-2024</t>
+          <t>A 18438-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45531</v>
+        <v>46127</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 8924-2023</t>
+          <t>A 24286-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44974</v>
+        <v>46169</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>6.8</v>
+        <v>0.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 1901-2025</t>
+          <t>A 58970-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45671</v>
+        <v>45987</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.2</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 14533-2026</t>
+          <t>A 6335-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46100</v>
+        <v>44600</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 22794-2024</t>
+          <t>A 25522-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5155,10 +5155,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45448</v>
+        <v>46177</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.8</v>
+        <v>8.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 15747-2026</t>
+          <t>A 10196-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46107</v>
+        <v>45719</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 32620-2023</t>
+          <t>A 44112-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45111</v>
+        <v>45188</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 3430-2026</t>
+          <t>A 35911-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46042</v>
+        <v>45148</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>5.7</v>
+        <v>0.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 44196-2024</t>
+          <t>A 43294-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45573</v>
+        <v>45910</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 17731-2025</t>
+          <t>A 42588-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5516,14 +5516,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45758</v>
+        <v>45176</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5579,7 +5579,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 14543-2024</t>
+          <t>A 1901-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45394</v>
+        <v>45671</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 18926-2026</t>
+          <t>A 1920-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46127</v>
+        <v>45671</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5725,7 +5725,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 13273-2024</t>
+          <t>A 25832-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45386</v>
+        <v>46178</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>12.4</v>
+        <v>7.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5798,7 +5798,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 22792-2024</t>
+          <t>A 43736-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45448</v>
+        <v>45182</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5871,7 +5871,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 34810-2023</t>
+          <t>A 9716-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45141</v>
+        <v>44617</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5944,7 +5944,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 14546-2024</t>
+          <t>A 29337-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5958,10 +5958,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45394</v>
+        <v>46202</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6017,7 +6017,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 62201-2025</t>
+          <t>A 30535-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46006</v>
+        <v>46210</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>22.1</v>
+        <v>0.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6090,7 +6090,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 18121-2025</t>
+          <t>A 30202-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6104,10 +6104,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45761</v>
+        <v>46206</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6163,7 +6163,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 16215-2022</t>
+          <t>A 43466-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44670</v>
+        <v>45911</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 15487-2025</t>
+          <t>A 37354-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6250,10 +6250,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45747</v>
+        <v>44806</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 4964-2022</t>
+          <t>A 5190-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6323,10 +6323,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44593</v>
+        <v>45330</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6382,7 +6382,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 37354-2022</t>
+          <t>A 17731-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6392,14 +6392,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44806</v>
+        <v>45758</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6455,7 +6455,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 11633-2024</t>
+          <t>A 43004-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6469,10 +6469,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45373</v>
+        <v>45909</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.9</v>
+        <v>1.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6528,7 +6528,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 18438-2026</t>
+          <t>A 22792-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46127</v>
+        <v>45448</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6601,7 +6601,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 24286-2026</t>
+          <t>A 4964-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46169</v>
+        <v>44593</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6674,7 +6674,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 58970-2025</t>
+          <t>A 13791-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6688,10 +6688,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45987</v>
+        <v>46097</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 25522-2026</t>
+          <t>A 11177-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6761,10 +6761,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46177</v>
+        <v>44987</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>8.5</v>
+        <v>1.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6820,7 +6820,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 20170-2024</t>
+          <t>A 13787-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6834,10 +6834,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45434</v>
+        <v>46097</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6893,7 +6893,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 29337-2026</t>
+          <t>A 16215-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46202</v>
+        <v>44670</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6966,7 +6966,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 25832-2026</t>
+          <t>A 61620-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6980,10 +6980,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46178</v>
+        <v>44910</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>7.8</v>
+        <v>1.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 61620-2022</t>
+          <t>A 27380-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44910</v>
+        <v>46189</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7112,7 +7112,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 5190-2024</t>
+          <t>A 8924-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45330</v>
+        <v>44974</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.1</v>
+        <v>6.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7185,7 +7185,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 30202-2026</t>
+          <t>A 5068-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7199,10 +7199,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46206</v>
+        <v>46049</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7258,7 +7258,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 21774-2024</t>
+          <t>A 497-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45442</v>
+        <v>44930</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7331,7 +7331,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 62403-2022</t>
+          <t>A 59266-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7345,10 +7345,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44923</v>
+        <v>45988</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7404,7 +7404,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 30535-2026</t>
+          <t>A 11633-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7418,10 +7418,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46210</v>
+        <v>45373</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.8</v>
+        <v>4.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7477,7 +7477,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 43736-2023</t>
+          <t>A 11922-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7491,10 +7491,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45182</v>
+        <v>44993</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7550,7 +7550,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 42588-2023</t>
+          <t>A 14546-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7564,10 +7564,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45176</v>
+        <v>45394</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7623,7 +7623,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 15157-2023</t>
+          <t>A 32620-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7637,10 +7637,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45016</v>
+        <v>45111</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7696,7 +7696,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 497-2023</t>
+          <t>A 1592-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44930</v>
+        <v>45306</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7769,7 +7769,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 5184-2024</t>
+          <t>A 4149-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7779,14 +7779,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45330</v>
+        <v>44588</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7842,7 +7842,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 44107-2023</t>
+          <t>A 15487-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7856,10 +7856,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45188</v>
+        <v>45747</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7915,7 +7915,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 10196-2025</t>
+          <t>A 11101-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7929,10 +7929,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45719</v>
+        <v>44986</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7988,7 +7988,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 4149-2022</t>
+          <t>A 5184-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7998,14 +7998,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44588</v>
+        <v>45330</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8061,7 +8061,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 13245-2024</t>
+          <t>A 13273-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8078,7 +8078,7 @@
         <v>45386</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>13</v>
+        <v>12.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8134,7 +8134,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 13791-2026</t>
+          <t>A 44196-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46097</v>
+        <v>45573</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8207,7 +8207,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 13787-2026</t>
+          <t>A 21556-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8221,10 +8221,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46097</v>
+        <v>45782</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8280,7 +8280,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 27380-2026</t>
+          <t>A 21541-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8294,10 +8294,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46189</v>
+        <v>45782</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8370,7 +8370,7 @@
         <v>45783</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 21541-2025</t>
+          <t>A 20047-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45782</v>
+        <v>45434</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8499,7 +8499,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 21556-2025</t>
+          <t>A 34808-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45782</v>
+        <v>45526</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8572,7 +8572,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 20047-2024</t>
+          <t>A 5167-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45434</v>
+        <v>45330</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.3</v>
+        <v>6.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8645,7 +8645,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 34808-2024</t>
+          <t>A 23747-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8659,10 +8659,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45526</v>
+        <v>45793</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8718,7 +8718,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 5167-2024</t>
+          <t>A 24513-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8732,10 +8732,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45330</v>
+        <v>45798</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>6.5</v>
+        <v>0.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8791,7 +8791,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 23747-2025</t>
+          <t>A 27310-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45793</v>
+        <v>45096</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8881,7 +8881,7 @@
         <v>45854</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>

--- a/Översikt SVALÖV.xlsx
+++ b/Översikt SVALÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45910</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 15475-2024</t>
+          <t>A 38522-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45401</v>
+        <v>45884</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.7</v>
+        <v>2.6</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -848,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -857,10 +857,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -869,146 +869,146 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Skogsknipprot
+Stor häxört</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 38522-2025 artfynd.xlsx", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 38522-2025 karta.png", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 38522-2025 georefererad karta.tif", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 38522-2025 FSC-klagomål.docx", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 38522-2025 FSC-klagomål mail.docx", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 38522-2025 tillsynsbegäran.docx", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 38522-2025 tillsynsbegäran mail.docx", "A 38522-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 15475-2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45401</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SVALÖV</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>1</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Ask
 Strutbräken</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15475-2024 artfynd.xlsx", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15475-2024 karta.png", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15475-2024 georefererad karta.tif", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15475-2024 FSC-klagomål.docx", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15475-2024 FSC-klagomål mail.docx", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15475-2024 tillsynsbegäran.docx", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15475-2024 tillsynsbegäran mail.docx", "A 15475-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 38522-2025</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45884</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SVALÖV</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Skogsknipprot
-Stor häxört</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 38522-2025 artfynd.xlsx", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 38522-2025 karta.png", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 38522-2025 georefererad karta.tif", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 38522-2025 FSC-klagomål.docx", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 38522-2025 FSC-klagomål mail.docx", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 38522-2025 tillsynsbegäran.docx", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 38522-2025 tillsynsbegäran mail.docx", "A 38522-2025")</f>
         <v/>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
         <v>45645</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 15456-2024</t>
+          <t>A 11170-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45401</v>
+        <v>44987</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1187,46 +1187,46 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Lundticka</t>
+          <t>Korndådra</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15456-2024 artfynd.xlsx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11170-2023 artfynd.xlsx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15456-2024 karta.png", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11170-2023 karta.png", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15456-2024 georefererad karta.tif", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11170-2023 georefererad karta.tif", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15456-2024 FSC-klagomål.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11170-2023 FSC-klagomål.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15456-2024 FSC-klagomål mail.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11170-2023 FSC-klagomål mail.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15456-2024 tillsynsbegäran.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11170-2023 tillsynsbegäran.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15456-2024 tillsynsbegäran mail.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11170-2023 tillsynsbegäran mail.docx", "A 11170-2023")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 1577-2024</t>
+          <t>A 15456-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45306</v>
+        <v>45401</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1256,20 +1256,20 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>21.2</v>
+        <v>2.5</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
@@ -1280,10 +1280,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1296,35 +1296,35 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Lundticka</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15456-2024 artfynd.xlsx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15456-2024 karta.png", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15456-2024 georefererad karta.tif", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15456-2024 FSC-klagomål.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15456-2024 FSC-klagomål mail.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15456-2024 tillsynsbegäran.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15456-2024 tillsynsbegäran mail.docx", "A 15456-2024")</f>
         <v/>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
         <v>45434</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 11672-2024</t>
+          <t>A 52664-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45373</v>
+        <v>45225</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1466,16 +1466,16 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>13.9</v>
+        <v>6.4</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1490,7 +1490,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1502,46 +1502,46 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11672-2024 artfynd.xlsx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 52664-2023 artfynd.xlsx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11672-2024 karta.png", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 52664-2023 karta.png", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11672-2024 georefererad karta.tif", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 52664-2023 georefererad karta.tif", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11672-2024 FSC-klagomål.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 52664-2023 FSC-klagomål.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11672-2024 FSC-klagomål mail.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 52664-2023 FSC-klagomål mail.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11672-2024 tillsynsbegäran.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 52664-2023 tillsynsbegäran.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11672-2024 tillsynsbegäran mail.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 52664-2023 tillsynsbegäran mail.docx", "A 52664-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 52664-2023</t>
+          <t>A 11672-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45225</v>
+        <v>45373</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1571,31 +1571,31 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>6.4</v>
+        <v>13.9</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1607,46 +1607,46 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 52664-2023 artfynd.xlsx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11672-2024 artfynd.xlsx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 52664-2023 karta.png", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11672-2024 karta.png", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 52664-2023 georefererad karta.tif", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11672-2024 georefererad karta.tif", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 52664-2023 FSC-klagomål.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11672-2024 FSC-klagomål.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 52664-2023 FSC-klagomål mail.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11672-2024 FSC-klagomål mail.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 52664-2023 tillsynsbegäran.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11672-2024 tillsynsbegäran.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 52664-2023 tillsynsbegäran mail.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11672-2024 tillsynsbegäran mail.docx", "A 11672-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 54127-2025</t>
+          <t>A 1577-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1660,10 +1660,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45964</v>
+        <v>45306</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.3</v>
+        <v>21.2</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1685,7 +1685,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1700,7 +1700,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1712,50 +1712,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 54127-2025 artfynd.xlsx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 54127-2025 karta.png", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 54127-2025 georefererad karta.tif", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 54127-2025 FSC-klagomål.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 54127-2025 FSC-klagomål mail.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 54127-2025 tillsynsbegäran.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 54127-2025 tillsynsbegäran mail.docx", "A 54127-2025")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/fåglar/A 54127-2025 prioriterade fågelarter.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 11170-2023</t>
+          <t>A 54127-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1769,10 +1765,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44987</v>
+        <v>45964</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1785,22 +1781,22 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1812,7 +1808,7 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1825,35 +1821,39 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Korndådra</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11170-2023 artfynd.xlsx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 54127-2025 artfynd.xlsx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11170-2023 karta.png", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 54127-2025 karta.png", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11170-2023 georefererad karta.tif", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 54127-2025 georefererad karta.tif", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11170-2023 FSC-klagomål.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 54127-2025 FSC-klagomål.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11170-2023 FSC-klagomål mail.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 54127-2025 FSC-klagomål mail.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11170-2023 tillsynsbegäran.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 54127-2025 tillsynsbegäran.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11170-2023 tillsynsbegäran mail.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 54127-2025 tillsynsbegäran mail.docx", "A 54127-2025")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/fåglar/A 54127-2025 prioriterade fågelarter.docx", "A 54127-2025")</f>
         <v/>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
         <v>45351</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>45218</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>44763</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44598</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44483</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44847</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44501</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>44831</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>44854</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 13245-2024</t>
+          <t>A 49032-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2595,10 +2595,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45386</v>
+        <v>44860</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>13</v>
+        <v>3.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 21774-2024</t>
+          <t>A 35911-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45442</v>
+        <v>45148</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 35587-2024</t>
+          <t>A 9716-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45531</v>
+        <v>44617</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2800,7 +2800,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 22794-2024</t>
+          <t>A 11101-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2814,10 +2814,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45448</v>
+        <v>44986</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 16667-2023</t>
+          <t>A 11177-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45030</v>
+        <v>44987</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 6365-2026</t>
+          <t>A 1592-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46051</v>
+        <v>45306</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3019,7 +3019,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 8332-2025</t>
+          <t>A 10209-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45708</v>
+        <v>44986</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3092,7 +3092,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 14543-2024</t>
+          <t>A 6335-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3106,10 +3106,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45394</v>
+        <v>44600</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3165,7 +3165,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 22063-2025</t>
+          <t>A 22262-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45785</v>
+        <v>45070</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3238,7 +3238,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 20170-2024</t>
+          <t>A 16667-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45434</v>
+        <v>45030</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3311,7 +3311,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 17980-2025</t>
+          <t>A 1920-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45761</v>
+        <v>45671</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3384,7 +3384,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 19282-2025</t>
+          <t>A 8332-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3394,14 +3394,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45769</v>
+        <v>45708</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 14533-2026</t>
+          <t>A 44112-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46100</v>
+        <v>45188</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 62403-2022</t>
+          <t>A 11491-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44923</v>
+        <v>44991</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3603,7 +3603,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 15747-2026</t>
+          <t>A 11922-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46107</v>
+        <v>44993</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3676,7 +3676,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 3430-2026</t>
+          <t>A 34810-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46042</v>
+        <v>45141</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 15157-2023</t>
+          <t>A 62201-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45016</v>
+        <v>46006</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>22.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 11491-2023</t>
+          <t>A 35587-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44991</v>
+        <v>45531</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3895,7 +3895,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 37907-2025</t>
+          <t>A 42706-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45880</v>
+        <v>45908</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3924,13 +3924,8 @@
           <t>SVALÖV</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>5.7</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3973,7 +3968,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 40470-2025</t>
+          <t>A 43425-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3983,14 +3978,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45895</v>
+        <v>45911</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4003,7 +3998,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.1</v>
+        <v>2.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4046,7 +4041,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 18926-2026</t>
+          <t>A 8924-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4060,10 +4055,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46127</v>
+        <v>44974</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4076,7 +4071,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.2</v>
+        <v>6.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4119,7 +4114,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 10209-2023</t>
+          <t>A 1901-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4133,10 +4128,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44986</v>
+        <v>45671</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4149,7 +4144,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.2</v>
+        <v>4.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4192,7 +4187,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 42706-2025</t>
+          <t>A 47139-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4206,10 +4201,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45908</v>
+        <v>45929</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4222,7 +4217,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4265,7 +4260,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 43425-2025</t>
+          <t>A 22794-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4279,10 +4274,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45911</v>
+        <v>45448</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4295,7 +4290,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4338,7 +4333,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 34810-2023</t>
+          <t>A 32620-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4352,10 +4347,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45141</v>
+        <v>45111</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4368,7 +4363,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>7</v>
+        <v>1.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4411,7 +4406,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 44107-2023</t>
+          <t>A 44196-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4425,10 +4420,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45188</v>
+        <v>45573</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4441,7 +4436,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4484,7 +4479,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 62201-2025</t>
+          <t>A 17731-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4494,14 +4489,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46006</v>
+        <v>45758</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4514,7 +4509,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>22.1</v>
+        <v>0.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4557,7 +4552,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 22262-2023</t>
+          <t>A 14543-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4571,10 +4566,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45070</v>
+        <v>45394</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4587,7 +4582,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4630,7 +4625,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 49032-2022</t>
+          <t>A 13273-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4644,10 +4639,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44860</v>
+        <v>45386</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4660,7 +4655,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.7</v>
+        <v>12.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4703,7 +4698,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 47139-2025</t>
+          <t>A 43294-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4717,10 +4712,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45929</v>
+        <v>45910</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4733,7 +4728,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4776,7 +4771,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 18121-2025</t>
+          <t>A 22792-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4790,10 +4785,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45761</v>
+        <v>45448</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4806,7 +4801,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4849,7 +4844,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 18438-2026</t>
+          <t>A 14546-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4863,10 +4858,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46127</v>
+        <v>45394</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4879,7 +4874,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4922,7 +4917,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 24286-2026</t>
+          <t>A 18121-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4936,10 +4931,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46169</v>
+        <v>45761</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4952,7 +4947,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4995,7 +4990,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 58970-2025</t>
+          <t>A 16215-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5009,10 +5004,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45987</v>
+        <v>44670</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5025,7 +5020,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5068,7 +5063,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 6335-2022</t>
+          <t>A 43466-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5082,10 +5077,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44600</v>
+        <v>45911</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5098,7 +5093,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5141,7 +5136,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 25522-2026</t>
+          <t>A 43004-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5155,10 +5150,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46177</v>
+        <v>45909</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5171,7 +5166,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>8.5</v>
+        <v>1.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5214,7 +5209,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 10196-2025</t>
+          <t>A 15487-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5228,10 +5223,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45719</v>
+        <v>45747</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5244,7 +5239,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5287,7 +5282,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 44112-2023</t>
+          <t>A 4964-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5301,10 +5296,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45188</v>
+        <v>44593</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5317,7 +5312,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5360,7 +5355,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 35911-2023</t>
+          <t>A 37354-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5374,10 +5369,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45148</v>
+        <v>44806</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5390,7 +5385,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5433,7 +5428,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 43294-2025</t>
+          <t>A 18438-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5447,10 +5442,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45910</v>
+        <v>46127</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5463,7 +5458,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5506,7 +5501,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 42588-2023</t>
+          <t>A 24286-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5520,10 +5515,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45176</v>
+        <v>46169</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5536,7 +5531,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5579,7 +5574,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 1901-2025</t>
+          <t>A 11633-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5593,10 +5588,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45671</v>
+        <v>45373</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5609,7 +5604,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5652,7 +5647,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 1920-2025</t>
+          <t>A 58970-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5666,10 +5661,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45671</v>
+        <v>45987</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5682,7 +5677,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5725,7 +5720,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 25832-2026</t>
+          <t>A 5068-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5739,10 +5734,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46178</v>
+        <v>46049</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5755,7 +5750,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>7.8</v>
+        <v>3.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5798,7 +5793,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 43736-2023</t>
+          <t>A 59266-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5812,10 +5807,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45182</v>
+        <v>45988</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5828,7 +5823,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5871,7 +5866,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 9716-2022</t>
+          <t>A 25522-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5885,10 +5880,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44617</v>
+        <v>46177</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5901,7 +5896,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.7</v>
+        <v>8.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5944,7 +5939,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 29337-2026</t>
+          <t>A 6365-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5958,10 +5953,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46202</v>
+        <v>46051</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5974,7 +5969,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6017,7 +6012,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 30535-2026</t>
+          <t>A 20170-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6031,10 +6026,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46210</v>
+        <v>45434</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6047,7 +6042,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6090,7 +6085,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 30202-2026</t>
+          <t>A 14533-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6104,10 +6099,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46206</v>
+        <v>46100</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6120,7 +6115,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6163,7 +6158,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 43466-2025</t>
+          <t>A 15747-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6177,10 +6172,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45911</v>
+        <v>46107</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6193,7 +6188,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6236,7 +6231,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 37354-2022</t>
+          <t>A 3430-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6250,10 +6245,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44806</v>
+        <v>46042</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6266,7 +6261,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.4</v>
+        <v>5.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6309,7 +6304,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 5190-2024</t>
+          <t>A 61620-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6323,10 +6318,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45330</v>
+        <v>44910</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6339,7 +6334,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6382,7 +6377,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 17731-2025</t>
+          <t>A 5190-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6392,14 +6387,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45758</v>
+        <v>45330</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6412,7 +6407,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6455,7 +6450,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 43004-2025</t>
+          <t>A 29337-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6469,10 +6464,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45909</v>
+        <v>46202</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6485,7 +6480,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6528,7 +6523,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 22792-2024</t>
+          <t>A 25832-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6542,10 +6537,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45448</v>
+        <v>46178</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6558,7 +6553,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>7.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6601,7 +6596,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 4964-2022</t>
+          <t>A 18926-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6615,10 +6610,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44593</v>
+        <v>46127</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6631,7 +6626,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6674,7 +6669,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 13791-2026</t>
+          <t>A 21774-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6688,10 +6683,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46097</v>
+        <v>45442</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6704,7 +6699,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6747,7 +6742,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 11177-2023</t>
+          <t>A 62403-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6761,10 +6756,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44987</v>
+        <v>44923</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6777,7 +6772,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6820,7 +6815,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 13787-2026</t>
+          <t>A 43736-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6834,10 +6829,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46097</v>
+        <v>45182</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6850,7 +6845,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6893,7 +6888,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 16215-2022</t>
+          <t>A 42588-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6907,10 +6902,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44670</v>
+        <v>45176</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6923,7 +6918,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6966,7 +6961,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 61620-2022</t>
+          <t>A 15157-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6980,10 +6975,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44910</v>
+        <v>45016</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6996,7 +6991,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7039,7 +7034,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 27380-2026</t>
+          <t>A 30202-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7053,10 +7048,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46189</v>
+        <v>46206</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7069,7 +7064,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7112,7 +7107,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 8924-2023</t>
+          <t>A 30535-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7126,10 +7121,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44974</v>
+        <v>46210</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7142,7 +7137,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>6.8</v>
+        <v>0.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7185,7 +7180,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 5068-2026</t>
+          <t>A 497-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7199,10 +7194,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46049</v>
+        <v>44930</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7215,7 +7210,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.5</v>
+        <v>0.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7258,7 +7253,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 497-2023</t>
+          <t>A 5184-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7272,10 +7267,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44930</v>
+        <v>45330</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7288,7 +7283,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7331,7 +7326,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 59266-2025</t>
+          <t>A 44107-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7345,10 +7340,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45988</v>
+        <v>45188</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7361,7 +7356,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7404,7 +7399,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 11633-2024</t>
+          <t>A 10196-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7418,10 +7413,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45373</v>
+        <v>45719</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7434,7 +7429,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.9</v>
+        <v>0.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7477,7 +7472,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 11922-2023</t>
+          <t>A 4149-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7487,14 +7482,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44993</v>
+        <v>44588</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7507,7 +7502,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7550,7 +7545,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 14546-2024</t>
+          <t>A 13245-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7564,10 +7559,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45394</v>
+        <v>45386</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7580,7 +7575,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7623,7 +7618,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 32620-2023</t>
+          <t>A 21814-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7637,10 +7632,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45111</v>
+        <v>45783</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7653,7 +7648,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7696,7 +7691,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 1592-2024</t>
+          <t>A 21541-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7710,10 +7705,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45306</v>
+        <v>45782</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7726,7 +7721,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7769,7 +7764,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 4149-2022</t>
+          <t>A 21556-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7779,14 +7774,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44588</v>
+        <v>45782</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7799,7 +7794,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7842,7 +7837,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 15487-2025</t>
+          <t>A 13791-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7856,10 +7851,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45747</v>
+        <v>46097</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7872,7 +7867,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7915,7 +7910,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 11101-2023</t>
+          <t>A 20047-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7929,10 +7924,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44986</v>
+        <v>45434</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7945,7 +7940,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7988,7 +7983,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 5184-2024</t>
+          <t>A 13787-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8002,10 +7997,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45330</v>
+        <v>46097</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8018,7 +8013,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8061,7 +8056,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 13273-2024</t>
+          <t>A 34808-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8075,10 +8070,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45386</v>
+        <v>45526</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8091,7 +8086,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>12.4</v>
+        <v>3.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8134,7 +8129,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 44196-2024</t>
+          <t>A 5167-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8148,10 +8143,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45573</v>
+        <v>45330</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8164,7 +8159,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.8</v>
+        <v>6.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8207,7 +8202,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 21556-2025</t>
+          <t>A 23747-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8221,10 +8216,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45782</v>
+        <v>45793</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8237,7 +8232,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8280,7 +8275,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 21541-2025</t>
+          <t>A 24513-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8294,10 +8289,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45782</v>
+        <v>45798</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8310,7 +8305,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.1</v>
+        <v>0.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8353,7 +8348,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 21814-2025</t>
+          <t>A 27310-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8367,10 +8362,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45783</v>
+        <v>45096</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8383,7 +8378,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8426,7 +8421,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 20047-2024</t>
+          <t>A 27380-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8440,10 +8435,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45434</v>
+        <v>46189</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8456,7 +8451,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8499,7 +8494,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 34808-2024</t>
+          <t>A 22063-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8513,10 +8508,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45526</v>
+        <v>45785</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8529,7 +8524,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8572,7 +8567,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 5167-2024</t>
+          <t>A 17980-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8586,10 +8581,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45330</v>
+        <v>45761</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8602,7 +8597,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>6.5</v>
+        <v>3.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8645,7 +8640,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 23747-2025</t>
+          <t>A 19282-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8655,14 +8650,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45793</v>
+        <v>45769</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8675,7 +8670,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8718,7 +8713,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 24513-2025</t>
+          <t>A 37907-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8732,10 +8727,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45798</v>
+        <v>45880</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8747,8 +8742,13 @@
           <t>SVALÖV</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>0.4</v>
+        <v>5.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8791,7 +8791,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 27310-2023</t>
+          <t>A 40470-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8801,14 +8801,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45096</v>
+        <v>45895</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.5</v>
+        <v>0.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8881,7 +8881,7 @@
         <v>45854</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>

--- a/Översikt SVALÖV.xlsx
+++ b/Översikt SVALÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45910</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>45884</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45401</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45645</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>44987</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>45401</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>45434</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>45225</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>45373</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>45306</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>45964</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>45351</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>45218</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>44763</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44598</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44483</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44847</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44501</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>44831</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>44854</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>44860</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>45148</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>44617</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>44986</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>44987</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>45306</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>44986</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>44600</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45070</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>45030</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>45671</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>45708</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>45188</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>44991</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>44993</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>45141</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>46006</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>45531</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>45908</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>45911</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44974</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>45671</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>45929</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>45448</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>45111</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>45573</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>45758</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>45394</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>45386</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>45910</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>45448</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>45394</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>45761</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>44670</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>45911</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>45909</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>45747</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         <v>44593</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         <v>44806</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>46127</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>46169</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>45373</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>45987</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>46049</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         <v>45988</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>46177</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>46051</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>45434</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>46100</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>46107</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>46042</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>44910</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>45330</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>46202</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>46178</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>46127</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v>45442</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         <v>44923</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6832,7 +6832,7 @@
         <v>45182</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>45176</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>45016</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>46206</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>46210</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
         <v>44930</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>45330</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>45188</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7416,7 +7416,7 @@
         <v>45719</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7489,7 +7489,7 @@
         <v>44588</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>45386</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>45783</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>45782</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
         <v>45782</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>46097</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>45434</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>46097</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>45526</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         <v>45330</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>45793</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         <v>45798</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         <v>45096</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>46189</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>45785</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         <v>45761</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>45769</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>45880</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>45895</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>45854</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>

--- a/Översikt SVALÖV.xlsx
+++ b/Översikt SVALÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45910</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>45884</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45401</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45645</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>44987</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>45401</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>45434</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 52664-2023</t>
+          <t>A 54127-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45225</v>
+        <v>45964</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1466,17 +1466,17 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>6.4</v>
+        <v>1.3</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
@@ -1490,7 +1490,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1502,46 +1502,50 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 52664-2023 artfynd.xlsx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 54127-2025 artfynd.xlsx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 52664-2023 karta.png", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 54127-2025 karta.png", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 52664-2023 georefererad karta.tif", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 54127-2025 georefererad karta.tif", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 52664-2023 FSC-klagomål.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 54127-2025 FSC-klagomål.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 52664-2023 FSC-klagomål mail.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 54127-2025 FSC-klagomål mail.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 52664-2023 tillsynsbegäran.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 54127-2025 tillsynsbegäran.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 52664-2023 tillsynsbegäran mail.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 54127-2025 tillsynsbegäran mail.docx", "A 54127-2025")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/fåglar/A 54127-2025 prioriterade fågelarter.docx", "A 54127-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 11672-2024</t>
+          <t>A 52664-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1555,10 +1559,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45373</v>
+        <v>45225</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1571,16 +1575,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>13.9</v>
+        <v>6.4</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1595,7 +1599,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1607,46 +1611,46 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11672-2024 artfynd.xlsx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 52664-2023 artfynd.xlsx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11672-2024 karta.png", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 52664-2023 karta.png", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11672-2024 georefererad karta.tif", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 52664-2023 georefererad karta.tif", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11672-2024 FSC-klagomål.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 52664-2023 FSC-klagomål.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11672-2024 FSC-klagomål mail.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 52664-2023 FSC-klagomål mail.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11672-2024 tillsynsbegäran.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 52664-2023 tillsynsbegäran.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11672-2024 tillsynsbegäran mail.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 52664-2023 tillsynsbegäran mail.docx", "A 52664-2023")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 1577-2024</t>
+          <t>A 11672-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1660,10 +1664,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45306</v>
+        <v>45373</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1676,17 +1680,17 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>21.2</v>
+        <v>13.9</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
@@ -1700,7 +1704,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1712,46 +1716,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11672-2024 artfynd.xlsx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11672-2024 karta.png", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11672-2024 georefererad karta.tif", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11672-2024 FSC-klagomål.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11672-2024 FSC-klagomål mail.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11672-2024 tillsynsbegäran.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11672-2024 tillsynsbegäran mail.docx", "A 11672-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 54127-2025</t>
+          <t>A 1577-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1765,10 +1769,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45964</v>
+        <v>45306</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1781,7 +1785,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>21.2</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1790,7 +1794,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1805,7 +1809,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1817,43 +1821,39 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 54127-2025 artfynd.xlsx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 54127-2025 karta.png", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 54127-2025 georefererad karta.tif", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 54127-2025 FSC-klagomål.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 54127-2025 FSC-klagomål mail.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 54127-2025 tillsynsbegäran.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 54127-2025 tillsynsbegäran mail.docx", "A 54127-2025")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/fåglar/A 54127-2025 prioriterade fågelarter.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
         <v>45351</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>45218</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>44763</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44598</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44483</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44847</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44501</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>44831</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>44854</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>44860</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>45148</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>44617</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>44986</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>44987</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>45306</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>44986</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 6335-2022</t>
+          <t>A 22262-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3106,10 +3106,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44600</v>
+        <v>45070</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3165,7 +3165,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 22262-2023</t>
+          <t>A 6335-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45070</v>
+        <v>44600</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3255,7 +3255,7 @@
         <v>45030</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>45671</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>45708</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>45188</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 11491-2023</t>
+          <t>A 11922-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44991</v>
+        <v>44993</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3603,7 +3603,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 11922-2023</t>
+          <t>A 11491-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44993</v>
+        <v>44991</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3676,7 +3676,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 34810-2023</t>
+          <t>A 37907-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45141</v>
+        <v>45880</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3705,8 +3705,13 @@
           <t>SVALÖV</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3749,7 +3754,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 62201-2025</t>
+          <t>A 40470-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3759,14 +3764,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46006</v>
+        <v>45895</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3779,7 +3784,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>22.1</v>
+        <v>0.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3822,7 +3827,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 35587-2024</t>
+          <t>A 34810-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3836,10 +3841,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45531</v>
+        <v>45141</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3852,7 +3857,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.6</v>
+        <v>7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3895,7 +3900,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 42706-2025</t>
+          <t>A 62201-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3909,10 +3914,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45908</v>
+        <v>46006</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3925,7 +3930,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>22.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3968,7 +3973,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 43425-2025</t>
+          <t>A 42706-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3982,10 +3987,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45911</v>
+        <v>45908</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3998,7 +4003,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4041,7 +4046,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 8924-2023</t>
+          <t>A 43425-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4055,10 +4060,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44974</v>
+        <v>45911</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4071,7 +4076,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>6.8</v>
+        <v>2.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4114,7 +4119,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 1901-2025</t>
+          <t>A 47139-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4128,10 +4133,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45671</v>
+        <v>45929</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4144,7 +4149,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4187,7 +4192,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 47139-2025</t>
+          <t>A 35587-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4201,10 +4206,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45929</v>
+        <v>45531</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4217,7 +4222,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4260,7 +4265,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 22794-2024</t>
+          <t>A 8924-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4274,10 +4279,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45448</v>
+        <v>44974</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4290,7 +4295,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.8</v>
+        <v>6.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4333,7 +4338,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 32620-2023</t>
+          <t>A 1901-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4347,10 +4352,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45111</v>
+        <v>45671</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4363,7 +4368,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4406,7 +4411,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 44196-2024</t>
+          <t>A 43294-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4420,10 +4425,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45573</v>
+        <v>45910</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4436,7 +4441,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4479,7 +4484,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 17731-2025</t>
+          <t>A 22794-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4489,14 +4494,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45758</v>
+        <v>45448</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4509,7 +4514,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4552,7 +4557,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 14543-2024</t>
+          <t>A 32620-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4566,10 +4571,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45394</v>
+        <v>45111</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4582,7 +4587,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4625,7 +4630,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 13273-2024</t>
+          <t>A 18438-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4639,10 +4644,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45386</v>
+        <v>46127</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4655,7 +4660,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>12.4</v>
+        <v>1.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4698,7 +4703,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 43294-2025</t>
+          <t>A 44196-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4712,10 +4717,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45910</v>
+        <v>45573</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4728,7 +4733,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4771,7 +4776,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 22792-2024</t>
+          <t>A 17731-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4781,14 +4786,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45448</v>
+        <v>45758</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4801,7 +4806,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4844,7 +4849,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 14546-2024</t>
+          <t>A 24286-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4858,10 +4863,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45394</v>
+        <v>46169</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4874,7 +4879,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4917,7 +4922,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 18121-2025</t>
+          <t>A 14543-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4931,10 +4936,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45761</v>
+        <v>45394</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4947,7 +4952,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4990,7 +4995,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 16215-2022</t>
+          <t>A 13273-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5004,10 +5009,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44670</v>
+        <v>45386</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5020,7 +5025,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.9</v>
+        <v>12.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5080,7 +5085,7 @@
         <v>45911</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5136,7 +5141,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 43004-2025</t>
+          <t>A 58970-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5150,10 +5155,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45909</v>
+        <v>45987</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5166,7 +5171,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5209,7 +5214,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 15487-2025</t>
+          <t>A 43004-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5223,10 +5228,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45747</v>
+        <v>45909</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5239,7 +5244,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5282,7 +5287,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 4964-2022</t>
+          <t>A 22792-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5296,10 +5301,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44593</v>
+        <v>45448</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5312,7 +5317,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5355,7 +5360,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 37354-2022</t>
+          <t>A 14546-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5369,10 +5374,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44806</v>
+        <v>45394</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5385,7 +5390,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5428,7 +5433,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 18438-2026</t>
+          <t>A 25522-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5442,10 +5447,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46127</v>
+        <v>46177</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5458,7 +5463,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.6</v>
+        <v>8.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5501,7 +5506,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 24286-2026</t>
+          <t>A 18121-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5515,10 +5520,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46169</v>
+        <v>45761</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5531,7 +5536,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5574,7 +5579,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 11633-2024</t>
+          <t>A 16215-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5588,10 +5593,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45373</v>
+        <v>44670</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5604,7 +5609,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.9</v>
+        <v>2.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5647,7 +5652,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 58970-2025</t>
+          <t>A 5068-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5661,10 +5666,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45987</v>
+        <v>46049</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5677,7 +5682,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5720,7 +5725,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 5068-2026</t>
+          <t>A 59266-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5734,10 +5739,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46049</v>
+        <v>45988</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5750,7 +5755,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5793,7 +5798,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 59266-2025</t>
+          <t>A 15487-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5807,10 +5812,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45988</v>
+        <v>45747</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5823,7 +5828,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5866,7 +5871,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 25522-2026</t>
+          <t>A 6365-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5880,10 +5885,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46177</v>
+        <v>46051</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5896,7 +5901,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>8.5</v>
+        <v>2.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5939,7 +5944,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 6365-2026</t>
+          <t>A 4964-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5953,10 +5958,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46051</v>
+        <v>44593</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5969,7 +5974,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6012,7 +6017,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 20170-2024</t>
+          <t>A 37354-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6026,10 +6031,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45434</v>
+        <v>44806</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6042,7 +6047,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6085,7 +6090,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 14533-2026</t>
+          <t>A 29337-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6099,10 +6104,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46100</v>
+        <v>46202</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6115,7 +6120,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6158,7 +6163,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 15747-2026</t>
+          <t>A 25832-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6172,10 +6177,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46107</v>
+        <v>46178</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6188,7 +6193,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.4</v>
+        <v>7.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6231,7 +6236,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 3430-2026</t>
+          <t>A 14533-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6245,10 +6250,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46042</v>
+        <v>46100</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6261,7 +6266,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>5.7</v>
+        <v>1.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6304,7 +6309,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 61620-2022</t>
+          <t>A 11633-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6318,10 +6323,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44910</v>
+        <v>45373</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6334,7 +6339,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.5</v>
+        <v>4.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6377,7 +6382,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 5190-2024</t>
+          <t>A 15747-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6391,10 +6396,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45330</v>
+        <v>46107</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6407,7 +6412,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6450,7 +6455,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 29337-2026</t>
+          <t>A 3430-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6464,10 +6469,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46202</v>
+        <v>46042</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6480,7 +6485,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2</v>
+        <v>5.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6523,7 +6528,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 25832-2026</t>
+          <t>A 18926-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6537,10 +6542,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46178</v>
+        <v>46127</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6553,7 +6558,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>7.8</v>
+        <v>1.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6596,7 +6601,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 18926-2026</t>
+          <t>A 20170-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6610,10 +6615,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46127</v>
+        <v>45434</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6626,7 +6631,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6669,7 +6674,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 21774-2024</t>
+          <t>A 30202-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6683,10 +6688,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45442</v>
+        <v>46206</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6699,7 +6704,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6742,7 +6747,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 62403-2022</t>
+          <t>A 30535-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6756,10 +6761,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44923</v>
+        <v>46210</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6772,7 +6777,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6815,7 +6820,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 43736-2023</t>
+          <t>A 61620-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6829,10 +6834,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45182</v>
+        <v>44910</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6845,7 +6850,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6888,7 +6893,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 42588-2023</t>
+          <t>A 5190-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6902,10 +6907,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45176</v>
+        <v>45330</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6918,7 +6923,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6961,7 +6966,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 15157-2023</t>
+          <t>A 21774-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6975,10 +6980,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45016</v>
+        <v>45442</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6991,7 +6996,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7034,7 +7039,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 30202-2026</t>
+          <t>A 62403-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7048,10 +7053,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46206</v>
+        <v>44923</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7064,7 +7069,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7107,7 +7112,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 30535-2026</t>
+          <t>A 43736-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7121,10 +7126,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46210</v>
+        <v>45182</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7137,7 +7142,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7180,7 +7185,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 497-2023</t>
+          <t>A 42588-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7194,10 +7199,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44930</v>
+        <v>45176</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7210,7 +7215,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7253,7 +7258,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 5184-2024</t>
+          <t>A 15157-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7267,10 +7272,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45330</v>
+        <v>45016</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7283,7 +7288,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7326,7 +7331,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 44107-2023</t>
+          <t>A 13791-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7340,10 +7345,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45188</v>
+        <v>46097</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7356,7 +7361,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7399,7 +7404,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 10196-2025</t>
+          <t>A 13787-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7413,10 +7418,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45719</v>
+        <v>46097</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7429,7 +7434,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7472,7 +7477,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 4149-2022</t>
+          <t>A 497-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7482,14 +7487,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44588</v>
+        <v>44930</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7502,7 +7507,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7545,7 +7550,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 13245-2024</t>
+          <t>A 5184-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7559,10 +7564,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45386</v>
+        <v>45330</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7575,7 +7580,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>13</v>
+        <v>2.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7618,7 +7623,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 21814-2025</t>
+          <t>A 44107-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7632,10 +7637,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45783</v>
+        <v>45188</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7648,7 +7653,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7691,7 +7696,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 21541-2025</t>
+          <t>A 27380-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7705,10 +7710,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45782</v>
+        <v>46189</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7721,7 +7726,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7764,7 +7769,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 21556-2025</t>
+          <t>A 10196-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7778,10 +7783,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45782</v>
+        <v>45719</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7794,7 +7799,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7837,7 +7842,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 13791-2026</t>
+          <t>A 4149-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7847,14 +7852,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46097</v>
+        <v>44588</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7867,7 +7872,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7910,7 +7915,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 20047-2024</t>
+          <t>A 13245-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7924,10 +7929,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45434</v>
+        <v>45386</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7940,7 +7945,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.3</v>
+        <v>13</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7983,7 +7988,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 13787-2026</t>
+          <t>A 21814-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7997,10 +8002,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46097</v>
+        <v>45783</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8013,7 +8018,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8056,7 +8061,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 34808-2024</t>
+          <t>A 21541-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8070,10 +8075,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45526</v>
+        <v>45782</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8086,7 +8091,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8129,7 +8134,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 5167-2024</t>
+          <t>A 21556-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8143,10 +8148,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45330</v>
+        <v>45782</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8159,7 +8164,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>6.5</v>
+        <v>1.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8202,7 +8207,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 23747-2025</t>
+          <t>A 20047-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8216,10 +8221,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45793</v>
+        <v>45434</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8232,7 +8237,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8275,7 +8280,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 24513-2025</t>
+          <t>A 34808-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8289,10 +8294,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45798</v>
+        <v>45526</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8305,7 +8310,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.4</v>
+        <v>3.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8348,7 +8353,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 27310-2023</t>
+          <t>A 5167-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8362,10 +8367,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45096</v>
+        <v>45330</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8378,7 +8383,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8421,7 +8426,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 27380-2026</t>
+          <t>A 23747-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8435,10 +8440,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46189</v>
+        <v>45793</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8451,7 +8456,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8494,7 +8499,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 22063-2025</t>
+          <t>A 24513-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8508,10 +8513,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45785</v>
+        <v>45798</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8524,7 +8529,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8567,7 +8572,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 17980-2025</t>
+          <t>A 27310-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8581,10 +8586,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45761</v>
+        <v>45096</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8597,7 +8602,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8640,7 +8645,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 19282-2025</t>
+          <t>A 22063-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8650,14 +8655,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45769</v>
+        <v>45785</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8670,7 +8675,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8713,7 +8718,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 37907-2025</t>
+          <t>A 17980-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8727,10 +8732,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45880</v>
+        <v>45761</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8742,13 +8747,8 @@
           <t>SVALÖV</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8791,7 +8791,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 40470-2025</t>
+          <t>A 19282-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45895</v>
+        <v>45769</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8881,7 +8881,7 @@
         <v>45854</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>

--- a/Översikt SVALÖV.xlsx
+++ b/Översikt SVALÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45910</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 38522-2025</t>
+          <t>A 15475-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45884</v>
+        <v>45401</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -833,14 +833,14 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
@@ -848,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -857,10 +857,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -869,146 +869,146 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15475-2024 artfynd.xlsx", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15475-2024 karta.png", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15475-2024 georefererad karta.tif", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15475-2024 FSC-klagomål.docx", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15475-2024 FSC-klagomål mail.docx", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15475-2024 tillsynsbegäran.docx", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15475-2024 tillsynsbegäran mail.docx", "A 15475-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 38522-2025</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SVALÖV</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Skogsknipprot
 Stor häxört</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 38522-2025 artfynd.xlsx", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 38522-2025 karta.png", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 38522-2025 georefererad karta.tif", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 38522-2025 FSC-klagomål.docx", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 38522-2025 FSC-klagomål mail.docx", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 38522-2025 tillsynsbegäran.docx", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 38522-2025 tillsynsbegäran mail.docx", "A 38522-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 15475-2024</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45401</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SVALÖV</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15475-2024 artfynd.xlsx", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15475-2024 karta.png", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15475-2024 georefererad karta.tif", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15475-2024 FSC-klagomål.docx", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15475-2024 FSC-klagomål mail.docx", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15475-2024 tillsynsbegäran.docx", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15475-2024 tillsynsbegäran mail.docx", "A 15475-2024")</f>
         <v/>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
         <v>45645</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 11170-2023</t>
+          <t>A 15456-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44987</v>
+        <v>45401</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1187,46 +1187,46 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Korndådra</t>
+          <t>Lundticka</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11170-2023 artfynd.xlsx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15456-2024 artfynd.xlsx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11170-2023 karta.png", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15456-2024 karta.png", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11170-2023 georefererad karta.tif", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15456-2024 georefererad karta.tif", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11170-2023 FSC-klagomål.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15456-2024 FSC-klagomål.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11170-2023 FSC-klagomål mail.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15456-2024 FSC-klagomål mail.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11170-2023 tillsynsbegäran.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15456-2024 tillsynsbegäran.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11170-2023 tillsynsbegäran mail.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15456-2024 tillsynsbegäran mail.docx", "A 15456-2024")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 15456-2024</t>
+          <t>A 8169-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45401</v>
+        <v>45351</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1265,10 +1265,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1283,7 +1283,7 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1296,42 +1296,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Lundticka</t>
+          <t>Mjukdån</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15456-2024 artfynd.xlsx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 8169-2024 artfynd.xlsx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15456-2024 karta.png", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 8169-2024 karta.png", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15456-2024 georefererad karta.tif", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 8169-2024 georefererad karta.tif", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15456-2024 FSC-klagomål.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 8169-2024 FSC-klagomål.docx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15456-2024 FSC-klagomål mail.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 8169-2024 FSC-klagomål mail.docx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15456-2024 tillsynsbegäran.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 8169-2024 tillsynsbegäran.docx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15456-2024 tillsynsbegäran mail.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 8169-2024 tillsynsbegäran mail.docx", "A 8169-2024")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 20125-2024</t>
+          <t>A 1577-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45434</v>
+        <v>45306</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.7</v>
+        <v>21.2</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1401,42 +1401,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 20125-2024 artfynd.xlsx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 20125-2024 karta.png", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 20125-2024 georefererad karta.tif", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 20125-2024 FSC-klagomål.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 20125-2024 FSC-klagomål mail.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 20125-2024 tillsynsbegäran.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 20125-2024 tillsynsbegäran mail.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 54127-2025</t>
+          <t>A 20125-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45964</v>
+        <v>45434</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1466,16 +1466,16 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.3</v>
+        <v>5.7</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1490,7 +1490,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1502,50 +1502,46 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 54127-2025 artfynd.xlsx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 20125-2024 artfynd.xlsx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 54127-2025 karta.png", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 20125-2024 karta.png", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 54127-2025 georefererad karta.tif", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 20125-2024 georefererad karta.tif", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 54127-2025 FSC-klagomål.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 20125-2024 FSC-klagomål.docx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 54127-2025 FSC-klagomål mail.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 20125-2024 FSC-klagomål mail.docx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 54127-2025 tillsynsbegäran.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 20125-2024 tillsynsbegäran.docx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 54127-2025 tillsynsbegäran mail.docx", "A 54127-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/fåglar/A 54127-2025 prioriterade fågelarter.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 20125-2024 tillsynsbegäran mail.docx", "A 20125-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 52664-2023</t>
+          <t>A 11672-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1559,10 +1555,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45225</v>
+        <v>45373</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1575,31 +1571,31 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>6.4</v>
+        <v>13.9</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1611,46 +1607,46 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 52664-2023 artfynd.xlsx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11672-2024 artfynd.xlsx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 52664-2023 karta.png", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11672-2024 karta.png", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 52664-2023 georefererad karta.tif", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11672-2024 georefererad karta.tif", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 52664-2023 FSC-klagomål.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11672-2024 FSC-klagomål.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 52664-2023 FSC-klagomål mail.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11672-2024 FSC-klagomål mail.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 52664-2023 tillsynsbegäran.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11672-2024 tillsynsbegäran.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 52664-2023 tillsynsbegäran mail.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11672-2024 tillsynsbegäran mail.docx", "A 11672-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 11672-2024</t>
+          <t>A 52664-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1664,10 +1660,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45373</v>
+        <v>45225</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1680,16 +1676,16 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>13.9</v>
+        <v>6.4</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1704,7 +1700,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1716,46 +1712,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11672-2024 artfynd.xlsx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 52664-2023 artfynd.xlsx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11672-2024 karta.png", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 52664-2023 karta.png", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11672-2024 georefererad karta.tif", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 52664-2023 georefererad karta.tif", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11672-2024 FSC-klagomål.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 52664-2023 FSC-klagomål.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11672-2024 FSC-klagomål mail.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 52664-2023 FSC-klagomål mail.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11672-2024 tillsynsbegäran.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 52664-2023 tillsynsbegäran.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11672-2024 tillsynsbegäran mail.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 52664-2023 tillsynsbegäran mail.docx", "A 52664-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 1577-2024</t>
+          <t>A 11170-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1769,10 +1765,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45306</v>
+        <v>44987</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1785,23 +1781,23 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>21.2</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
@@ -1809,10 +1805,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1821,46 +1817,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Korndådra</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11170-2023 artfynd.xlsx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11170-2023 karta.png", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11170-2023 georefererad karta.tif", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11170-2023 FSC-klagomål.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11170-2023 FSC-klagomål mail.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11170-2023 tillsynsbegäran.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11170-2023 tillsynsbegäran mail.docx", "A 11170-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 8169-2024</t>
+          <t>A 54127-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1874,10 +1870,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45351</v>
+        <v>45964</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1890,10 +1886,10 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1926,39 +1922,43 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Mjukdån</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 8169-2024 artfynd.xlsx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 54127-2025 artfynd.xlsx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 8169-2024 karta.png", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 54127-2025 karta.png", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 8169-2024 georefererad karta.tif", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 54127-2025 georefererad karta.tif", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 8169-2024 FSC-klagomål.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 54127-2025 FSC-klagomål.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 8169-2024 FSC-klagomål mail.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 54127-2025 FSC-klagomål mail.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 8169-2024 tillsynsbegäran.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 54127-2025 tillsynsbegäran.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 8169-2024 tillsynsbegäran mail.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 54127-2025 tillsynsbegäran mail.docx", "A 54127-2025")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/fåglar/A 54127-2025 prioriterade fågelarter.docx", "A 54127-2025")</f>
         <v/>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         <v>45218</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>44763</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44598</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44483</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44847</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44501</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>44831</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>44854</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 49032-2022</t>
+          <t>A 10209-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2595,10 +2595,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44860</v>
+        <v>44986</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 35911-2023</t>
+          <t>A 20047-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45148</v>
+        <v>45434</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 9716-2022</t>
+          <t>A 34808-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44617</v>
+        <v>45526</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2800,7 +2800,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 11101-2023</t>
+          <t>A 44107-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2814,10 +2814,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44986</v>
+        <v>45188</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 11177-2023</t>
+          <t>A 5167-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44987</v>
+        <v>45330</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.2</v>
+        <v>6.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 1592-2024</t>
+          <t>A 13245-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45306</v>
+        <v>45386</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.2</v>
+        <v>13</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3019,7 +3019,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 10209-2023</t>
+          <t>A 22262-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44986</v>
+        <v>45070</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3092,7 +3092,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 22262-2023</t>
+          <t>A 49032-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3106,10 +3106,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45070</v>
+        <v>44860</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3165,7 +3165,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 6335-2022</t>
+          <t>A 23747-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44600</v>
+        <v>45793</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3238,7 +3238,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 16667-2023</t>
+          <t>A 21774-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45030</v>
+        <v>45442</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3311,7 +3311,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 1920-2025</t>
+          <t>A 18121-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45671</v>
+        <v>45761</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3384,7 +3384,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 8332-2025</t>
+          <t>A 24513-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45708</v>
+        <v>45798</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 44112-2023</t>
+          <t>A 22794-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45188</v>
+        <v>45448</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 11922-2023</t>
+          <t>A 42706-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44993</v>
+        <v>45908</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3603,7 +3603,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 11491-2023</t>
+          <t>A 27310-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44991</v>
+        <v>45096</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3676,7 +3676,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 37907-2025</t>
+          <t>A 43425-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45880</v>
+        <v>45911</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3705,13 +3705,8 @@
           <t>SVALÖV</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>5.7</v>
+        <v>2.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3754,7 +3749,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 40470-2025</t>
+          <t>A 35587-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3764,14 +3759,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45895</v>
+        <v>45531</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3784,7 +3779,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.1</v>
+        <v>1.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3827,7 +3822,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 34810-2023</t>
+          <t>A 6335-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3841,10 +3836,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45141</v>
+        <v>44600</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3857,7 +3852,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3900,7 +3895,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 62201-2025</t>
+          <t>A 47139-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3914,10 +3909,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46006</v>
+        <v>45929</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3930,7 +3925,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>22.1</v>
+        <v>1.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3973,7 +3968,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 42706-2025</t>
+          <t>A 16667-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3987,10 +3982,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45908</v>
+        <v>45030</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4003,7 +3998,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4046,7 +4041,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 43425-2025</t>
+          <t>A 10196-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4060,10 +4055,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45911</v>
+        <v>45719</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4076,7 +4071,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4119,7 +4114,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 47139-2025</t>
+          <t>A 44112-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4133,10 +4128,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45929</v>
+        <v>45188</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4149,7 +4144,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4192,7 +4187,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 35587-2024</t>
+          <t>A 35911-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4206,10 +4201,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45531</v>
+        <v>45148</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4222,7 +4217,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4265,7 +4260,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 8924-2023</t>
+          <t>A 8332-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4279,10 +4274,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44974</v>
+        <v>45708</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4295,7 +4290,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>6.8</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4338,7 +4333,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 1901-2025</t>
+          <t>A 14543-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4352,10 +4347,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45671</v>
+        <v>45394</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4368,7 +4363,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.2</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4411,7 +4406,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 43294-2025</t>
+          <t>A 42588-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4425,10 +4420,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45910</v>
+        <v>45176</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4441,7 +4436,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4484,7 +4479,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 22794-2024</t>
+          <t>A 1901-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4498,10 +4493,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45448</v>
+        <v>45671</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4514,7 +4509,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4557,7 +4552,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 32620-2023</t>
+          <t>A 1920-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4571,10 +4566,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45111</v>
+        <v>45671</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4587,7 +4582,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4630,7 +4625,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 18438-2026</t>
+          <t>A 43736-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4644,10 +4639,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46127</v>
+        <v>45182</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4660,7 +4655,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4703,7 +4698,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 44196-2024</t>
+          <t>A 43294-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4717,10 +4712,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45573</v>
+        <v>45910</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4733,7 +4728,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4776,7 +4771,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 17731-2025</t>
+          <t>A 20170-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4786,14 +4781,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45758</v>
+        <v>45434</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4806,7 +4801,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4849,7 +4844,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 24286-2026</t>
+          <t>A 9716-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4863,10 +4858,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46169</v>
+        <v>44617</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4879,7 +4874,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4922,7 +4917,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 14543-2024</t>
+          <t>A 62403-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4936,10 +4931,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45394</v>
+        <v>44923</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4952,7 +4947,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4995,7 +4990,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 13273-2024</t>
+          <t>A 15157-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5009,10 +5004,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45386</v>
+        <v>45016</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5025,7 +5020,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>12.4</v>
+        <v>2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5068,7 +5063,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 43466-2025</t>
+          <t>A 11491-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5082,10 +5077,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45911</v>
+        <v>44991</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5098,7 +5093,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5141,7 +5136,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 58970-2025</t>
+          <t>A 43466-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5155,10 +5150,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45987</v>
+        <v>45911</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5171,7 +5166,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5231,7 +5226,7 @@
         <v>45909</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5287,7 +5282,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 22792-2024</t>
+          <t>A 37354-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5301,10 +5296,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45448</v>
+        <v>44806</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5317,7 +5312,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5360,7 +5355,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 14546-2024</t>
+          <t>A 22063-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5374,10 +5369,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45394</v>
+        <v>45785</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5390,7 +5385,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5433,7 +5428,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 25522-2026</t>
+          <t>A 5190-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5447,10 +5442,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46177</v>
+        <v>45330</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5463,7 +5458,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>8.5</v>
+        <v>2.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5506,7 +5501,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 18121-2025</t>
+          <t>A 17731-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5516,14 +5511,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45761</v>
+        <v>45758</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5536,7 +5531,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5579,7 +5574,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 16215-2022</t>
+          <t>A 5068-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5593,10 +5588,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44670</v>
+        <v>46049</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5609,7 +5604,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5652,7 +5647,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 5068-2026</t>
+          <t>A 59266-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5666,10 +5661,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46049</v>
+        <v>45988</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5682,7 +5677,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5725,7 +5720,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 59266-2025</t>
+          <t>A 22792-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5739,10 +5734,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45988</v>
+        <v>45448</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5755,7 +5750,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5798,7 +5793,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 15487-2025</t>
+          <t>A 6365-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5812,10 +5807,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45747</v>
+        <v>46051</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5828,7 +5823,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5871,7 +5866,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 6365-2026</t>
+          <t>A 4964-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5885,10 +5880,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46051</v>
+        <v>44593</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5901,7 +5896,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5944,7 +5939,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 4964-2022</t>
+          <t>A 11177-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5958,10 +5953,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44593</v>
+        <v>44987</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5974,7 +5969,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6017,7 +6012,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 37354-2022</t>
+          <t>A 16215-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6031,10 +6026,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44806</v>
+        <v>44670</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6047,7 +6042,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6090,7 +6085,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 29337-2026</t>
+          <t>A 17980-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6104,10 +6099,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46202</v>
+        <v>45761</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6120,7 +6115,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6163,7 +6158,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 25832-2026</t>
+          <t>A 61620-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6177,10 +6172,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46178</v>
+        <v>44910</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6193,7 +6188,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>7.8</v>
+        <v>1.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6236,7 +6231,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 14533-2026</t>
+          <t>A 19282-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6246,14 +6241,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46100</v>
+        <v>45769</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6266,7 +6261,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6309,7 +6304,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 11633-2024</t>
+          <t>A 14533-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6323,10 +6318,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45373</v>
+        <v>46100</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6339,7 +6334,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.9</v>
+        <v>1.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6399,7 +6394,7 @@
         <v>46107</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6455,7 +6450,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 3430-2026</t>
+          <t>A 8924-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6469,10 +6464,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46042</v>
+        <v>44974</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6485,7 +6480,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6528,7 +6523,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 18926-2026</t>
+          <t>A 3430-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6542,10 +6537,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46127</v>
+        <v>46042</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6558,7 +6553,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.2</v>
+        <v>5.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6601,7 +6596,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 20170-2024</t>
+          <t>A 497-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6615,10 +6610,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45434</v>
+        <v>44930</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6631,7 +6626,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6674,7 +6669,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 30202-2026</t>
+          <t>A 11633-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6688,10 +6683,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46206</v>
+        <v>45373</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6704,7 +6699,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6747,7 +6742,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 30535-2026</t>
+          <t>A 18926-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6761,10 +6756,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46210</v>
+        <v>46127</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6777,7 +6772,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6820,7 +6815,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 61620-2022</t>
+          <t>A 11922-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6834,10 +6829,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44910</v>
+        <v>44993</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6850,7 +6845,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6893,7 +6888,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 5190-2024</t>
+          <t>A 14546-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6907,10 +6902,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45330</v>
+        <v>45394</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6923,7 +6918,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6966,7 +6961,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 21774-2024</t>
+          <t>A 32620-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6980,10 +6975,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45442</v>
+        <v>45111</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6996,7 +6991,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7039,7 +7034,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 62403-2022</t>
+          <t>A 37907-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7053,10 +7048,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44923</v>
+        <v>45880</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7068,8 +7063,13 @@
           <t>SVALÖV</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>2.2</v>
+        <v>5.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7112,7 +7112,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 43736-2023</t>
+          <t>A 34810-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45182</v>
+        <v>45141</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.2</v>
+        <v>7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7185,7 +7185,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 42588-2023</t>
+          <t>A 40470-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7195,14 +7195,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45176</v>
+        <v>45895</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7258,7 +7258,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 15157-2023</t>
+          <t>A 1592-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45016</v>
+        <v>45306</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7331,7 +7331,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 13791-2026</t>
+          <t>A 4149-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7341,14 +7341,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46097</v>
+        <v>44588</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7404,7 +7404,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 13787-2026</t>
+          <t>A 15487-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7418,10 +7418,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46097</v>
+        <v>45747</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7477,7 +7477,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 497-2023</t>
+          <t>A 62201-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7491,10 +7491,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44930</v>
+        <v>46006</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.8</v>
+        <v>22.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7550,7 +7550,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 5184-2024</t>
+          <t>A 11101-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7564,10 +7564,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45330</v>
+        <v>44986</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7623,7 +7623,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 44107-2023</t>
+          <t>A 5184-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7637,10 +7637,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45188</v>
+        <v>45330</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7696,7 +7696,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 27380-2026</t>
+          <t>A 13273-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46189</v>
+        <v>45386</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.7</v>
+        <v>12.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7769,7 +7769,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 10196-2025</t>
+          <t>A 44196-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45719</v>
+        <v>45573</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7842,7 +7842,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 4149-2022</t>
+          <t>A 21556-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7852,14 +7852,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44588</v>
+        <v>45782</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7915,7 +7915,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 13245-2024</t>
+          <t>A 21541-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7929,10 +7929,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45386</v>
+        <v>45782</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>13</v>
+        <v>3.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8005,7 +8005,7 @@
         <v>45783</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 21541-2025</t>
+          <t>A 18438-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8075,10 +8075,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45782</v>
+        <v>46127</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8134,7 +8134,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 21556-2025</t>
+          <t>A 24286-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45782</v>
+        <v>46169</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8207,7 +8207,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 20047-2024</t>
+          <t>A 58970-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8221,10 +8221,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45434</v>
+        <v>45987</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8280,7 +8280,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 34808-2024</t>
+          <t>A 25522-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8294,10 +8294,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45526</v>
+        <v>46177</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.6</v>
+        <v>8.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8353,7 +8353,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 5167-2024</t>
+          <t>A 25832-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8367,10 +8367,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45330</v>
+        <v>46178</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>6.5</v>
+        <v>7.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 23747-2025</t>
+          <t>A 29337-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45793</v>
+        <v>46202</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8499,7 +8499,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 24513-2025</t>
+          <t>A 30535-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45798</v>
+        <v>46210</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8572,7 +8572,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 27310-2023</t>
+          <t>A 30202-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45096</v>
+        <v>46206</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8645,7 +8645,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 22063-2025</t>
+          <t>A 13791-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8659,10 +8659,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45785</v>
+        <v>46097</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8718,7 +8718,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 17980-2025</t>
+          <t>A 13787-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8732,10 +8732,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45761</v>
+        <v>46097</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8791,7 +8791,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 19282-2025</t>
+          <t>A 27380-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8801,14 +8801,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45769</v>
+        <v>46189</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8881,7 +8881,7 @@
         <v>45854</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>

--- a/Översikt SVALÖV.xlsx
+++ b/Översikt SVALÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45910</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 15475-2024</t>
+          <t>A 38522-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45401</v>
+        <v>45884</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.7</v>
+        <v>2.6</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -848,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -857,10 +857,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -869,146 +869,146 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Skogsknipprot
+Stor häxört</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 38522-2025 artfynd.xlsx", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 38522-2025 karta.png", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 38522-2025 georefererad karta.tif", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 38522-2025 FSC-klagomål.docx", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 38522-2025 FSC-klagomål mail.docx", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 38522-2025 tillsynsbegäran.docx", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 38522-2025 tillsynsbegäran mail.docx", "A 38522-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 15475-2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45401</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SVALÖV</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>1</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Ask
 Strutbräken</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15475-2024 artfynd.xlsx", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15475-2024 karta.png", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15475-2024 georefererad karta.tif", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15475-2024 FSC-klagomål.docx", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15475-2024 FSC-klagomål mail.docx", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15475-2024 tillsynsbegäran.docx", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15475-2024 tillsynsbegäran mail.docx", "A 15475-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 38522-2025</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45884</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SVALÖV</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Skogsknipprot
-Stor häxört</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 38522-2025 artfynd.xlsx", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 38522-2025 karta.png", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 38522-2025 georefererad karta.tif", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 38522-2025 FSC-klagomål.docx", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 38522-2025 FSC-klagomål mail.docx", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 38522-2025 tillsynsbegäran.docx", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 38522-2025 tillsynsbegäran mail.docx", "A 38522-2025")</f>
         <v/>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
         <v>45645</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 15456-2024</t>
+          <t>A 11170-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45401</v>
+        <v>44987</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1187,46 +1187,46 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Lundticka</t>
+          <t>Korndådra</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15456-2024 artfynd.xlsx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11170-2023 artfynd.xlsx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15456-2024 karta.png", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11170-2023 karta.png", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15456-2024 georefererad karta.tif", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11170-2023 georefererad karta.tif", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15456-2024 FSC-klagomål.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11170-2023 FSC-klagomål.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15456-2024 FSC-klagomål mail.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11170-2023 FSC-klagomål mail.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15456-2024 tillsynsbegäran.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11170-2023 tillsynsbegäran.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15456-2024 tillsynsbegäran mail.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11170-2023 tillsynsbegäran mail.docx", "A 11170-2023")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 8169-2024</t>
+          <t>A 15456-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45351</v>
+        <v>45401</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1265,10 +1265,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1283,7 +1283,7 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1296,42 +1296,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Mjukdån</t>
+          <t>Lundticka</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 8169-2024 artfynd.xlsx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15456-2024 artfynd.xlsx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 8169-2024 karta.png", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15456-2024 karta.png", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 8169-2024 georefererad karta.tif", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15456-2024 georefererad karta.tif", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 8169-2024 FSC-klagomål.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15456-2024 FSC-klagomål.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 8169-2024 FSC-klagomål mail.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15456-2024 FSC-klagomål mail.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 8169-2024 tillsynsbegäran.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15456-2024 tillsynsbegäran.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 8169-2024 tillsynsbegäran mail.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15456-2024 tillsynsbegäran mail.docx", "A 15456-2024")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 1577-2024</t>
+          <t>A 20125-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45306</v>
+        <v>45434</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>21.2</v>
+        <v>5.7</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1401,42 +1401,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 20125-2024 artfynd.xlsx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 20125-2024 karta.png", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 20125-2024 georefererad karta.tif", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 20125-2024 FSC-klagomål.docx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 20125-2024 FSC-klagomål mail.docx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 20125-2024 tillsynsbegäran.docx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 20125-2024 tillsynsbegäran mail.docx", "A 20125-2024")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 20125-2024</t>
+          <t>A 52664-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45434</v>
+        <v>45225</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
@@ -1506,35 +1506,35 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 20125-2024 artfynd.xlsx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 52664-2023 artfynd.xlsx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 20125-2024 karta.png", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 52664-2023 karta.png", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 20125-2024 georefererad karta.tif", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 52664-2023 georefererad karta.tif", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 20125-2024 FSC-klagomål.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 52664-2023 FSC-klagomål.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 20125-2024 FSC-klagomål mail.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 52664-2023 FSC-klagomål mail.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 20125-2024 tillsynsbegäran.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 52664-2023 tillsynsbegäran.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 20125-2024 tillsynsbegäran mail.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 52664-2023 tillsynsbegäran mail.docx", "A 52664-2023")</f>
         <v/>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
         <v>45373</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 52664-2023</t>
+          <t>A 54127-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1660,10 +1660,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45225</v>
+        <v>45964</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1676,17 +1676,17 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>6.4</v>
+        <v>1.3</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
       </c>
       <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
@@ -1700,7 +1700,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1712,46 +1712,50 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 52664-2023 artfynd.xlsx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 54127-2025 artfynd.xlsx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 52664-2023 karta.png", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 54127-2025 karta.png", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 52664-2023 georefererad karta.tif", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 54127-2025 georefererad karta.tif", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 52664-2023 FSC-klagomål.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 54127-2025 FSC-klagomål.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 52664-2023 FSC-klagomål mail.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 54127-2025 FSC-klagomål mail.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 52664-2023 tillsynsbegäran.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 54127-2025 tillsynsbegäran.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 52664-2023 tillsynsbegäran mail.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 54127-2025 tillsynsbegäran mail.docx", "A 54127-2025")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/fåglar/A 54127-2025 prioriterade fågelarter.docx", "A 54127-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 11170-2023</t>
+          <t>A 1577-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1765,10 +1769,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44987</v>
+        <v>45306</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1781,10 +1785,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>21.2</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1796,7 +1800,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1805,10 +1809,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1817,46 +1821,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Korndådra</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11170-2023 artfynd.xlsx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11170-2023 karta.png", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11170-2023 georefererad karta.tif", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11170-2023 FSC-klagomål.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11170-2023 FSC-klagomål mail.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11170-2023 tillsynsbegäran.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11170-2023 tillsynsbegäran mail.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 54127-2025</t>
+          <t>A 8169-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1870,10 +1874,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45964</v>
+        <v>45351</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1886,10 +1890,10 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1922,43 +1926,39 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Mjukdån</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 54127-2025 artfynd.xlsx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 8169-2024 artfynd.xlsx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 54127-2025 karta.png", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 8169-2024 karta.png", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 54127-2025 georefererad karta.tif", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 8169-2024 georefererad karta.tif", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 54127-2025 FSC-klagomål.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 8169-2024 FSC-klagomål.docx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 54127-2025 FSC-klagomål mail.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 8169-2024 FSC-klagomål mail.docx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 54127-2025 tillsynsbegäran.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 8169-2024 tillsynsbegäran.docx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 54127-2025 tillsynsbegäran mail.docx", "A 54127-2025")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/fåglar/A 54127-2025 prioriterade fågelarter.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 8169-2024 tillsynsbegäran mail.docx", "A 8169-2024")</f>
         <v/>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         <v>45218</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>44763</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44598</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44483</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44847</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44501</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>44831</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>44854</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 10209-2023</t>
+          <t>A 49032-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2595,10 +2595,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44986</v>
+        <v>44860</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 20047-2024</t>
+          <t>A 35911-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45434</v>
+        <v>45148</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 34808-2024</t>
+          <t>A 9716-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45526</v>
+        <v>44617</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2800,7 +2800,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 44107-2023</t>
+          <t>A 11101-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2814,10 +2814,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45188</v>
+        <v>44986</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 5167-2024</t>
+          <t>A 11177-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45330</v>
+        <v>44987</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>6.5</v>
+        <v>1.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 13245-2024</t>
+          <t>A 10209-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45386</v>
+        <v>44986</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>13</v>
+        <v>1.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3019,7 +3019,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 22262-2023</t>
+          <t>A 1592-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45070</v>
+        <v>45306</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3092,7 +3092,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 49032-2022</t>
+          <t>A 6335-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3106,10 +3106,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44860</v>
+        <v>44600</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3165,7 +3165,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 23747-2025</t>
+          <t>A 22262-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45793</v>
+        <v>45070</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3238,7 +3238,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 21774-2024</t>
+          <t>A 16667-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45442</v>
+        <v>45030</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3311,7 +3311,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 18121-2025</t>
+          <t>A 8332-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45761</v>
+        <v>45708</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3384,7 +3384,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 24513-2025</t>
+          <t>A 44112-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45798</v>
+        <v>45188</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 22794-2024</t>
+          <t>A 11491-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45448</v>
+        <v>44991</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 42706-2025</t>
+          <t>A 1920-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45908</v>
+        <v>45671</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3603,7 +3603,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 27310-2023</t>
+          <t>A 11922-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45096</v>
+        <v>44993</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3676,7 +3676,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 43425-2025</t>
+          <t>A 37907-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45911</v>
+        <v>45880</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3705,8 +3705,13 @@
           <t>SVALÖV</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>2.1</v>
+        <v>5.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3749,7 +3754,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 35587-2024</t>
+          <t>A 40470-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3759,14 +3764,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45531</v>
+        <v>45895</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3779,7 +3784,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3822,7 +3827,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 6335-2022</t>
+          <t>A 34810-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3836,10 +3841,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44600</v>
+        <v>45141</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3852,7 +3857,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3895,7 +3900,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 47139-2025</t>
+          <t>A 42706-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3909,10 +3914,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45929</v>
+        <v>45908</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3925,7 +3930,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3968,7 +3973,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 16667-2023</t>
+          <t>A 43425-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3982,10 +3987,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45030</v>
+        <v>45911</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3998,7 +4003,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4041,7 +4046,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 10196-2025</t>
+          <t>A 62201-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4055,10 +4060,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45719</v>
+        <v>46006</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4071,7 +4076,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>22.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4114,7 +4119,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 44112-2023</t>
+          <t>A 47139-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4128,10 +4133,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45188</v>
+        <v>45929</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4144,7 +4149,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4187,7 +4192,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 35911-2023</t>
+          <t>A 35587-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4201,10 +4206,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45148</v>
+        <v>45531</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4217,7 +4222,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4260,7 +4265,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 8332-2025</t>
+          <t>A 8924-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4274,10 +4279,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45708</v>
+        <v>44974</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4290,7 +4295,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>6.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4333,7 +4338,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 14543-2024</t>
+          <t>A 1901-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4347,10 +4352,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45394</v>
+        <v>45671</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4363,7 +4368,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4406,7 +4411,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 42588-2023</t>
+          <t>A 22794-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4420,10 +4425,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45176</v>
+        <v>45448</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4436,7 +4441,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4479,7 +4484,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 1901-2025</t>
+          <t>A 32620-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4493,10 +4498,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45671</v>
+        <v>45111</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4509,7 +4514,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4552,7 +4557,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 1920-2025</t>
+          <t>A 43294-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4566,10 +4571,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45671</v>
+        <v>45910</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4582,7 +4587,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4625,7 +4630,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 43736-2023</t>
+          <t>A 44196-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4639,10 +4644,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45182</v>
+        <v>45573</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4655,7 +4660,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4698,7 +4703,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 43294-2025</t>
+          <t>A 17731-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4708,14 +4713,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45910</v>
+        <v>45758</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4728,7 +4733,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4771,7 +4776,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 20170-2024</t>
+          <t>A 14543-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4785,10 +4790,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45434</v>
+        <v>45394</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4801,7 +4806,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4844,7 +4849,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 9716-2022</t>
+          <t>A 13273-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4858,10 +4863,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44617</v>
+        <v>45386</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4874,7 +4879,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>12.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4917,7 +4922,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 62403-2022</t>
+          <t>A 43466-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4931,10 +4936,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44923</v>
+        <v>45911</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4947,7 +4952,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4990,7 +4995,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 15157-2023</t>
+          <t>A 43004-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5004,10 +5009,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45016</v>
+        <v>45909</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5020,7 +5025,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5063,7 +5068,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 11491-2023</t>
+          <t>A 22792-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5077,10 +5082,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44991</v>
+        <v>45448</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5093,7 +5098,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5136,7 +5141,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 43466-2025</t>
+          <t>A 14546-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5150,10 +5155,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45911</v>
+        <v>45394</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5166,7 +5171,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5209,7 +5214,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 43004-2025</t>
+          <t>A 18121-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5223,10 +5228,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45909</v>
+        <v>45761</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5239,7 +5244,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5282,7 +5287,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 37354-2022</t>
+          <t>A 16215-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5296,10 +5301,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44806</v>
+        <v>44670</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5312,7 +5317,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5355,7 +5360,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 22063-2025</t>
+          <t>A 15487-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5369,10 +5374,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45785</v>
+        <v>45747</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5385,7 +5390,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5428,7 +5433,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 5190-2024</t>
+          <t>A 5068-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5442,10 +5447,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45330</v>
+        <v>46049</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5458,7 +5463,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5501,7 +5506,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 17731-2025</t>
+          <t>A 18438-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5511,14 +5516,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45758</v>
+        <v>46127</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5531,7 +5536,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5574,7 +5579,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 5068-2026</t>
+          <t>A 59266-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5588,10 +5593,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46049</v>
+        <v>45988</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5604,7 +5609,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5647,7 +5652,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 59266-2025</t>
+          <t>A 4964-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5661,10 +5666,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45988</v>
+        <v>44593</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5677,7 +5682,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5720,7 +5725,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 22792-2024</t>
+          <t>A 37354-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5734,10 +5739,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45448</v>
+        <v>44806</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5750,7 +5755,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5793,7 +5798,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 6365-2026</t>
+          <t>A 24286-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5807,10 +5812,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46051</v>
+        <v>46169</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5823,7 +5828,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5866,7 +5871,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 4964-2022</t>
+          <t>A 6365-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5880,10 +5885,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44593</v>
+        <v>46051</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5896,7 +5901,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5939,7 +5944,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 11177-2023</t>
+          <t>A 58970-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5953,10 +5958,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44987</v>
+        <v>45987</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5969,7 +5974,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6012,7 +6017,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 16215-2022</t>
+          <t>A 11633-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6026,10 +6031,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44670</v>
+        <v>45373</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6042,7 +6047,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.9</v>
+        <v>4.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6085,7 +6090,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 17980-2025</t>
+          <t>A 25522-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6099,10 +6104,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45761</v>
+        <v>46177</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6115,7 +6120,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.4</v>
+        <v>8.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6158,7 +6163,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 61620-2022</t>
+          <t>A 14533-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6172,10 +6177,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44910</v>
+        <v>46100</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6188,7 +6193,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6231,7 +6236,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 19282-2025</t>
+          <t>A 15747-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6241,14 +6246,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45769</v>
+        <v>46107</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6261,7 +6266,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6304,7 +6309,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 14533-2026</t>
+          <t>A 3430-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6318,10 +6323,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46100</v>
+        <v>46042</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6334,7 +6339,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.2</v>
+        <v>5.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6377,7 +6382,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 15747-2026</t>
+          <t>A 20170-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6391,10 +6396,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46107</v>
+        <v>45434</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6407,7 +6412,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6450,7 +6455,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 8924-2023</t>
+          <t>A 18926-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6464,10 +6469,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44974</v>
+        <v>46127</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6480,7 +6485,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>6.8</v>
+        <v>1.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6523,7 +6528,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 3430-2026</t>
+          <t>A 29337-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6537,10 +6542,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46042</v>
+        <v>46202</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6553,7 +6558,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>5.7</v>
+        <v>2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6596,7 +6601,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 497-2023</t>
+          <t>A 25832-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6610,10 +6615,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44930</v>
+        <v>46178</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6626,7 +6631,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.8</v>
+        <v>7.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6669,7 +6674,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 11633-2024</t>
+          <t>A 30202-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6683,10 +6688,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45373</v>
+        <v>46206</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6699,7 +6704,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6742,7 +6747,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 18926-2026</t>
+          <t>A 30535-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6756,10 +6761,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46127</v>
+        <v>46210</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6772,7 +6777,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6815,7 +6820,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 11922-2023</t>
+          <t>A 61620-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6829,10 +6834,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44993</v>
+        <v>44910</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6845,7 +6850,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6888,7 +6893,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 14546-2024</t>
+          <t>A 5190-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6902,10 +6907,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45394</v>
+        <v>45330</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6918,7 +6923,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6961,7 +6966,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 32620-2023</t>
+          <t>A 21774-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6975,10 +6980,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45111</v>
+        <v>45442</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6991,7 +6996,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7034,7 +7039,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 37907-2025</t>
+          <t>A 62403-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7048,10 +7053,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45880</v>
+        <v>44923</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7063,13 +7068,8 @@
           <t>SVALÖV</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>5.7</v>
+        <v>2.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7112,7 +7112,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 34810-2023</t>
+          <t>A 43736-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45141</v>
+        <v>45182</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>7</v>
+        <v>1.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7185,7 +7185,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 40470-2025</t>
+          <t>A 42588-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7195,14 +7195,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45895</v>
+        <v>45176</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7258,7 +7258,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 1592-2024</t>
+          <t>A 15157-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45306</v>
+        <v>45016</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7331,7 +7331,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 4149-2022</t>
+          <t>A 497-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7341,14 +7341,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44588</v>
+        <v>44930</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7404,7 +7404,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 15487-2025</t>
+          <t>A 5184-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7418,10 +7418,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45747</v>
+        <v>45330</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7477,7 +7477,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 62201-2025</t>
+          <t>A 44107-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7491,10 +7491,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46006</v>
+        <v>45188</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>22.1</v>
+        <v>2.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7550,7 +7550,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 11101-2023</t>
+          <t>A 10196-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7564,10 +7564,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44986</v>
+        <v>45719</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7623,7 +7623,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 5184-2024</t>
+          <t>A 4149-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7633,14 +7633,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45330</v>
+        <v>44588</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7696,7 +7696,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 13273-2024</t>
+          <t>A 13791-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45386</v>
+        <v>46097</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>12.4</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7769,7 +7769,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 44196-2024</t>
+          <t>A 13787-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45573</v>
+        <v>46097</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7842,7 +7842,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 21556-2025</t>
+          <t>A 13245-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7856,10 +7856,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45782</v>
+        <v>45386</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.3</v>
+        <v>13</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7915,7 +7915,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 21541-2025</t>
+          <t>A 27380-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7929,10 +7929,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45782</v>
+        <v>46189</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8005,7 +8005,7 @@
         <v>45783</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 18438-2026</t>
+          <t>A 21541-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8075,10 +8075,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46127</v>
+        <v>45782</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8134,7 +8134,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 24286-2026</t>
+          <t>A 21556-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46169</v>
+        <v>45782</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8207,7 +8207,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 58970-2025</t>
+          <t>A 20047-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8221,10 +8221,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45987</v>
+        <v>45434</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8280,7 +8280,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 25522-2026</t>
+          <t>A 34808-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8294,10 +8294,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46177</v>
+        <v>45526</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>8.5</v>
+        <v>3.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8353,7 +8353,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 25832-2026</t>
+          <t>A 5167-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8367,10 +8367,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46178</v>
+        <v>45330</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>7.8</v>
+        <v>6.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 29337-2026</t>
+          <t>A 23747-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46202</v>
+        <v>45793</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8499,7 +8499,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 30535-2026</t>
+          <t>A 24513-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46210</v>
+        <v>45798</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8572,7 +8572,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 30202-2026</t>
+          <t>A 27310-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46206</v>
+        <v>45096</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8645,7 +8645,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 13791-2026</t>
+          <t>A 22063-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8659,10 +8659,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46097</v>
+        <v>45785</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8718,7 +8718,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 13787-2026</t>
+          <t>A 17980-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8732,10 +8732,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46097</v>
+        <v>45761</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8791,7 +8791,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 27380-2026</t>
+          <t>A 19282-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8801,14 +8801,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46189</v>
+        <v>45769</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8881,7 +8881,7 @@
         <v>45854</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>

--- a/Översikt SVALÖV.xlsx
+++ b/Översikt SVALÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45910</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 38522-2025</t>
+          <t>A 15475-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45884</v>
+        <v>45401</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -833,14 +833,14 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
@@ -848,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -857,10 +857,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -869,259 +869,259 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15475-2024 artfynd.xlsx", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15475-2024 karta.png", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15475-2024 georefererad karta.tif", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15475-2024 FSC-klagomål.docx", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15475-2024 FSC-klagomål mail.docx", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15475-2024 tillsynsbegäran.docx", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15475-2024 tillsynsbegäran mail.docx", "A 15475-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 61064-2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45645</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SVALÖV</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 61064-2024 artfynd.xlsx", "A 61064-2024")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 61064-2024 karta.png", "A 61064-2024")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 61064-2024 georefererad karta.tif", "A 61064-2024")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 61064-2024 FSC-klagomål.docx", "A 61064-2024")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 61064-2024 FSC-klagomål mail.docx", "A 61064-2024")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 61064-2024 tillsynsbegäran.docx", "A 61064-2024")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 61064-2024 tillsynsbegäran mail.docx", "A 61064-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 38522-2025</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>SVALÖV</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Skogsknipprot
 Stor häxört</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 38522-2025 artfynd.xlsx", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 38522-2025 karta.png", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 38522-2025 georefererad karta.tif", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 38522-2025 FSC-klagomål.docx", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 38522-2025 FSC-klagomål mail.docx", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 38522-2025 tillsynsbegäran.docx", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 38522-2025 tillsynsbegäran mail.docx", "A 38522-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 15475-2024</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45401</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SVALÖV</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15475-2024 artfynd.xlsx", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15475-2024 karta.png", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15475-2024 georefererad karta.tif", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15475-2024 FSC-klagomål.docx", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15475-2024 FSC-klagomål mail.docx", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15475-2024 tillsynsbegäran.docx", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15475-2024 tillsynsbegäran mail.docx", "A 15475-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 61064-2024</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45645</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>SVALÖV</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 61064-2024 artfynd.xlsx", "A 61064-2024")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 61064-2024 karta.png", "A 61064-2024")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 61064-2024 georefererad karta.tif", "A 61064-2024")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 61064-2024 FSC-klagomål.docx", "A 61064-2024")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 61064-2024 FSC-klagomål mail.docx", "A 61064-2024")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 61064-2024 tillsynsbegäran.docx", "A 61064-2024")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 61064-2024 tillsynsbegäran mail.docx", "A 61064-2024")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 11170-2023</t>
+          <t>A 15456-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44987</v>
+        <v>45401</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1187,46 +1187,46 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Korndådra</t>
+          <t>Lundticka</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11170-2023 artfynd.xlsx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15456-2024 artfynd.xlsx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11170-2023 karta.png", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15456-2024 karta.png", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11170-2023 georefererad karta.tif", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15456-2024 georefererad karta.tif", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11170-2023 FSC-klagomål.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15456-2024 FSC-klagomål.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11170-2023 FSC-klagomål mail.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15456-2024 FSC-klagomål mail.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11170-2023 tillsynsbegäran.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15456-2024 tillsynsbegäran.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11170-2023 tillsynsbegäran mail.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15456-2024 tillsynsbegäran mail.docx", "A 15456-2024")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 15456-2024</t>
+          <t>A 1577-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45401</v>
+        <v>45306</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.5</v>
+        <v>21.2</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1268,7 +1268,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1280,10 +1280,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1296,35 +1296,35 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Lundticka</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15456-2024 artfynd.xlsx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15456-2024 karta.png", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15456-2024 georefererad karta.tif", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15456-2024 FSC-klagomål.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15456-2024 FSC-klagomål mail.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15456-2024 tillsynsbegäran.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15456-2024 tillsynsbegäran mail.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
         <v>45434</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 52664-2023</t>
+          <t>A 11672-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45225</v>
+        <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1466,31 +1466,31 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>6.4</v>
+        <v>13.9</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1502,46 +1502,46 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 52664-2023 artfynd.xlsx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11672-2024 artfynd.xlsx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 52664-2023 karta.png", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11672-2024 karta.png", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 52664-2023 georefererad karta.tif", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11672-2024 georefererad karta.tif", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 52664-2023 FSC-klagomål.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11672-2024 FSC-klagomål.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 52664-2023 FSC-klagomål mail.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11672-2024 FSC-klagomål mail.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 52664-2023 tillsynsbegäran.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11672-2024 tillsynsbegäran.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 52664-2023 tillsynsbegäran mail.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11672-2024 tillsynsbegäran mail.docx", "A 11672-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 11672-2024</t>
+          <t>A 52664-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45373</v>
+        <v>45225</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1571,16 +1571,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>13.9</v>
+        <v>6.4</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1595,7 +1595,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1607,39 +1607,39 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11672-2024 artfynd.xlsx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 52664-2023 artfynd.xlsx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11672-2024 karta.png", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 52664-2023 karta.png", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11672-2024 georefererad karta.tif", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 52664-2023 georefererad karta.tif", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11672-2024 FSC-klagomål.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 52664-2023 FSC-klagomål.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11672-2024 FSC-klagomål mail.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 52664-2023 FSC-klagomål mail.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11672-2024 tillsynsbegäran.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 52664-2023 tillsynsbegäran.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11672-2024 tillsynsbegäran mail.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 52664-2023 tillsynsbegäran mail.docx", "A 52664-2023")</f>
         <v/>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
         <v>45964</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 1577-2024</t>
+          <t>A 11170-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45306</v>
+        <v>44987</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1785,23 +1785,23 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>21.2</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
@@ -1809,10 +1809,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1821,39 +1821,39 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Korndådra</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11170-2023 artfynd.xlsx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11170-2023 karta.png", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11170-2023 georefererad karta.tif", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11170-2023 FSC-klagomål.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11170-2023 FSC-klagomål mail.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11170-2023 tillsynsbegäran.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11170-2023 tillsynsbegäran mail.docx", "A 11170-2023")</f>
         <v/>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
         <v>45351</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>45218</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>44763</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44598</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44483</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44847</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44501</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>44831</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>44854</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 49032-2022</t>
+          <t>A 13245-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2595,10 +2595,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44860</v>
+        <v>45386</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.7</v>
+        <v>13</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 35911-2023</t>
+          <t>A 21774-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45148</v>
+        <v>45442</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 9716-2022</t>
+          <t>A 23747-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44617</v>
+        <v>45793</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2800,7 +2800,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 11101-2023</t>
+          <t>A 22794-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2814,10 +2814,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44986</v>
+        <v>45448</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 11177-2023</t>
+          <t>A 24513-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44987</v>
+        <v>45798</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 10209-2023</t>
+          <t>A 35587-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44986</v>
+        <v>45531</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3019,7 +3019,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 1592-2024</t>
+          <t>A 27310-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45306</v>
+        <v>45096</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3092,7 +3092,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 6335-2022</t>
+          <t>A 5068-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3106,10 +3106,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44600</v>
+        <v>46049</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3165,7 +3165,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 22262-2023</t>
+          <t>A 42706-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45070</v>
+        <v>45908</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3238,7 +3238,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 16667-2023</t>
+          <t>A 59266-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45030</v>
+        <v>45988</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3311,7 +3311,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 8332-2025</t>
+          <t>A 43425-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45708</v>
+        <v>45911</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3384,7 +3384,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 44112-2023</t>
+          <t>A 16667-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45188</v>
+        <v>45030</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 11491-2023</t>
+          <t>A 6365-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44991</v>
+        <v>46051</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 1920-2025</t>
+          <t>A 47139-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45671</v>
+        <v>45929</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3603,7 +3603,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 11922-2023</t>
+          <t>A 8332-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44993</v>
+        <v>45708</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3676,7 +3676,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 37907-2025</t>
+          <t>A 14543-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45880</v>
+        <v>45394</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3705,13 +3705,8 @@
           <t>SVALÖV</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>5.7</v>
+        <v>0.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3754,7 +3749,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 40470-2025</t>
+          <t>A 14533-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3764,14 +3759,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45895</v>
+        <v>46100</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3784,7 +3779,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3827,7 +3822,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 34810-2023</t>
+          <t>A 20170-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3841,10 +3836,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45141</v>
+        <v>45434</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3857,7 +3852,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>7</v>
+        <v>0.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3900,7 +3895,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 42706-2025</t>
+          <t>A 15747-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3914,10 +3909,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45908</v>
+        <v>46107</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3930,7 +3925,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3973,7 +3968,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 43425-2025</t>
+          <t>A 3430-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3987,10 +3982,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45911</v>
+        <v>46042</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4003,7 +3998,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.1</v>
+        <v>5.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4046,7 +4041,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 62201-2025</t>
+          <t>A 62403-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4060,10 +4055,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46006</v>
+        <v>44923</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4076,7 +4071,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>22.1</v>
+        <v>2.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4119,7 +4114,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 47139-2025</t>
+          <t>A 43294-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4133,10 +4128,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45929</v>
+        <v>45910</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4149,7 +4144,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4192,7 +4187,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 35587-2024</t>
+          <t>A 18926-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4206,10 +4201,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45531</v>
+        <v>46127</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4222,7 +4217,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4265,7 +4260,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 8924-2023</t>
+          <t>A 15157-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4279,10 +4274,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44974</v>
+        <v>45016</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4295,7 +4290,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>6.8</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4338,7 +4333,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 1901-2025</t>
+          <t>A 11491-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4352,10 +4347,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45671</v>
+        <v>44991</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4368,7 +4363,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4411,7 +4406,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 22794-2024</t>
+          <t>A 34810-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4425,10 +4420,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45448</v>
+        <v>45141</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4441,7 +4436,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.8</v>
+        <v>7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4484,7 +4479,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 32620-2023</t>
+          <t>A 43466-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4498,10 +4493,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45111</v>
+        <v>45911</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4514,7 +4509,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>4.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4557,7 +4552,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 43294-2025</t>
+          <t>A 10209-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4571,10 +4566,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45910</v>
+        <v>44986</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4587,7 +4582,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4630,7 +4625,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 44196-2024</t>
+          <t>A 43004-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4644,10 +4639,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45573</v>
+        <v>45909</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4660,7 +4655,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4703,7 +4698,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 17731-2025</t>
+          <t>A 44107-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4713,14 +4708,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45758</v>
+        <v>45188</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4733,7 +4728,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4776,7 +4771,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 14543-2024</t>
+          <t>A 62201-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4790,10 +4785,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45394</v>
+        <v>46006</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4806,7 +4801,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>22.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4849,7 +4844,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 13273-2024</t>
+          <t>A 22262-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4863,10 +4858,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45386</v>
+        <v>45070</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4879,7 +4874,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>12.4</v>
+        <v>1.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4922,7 +4917,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 43466-2025</t>
+          <t>A 49032-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4936,10 +4931,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45911</v>
+        <v>44860</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4952,7 +4947,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4995,7 +4990,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 43004-2025</t>
+          <t>A 22063-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5009,10 +5004,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45909</v>
+        <v>45785</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5025,7 +5020,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5068,7 +5063,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 22792-2024</t>
+          <t>A 18121-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5082,10 +5077,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45448</v>
+        <v>45761</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5098,7 +5093,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5141,7 +5136,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 14546-2024</t>
+          <t>A 17980-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5155,10 +5150,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45394</v>
+        <v>45761</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5171,7 +5166,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5214,7 +5209,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 18121-2025</t>
+          <t>A 19282-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5224,14 +5219,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45761</v>
+        <v>45769</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5244,7 +5239,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5287,7 +5282,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 16215-2022</t>
+          <t>A 18438-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5301,10 +5296,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44670</v>
+        <v>46127</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5317,7 +5312,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5360,7 +5355,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 15487-2025</t>
+          <t>A 24286-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5374,10 +5369,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45747</v>
+        <v>46169</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5433,7 +5428,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 5068-2026</t>
+          <t>A 58970-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5447,10 +5442,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46049</v>
+        <v>45987</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5463,7 +5458,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5506,7 +5501,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 18438-2026</t>
+          <t>A 25522-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5520,10 +5515,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46127</v>
+        <v>46177</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5536,7 +5531,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.6</v>
+        <v>8.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5579,7 +5574,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 59266-2025</t>
+          <t>A 6335-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5593,10 +5588,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45988</v>
+        <v>44600</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5609,7 +5604,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5652,7 +5647,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 4964-2022</t>
+          <t>A 10196-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5666,10 +5661,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44593</v>
+        <v>45719</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5682,7 +5677,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5725,7 +5720,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 37354-2022</t>
+          <t>A 37907-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5739,10 +5734,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44806</v>
+        <v>45880</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5754,8 +5749,13 @@
           <t>SVALÖV</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>1.4</v>
+        <v>5.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5798,7 +5798,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 24286-2026</t>
+          <t>A 44112-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46169</v>
+        <v>45188</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5871,7 +5871,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 6365-2026</t>
+          <t>A 25832-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46051</v>
+        <v>46178</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.9</v>
+        <v>7.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5944,7 +5944,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 58970-2025</t>
+          <t>A 35911-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5958,10 +5958,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45987</v>
+        <v>45148</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6017,7 +6017,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 11633-2024</t>
+          <t>A 40470-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6027,14 +6027,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45373</v>
+        <v>45895</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.9</v>
+        <v>0.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6090,7 +6090,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 25522-2026</t>
+          <t>A 29337-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6104,10 +6104,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46177</v>
+        <v>46202</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6163,7 +6163,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 14533-2026</t>
+          <t>A 42588-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46100</v>
+        <v>45176</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 15747-2026</t>
+          <t>A 1901-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6250,10 +6250,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46107</v>
+        <v>45671</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 3430-2026</t>
+          <t>A 1920-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6323,10 +6323,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46042</v>
+        <v>45671</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>5.7</v>
+        <v>2.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6382,7 +6382,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 20170-2024</t>
+          <t>A 30535-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6396,10 +6396,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45434</v>
+        <v>46210</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6455,7 +6455,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 18926-2026</t>
+          <t>A 30202-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6469,10 +6469,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46127</v>
+        <v>46206</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6528,7 +6528,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 29337-2026</t>
+          <t>A 43736-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46202</v>
+        <v>45182</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6601,7 +6601,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 25832-2026</t>
+          <t>A 9716-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46178</v>
+        <v>44617</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>7.8</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6674,7 +6674,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 30202-2026</t>
+          <t>A 37354-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6688,10 +6688,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46206</v>
+        <v>44806</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5</v>
+        <v>1.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6747,7 +6747,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 30535-2026</t>
+          <t>A 5190-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6761,10 +6761,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46210</v>
+        <v>45330</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6820,7 +6820,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 61620-2022</t>
+          <t>A 17731-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6830,14 +6830,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44910</v>
+        <v>45758</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6893,7 +6893,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 5190-2024</t>
+          <t>A 13791-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45330</v>
+        <v>46097</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6966,7 +6966,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 21774-2024</t>
+          <t>A 13787-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6980,10 +6980,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45442</v>
+        <v>46097</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 62403-2022</t>
+          <t>A 27380-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44923</v>
+        <v>46189</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7112,7 +7112,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 43736-2023</t>
+          <t>A 22792-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45182</v>
+        <v>45448</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7185,7 +7185,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 42588-2023</t>
+          <t>A 4964-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7199,10 +7199,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45176</v>
+        <v>44593</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7258,7 +7258,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 15157-2023</t>
+          <t>A 11177-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45016</v>
+        <v>44987</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7331,7 +7331,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 497-2023</t>
+          <t>A 16215-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7345,10 +7345,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44930</v>
+        <v>44670</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7404,7 +7404,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 5184-2024</t>
+          <t>A 61620-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7418,10 +7418,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45330</v>
+        <v>44910</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7477,7 +7477,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 44107-2023</t>
+          <t>A 8924-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7491,10 +7491,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45188</v>
+        <v>44974</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.3</v>
+        <v>6.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7550,7 +7550,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 10196-2025</t>
+          <t>A 497-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7564,10 +7564,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45719</v>
+        <v>44930</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7623,7 +7623,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 4149-2022</t>
+          <t>A 11633-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7633,14 +7633,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44588</v>
+        <v>45373</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.1</v>
+        <v>4.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7696,7 +7696,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 13791-2026</t>
+          <t>A 11922-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46097</v>
+        <v>44993</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7769,7 +7769,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 13787-2026</t>
+          <t>A 14546-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46097</v>
+        <v>45394</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7842,7 +7842,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 13245-2024</t>
+          <t>A 32620-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7856,10 +7856,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45386</v>
+        <v>45111</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>13</v>
+        <v>1.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7915,7 +7915,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 27380-2026</t>
+          <t>A 1592-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7929,10 +7929,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46189</v>
+        <v>45306</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7988,7 +7988,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 21814-2025</t>
+          <t>A 4149-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7998,14 +7998,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45783</v>
+        <v>44588</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8061,7 +8061,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 21541-2025</t>
+          <t>A 15487-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8075,10 +8075,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45782</v>
+        <v>45747</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8134,7 +8134,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 21556-2025</t>
+          <t>A 11101-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45782</v>
+        <v>44986</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8207,7 +8207,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 20047-2024</t>
+          <t>A 5184-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8221,10 +8221,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45434</v>
+        <v>45330</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8280,7 +8280,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 34808-2024</t>
+          <t>A 13273-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8294,10 +8294,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45526</v>
+        <v>45386</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.6</v>
+        <v>12.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8353,7 +8353,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 5167-2024</t>
+          <t>A 44196-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8367,10 +8367,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45330</v>
+        <v>45573</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>6.5</v>
+        <v>1.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 23747-2025</t>
+          <t>A 21556-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45793</v>
+        <v>45782</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8499,7 +8499,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 24513-2025</t>
+          <t>A 21541-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45798</v>
+        <v>45782</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8572,7 +8572,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 27310-2023</t>
+          <t>A 21814-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45096</v>
+        <v>45783</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8645,7 +8645,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 22063-2025</t>
+          <t>A 20047-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8659,10 +8659,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45785</v>
+        <v>45434</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8718,7 +8718,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 17980-2025</t>
+          <t>A 34808-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8732,10 +8732,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45761</v>
+        <v>45526</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8791,7 +8791,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 19282-2025</t>
+          <t>A 5167-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8801,14 +8801,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45769</v>
+        <v>45330</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.8</v>
+        <v>6.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8881,7 +8881,7 @@
         <v>45854</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>

--- a/Översikt SVALÖV.xlsx
+++ b/Översikt SVALÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45910</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>45401</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45645</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45884</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>45401</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>45306</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>45434</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>45225</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>45964</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>44987</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>45351</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>45218</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>44763</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44598</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44483</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44847</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44501</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>44831</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>44854</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>45386</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>45442</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>45793</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>45448</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>45798</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>45531</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>45096</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>46049</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45908</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>45988</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>45911</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>45030</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>46051</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>45929</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>45708</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>45394</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>46100</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>45434</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>46107</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>46042</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44923</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>45910</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>46127</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>45016</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>44991</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>45141</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>45911</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>44986</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>45909</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>45188</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>46006</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>45070</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>44860</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>45785</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>45761</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>45761</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>45769</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         <v>46127</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         <v>46169</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>45987</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>46177</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>44600</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>45719</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>45880</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>45188</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>46178</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         <v>45148</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>45895</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>46202</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>45176</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>45671</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>45671</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>46210</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>46206</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>45182</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>44617</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>44806</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>45330</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>45758</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>46097</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>46097</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>46189</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         <v>45448</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>44593</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>44987</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         <v>44670</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>44910</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>44974</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>44930</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>45373</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         <v>44993</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         <v>45394</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>45111</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         <v>45306</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>44588</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>45747</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>44986</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         <v>45330</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>45386</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>45573</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>45782</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>45782</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8589,7 +8589,7 @@
         <v>45783</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>45434</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>45526</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>45330</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>45854</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>

--- a/Översikt SVALÖV.xlsx
+++ b/Översikt SVALÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45910</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>45401</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45645</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45884</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>45401</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>45306</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>45434</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>45225</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>45964</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>44987</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>45351</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>45218</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>44763</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44598</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44483</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44847</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44501</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>44831</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>44854</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>45386</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>45442</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>45793</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>45448</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>45798</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>45531</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>45096</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>46049</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45908</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>45988</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>45911</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>45030</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>46051</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>45929</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>45708</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>45394</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>46100</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>45434</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>46107</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>46042</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44923</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>45910</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>46127</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>45016</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>44991</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>45141</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>45911</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>44986</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>45909</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>45188</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>46006</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>45070</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>44860</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>45785</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>45761</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>45761</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>45769</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         <v>46127</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         <v>46169</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>45987</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>46177</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>44600</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>45719</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>45880</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>45188</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>46178</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         <v>45148</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>45895</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>46202</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>45176</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>45671</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>45671</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>46210</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>46206</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>45182</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>44617</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>44806</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>45330</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>45758</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>46097</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>46097</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>46189</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         <v>45448</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>44593</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>44987</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         <v>44670</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>44910</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>44974</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>44930</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>45373</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         <v>44993</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         <v>45394</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>45111</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         <v>45306</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>44588</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>45747</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>44986</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         <v>45330</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>45386</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>45573</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>45782</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>45782</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8589,7 +8589,7 @@
         <v>45783</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>45434</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>45526</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>45330</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>45854</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>

--- a/Översikt SVALÖV.xlsx
+++ b/Översikt SVALÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45910</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 15475-2024</t>
+          <t>A 38522-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45401</v>
+        <v>45884</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.7</v>
+        <v>2.6</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -848,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -857,10 +857,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -869,259 +869,259 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Skogsknipprot
+Stor häxört</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 38522-2025 artfynd.xlsx", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 38522-2025 karta.png", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 38522-2025 georefererad karta.tif", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 38522-2025 FSC-klagomål.docx", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 38522-2025 FSC-klagomål mail.docx", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 38522-2025 tillsynsbegäran.docx", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 38522-2025 tillsynsbegäran mail.docx", "A 38522-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 15475-2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45401</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SVALÖV</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>1</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Ask
 Strutbräken</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15475-2024 artfynd.xlsx", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15475-2024 karta.png", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15475-2024 georefererad karta.tif", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15475-2024 FSC-klagomål.docx", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15475-2024 FSC-klagomål mail.docx", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15475-2024 tillsynsbegäran.docx", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15475-2024 tillsynsbegäran mail.docx", "A 15475-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>A 61064-2024</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
         <v>45645</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SVALÖV</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
+      <c r="E6" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>SVALÖV</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>5.6</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K6" t="n">
         <v>1</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>1</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R6" t="n">
         <v>1</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S6" t="n">
         <v>2</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T6" t="n">
         <v>2</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Ask
 Skogsknipprot</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 61064-2024 artfynd.xlsx", "A 61064-2024")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 61064-2024 karta.png", "A 61064-2024")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 61064-2024 georefererad karta.tif", "A 61064-2024")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 61064-2024 FSC-klagomål.docx", "A 61064-2024")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 61064-2024 FSC-klagomål mail.docx", "A 61064-2024")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 61064-2024 tillsynsbegäran.docx", "A 61064-2024")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 61064-2024 tillsynsbegäran mail.docx", "A 61064-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 38522-2025</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45884</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>SVALÖV</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Skogsknipprot
-Stor häxört</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 38522-2025 artfynd.xlsx", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 38522-2025 karta.png", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 38522-2025 georefererad karta.tif", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 38522-2025 FSC-klagomål.docx", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 38522-2025 FSC-klagomål mail.docx", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 38522-2025 tillsynsbegäran.docx", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 38522-2025 tillsynsbegäran mail.docx", "A 38522-2025")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 15456-2024</t>
+          <t>A 8169-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45401</v>
+        <v>45351</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1160,10 +1160,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1178,7 +1178,7 @@
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1191,42 +1191,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Lundticka</t>
+          <t>Mjukdån</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15456-2024 artfynd.xlsx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 8169-2024 artfynd.xlsx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15456-2024 karta.png", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 8169-2024 karta.png", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15456-2024 georefererad karta.tif", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 8169-2024 georefererad karta.tif", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15456-2024 FSC-klagomål.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 8169-2024 FSC-klagomål.docx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15456-2024 FSC-klagomål mail.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 8169-2024 FSC-klagomål mail.docx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15456-2024 tillsynsbegäran.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 8169-2024 tillsynsbegäran.docx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15456-2024 tillsynsbegäran mail.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 8169-2024 tillsynsbegäran mail.docx", "A 8169-2024")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 1577-2024</t>
+          <t>A 11170-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45306</v>
+        <v>44987</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1256,23 +1256,23 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>21.2</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
@@ -1280,10 +1280,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1292,46 +1292,46 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Korndådra</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11170-2023 artfynd.xlsx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11170-2023 karta.png", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11170-2023 georefererad karta.tif", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11170-2023 FSC-klagomål.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11170-2023 FSC-klagomål mail.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11170-2023 tillsynsbegäran.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11170-2023 tillsynsbegäran mail.docx", "A 11170-2023")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 20125-2024</t>
+          <t>A 15456-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45434</v>
+        <v>45401</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1361,20 +1361,20 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.7</v>
+        <v>2.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
@@ -1385,10 +1385,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1401,42 +1401,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Lundticka</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 20125-2024 artfynd.xlsx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15456-2024 artfynd.xlsx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 20125-2024 karta.png", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15456-2024 karta.png", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 20125-2024 georefererad karta.tif", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15456-2024 georefererad karta.tif", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 20125-2024 FSC-klagomål.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15456-2024 FSC-klagomål.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 20125-2024 FSC-klagomål mail.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15456-2024 FSC-klagomål mail.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 20125-2024 tillsynsbegäran.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15456-2024 tillsynsbegäran.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 20125-2024 tillsynsbegäran mail.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15456-2024 tillsynsbegäran mail.docx", "A 15456-2024")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 11672-2024</t>
+          <t>A 20125-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45373</v>
+        <v>45434</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1466,16 +1466,16 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>13.9</v>
+        <v>5.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1490,7 +1490,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1502,39 +1502,39 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11672-2024 artfynd.xlsx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 20125-2024 artfynd.xlsx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11672-2024 karta.png", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 20125-2024 karta.png", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11672-2024 georefererad karta.tif", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 20125-2024 georefererad karta.tif", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11672-2024 FSC-klagomål.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 20125-2024 FSC-klagomål.docx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11672-2024 FSC-klagomål mail.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 20125-2024 FSC-klagomål mail.docx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11672-2024 tillsynsbegäran.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 20125-2024 tillsynsbegäran.docx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11672-2024 tillsynsbegäran mail.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 20125-2024 tillsynsbegäran mail.docx", "A 20125-2024")</f>
         <v/>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
         <v>45225</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 54127-2025</t>
+          <t>A 11672-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1660,10 +1660,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45964</v>
+        <v>45373</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.3</v>
+        <v>13.9</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1716,46 +1716,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 54127-2025 artfynd.xlsx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11672-2024 artfynd.xlsx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 54127-2025 karta.png", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11672-2024 karta.png", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 54127-2025 georefererad karta.tif", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11672-2024 georefererad karta.tif", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 54127-2025 FSC-klagomål.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11672-2024 FSC-klagomål.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 54127-2025 FSC-klagomål mail.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11672-2024 FSC-klagomål mail.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 54127-2025 tillsynsbegäran.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11672-2024 tillsynsbegäran.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 54127-2025 tillsynsbegäran mail.docx", "A 54127-2025")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/fåglar/A 54127-2025 prioriterade fågelarter.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11672-2024 tillsynsbegäran mail.docx", "A 11672-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 11170-2023</t>
+          <t>A 54127-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1769,10 +1765,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44987</v>
+        <v>45964</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1785,22 +1781,22 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1812,7 +1808,7 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1825,42 +1821,46 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Korndådra</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11170-2023 artfynd.xlsx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 54127-2025 artfynd.xlsx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11170-2023 karta.png", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 54127-2025 karta.png", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11170-2023 georefererad karta.tif", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 54127-2025 georefererad karta.tif", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11170-2023 FSC-klagomål.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 54127-2025 FSC-klagomål.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11170-2023 FSC-klagomål mail.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 54127-2025 FSC-klagomål mail.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11170-2023 tillsynsbegäran.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 54127-2025 tillsynsbegäran.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11170-2023 tillsynsbegäran mail.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 54127-2025 tillsynsbegäran mail.docx", "A 54127-2025")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/fåglar/A 54127-2025 prioriterade fågelarter.docx", "A 54127-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 8169-2024</t>
+          <t>A 1577-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45351</v>
+        <v>45306</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1890,16 +1890,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.1</v>
+        <v>21.2</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1914,7 +1914,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1930,35 +1930,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Mjukdån</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 8169-2024 artfynd.xlsx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 8169-2024 karta.png", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 8169-2024 georefererad karta.tif", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 8169-2024 FSC-klagomål.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 8169-2024 FSC-klagomål mail.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 8169-2024 tillsynsbegäran.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 8169-2024 tillsynsbegäran mail.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         <v>45218</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>44763</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44598</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44483</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44847</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44501</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>44831</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>44854</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 13245-2024</t>
+          <t>A 49032-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2595,10 +2595,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45386</v>
+        <v>44860</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>13</v>
+        <v>3.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 21774-2024</t>
+          <t>A 35911-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45442</v>
+        <v>45148</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 23747-2025</t>
+          <t>A 9716-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45793</v>
+        <v>44617</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2800,7 +2800,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 22794-2024</t>
+          <t>A 11101-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2814,10 +2814,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45448</v>
+        <v>44986</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 24513-2025</t>
+          <t>A 11177-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45798</v>
+        <v>44987</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 35587-2024</t>
+          <t>A 20047-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45531</v>
+        <v>45434</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3019,7 +3019,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 27310-2023</t>
+          <t>A 34808-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45096</v>
+        <v>45526</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3092,7 +3092,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 5068-2026</t>
+          <t>A 1592-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3106,10 +3106,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46049</v>
+        <v>45306</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3165,7 +3165,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 42706-2025</t>
+          <t>A 5167-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45908</v>
+        <v>45330</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>6.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3238,7 +3238,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 59266-2025</t>
+          <t>A 23747-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45988</v>
+        <v>45793</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3311,7 +3311,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 43425-2025</t>
+          <t>A 24513-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45911</v>
+        <v>45798</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3384,7 +3384,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 16667-2023</t>
+          <t>A 27310-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45030</v>
+        <v>45096</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 6365-2026</t>
+          <t>A 10209-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46051</v>
+        <v>44986</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 47139-2025</t>
+          <t>A 42706-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45929</v>
+        <v>45908</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3603,7 +3603,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 8332-2025</t>
+          <t>A 43425-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45708</v>
+        <v>45911</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3676,7 +3676,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 14543-2024</t>
+          <t>A 47139-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45394</v>
+        <v>45929</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 14533-2026</t>
+          <t>A 22262-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46100</v>
+        <v>45070</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 20170-2024</t>
+          <t>A 22063-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45434</v>
+        <v>45785</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3895,7 +3895,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 15747-2026</t>
+          <t>A 6335-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46107</v>
+        <v>44600</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3968,7 +3968,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 3430-2026</t>
+          <t>A 17980-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3982,10 +3982,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46042</v>
+        <v>45761</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4041,7 +4041,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 62403-2022</t>
+          <t>A 16667-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44923</v>
+        <v>45030</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 43294-2025</t>
+          <t>A 19282-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4124,14 +4124,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45910</v>
+        <v>45769</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4187,7 +4187,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 18926-2026</t>
+          <t>A 1920-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4201,10 +4201,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46127</v>
+        <v>45671</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4260,7 +4260,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 15157-2023</t>
+          <t>A 8332-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4274,10 +4274,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45016</v>
+        <v>45708</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4333,7 +4333,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 11491-2023</t>
+          <t>A 43294-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4347,10 +4347,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44991</v>
+        <v>45910</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4406,7 +4406,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 34810-2023</t>
+          <t>A 37907-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45141</v>
+        <v>45880</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4435,8 +4435,13 @@
           <t>SVALÖV</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4479,7 +4484,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 43466-2025</t>
+          <t>A 40470-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4489,14 +4494,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45911</v>
+        <v>45895</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4509,7 +4514,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.5</v>
+        <v>0.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4552,7 +4557,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 10209-2023</t>
+          <t>A 44112-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4566,10 +4571,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44986</v>
+        <v>45188</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4582,7 +4587,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4625,7 +4630,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 43004-2025</t>
+          <t>A 11491-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4639,10 +4644,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45909</v>
+        <v>44991</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4655,7 +4660,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4698,7 +4703,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 44107-2023</t>
+          <t>A 11922-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4712,10 +4717,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45188</v>
+        <v>44993</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4728,7 +4733,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4771,7 +4776,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 62201-2025</t>
+          <t>A 5068-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4785,10 +4790,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46006</v>
+        <v>46049</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4801,7 +4806,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>22.1</v>
+        <v>3.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4844,7 +4849,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 22262-2023</t>
+          <t>A 43466-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4858,10 +4863,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45070</v>
+        <v>45911</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4874,7 +4879,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4917,7 +4922,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 49032-2022</t>
+          <t>A 59266-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4931,10 +4936,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44860</v>
+        <v>45988</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4947,7 +4952,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4990,7 +4995,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 22063-2025</t>
+          <t>A 43004-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5004,10 +5009,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45785</v>
+        <v>45909</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5020,7 +5025,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5063,7 +5068,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 18121-2025</t>
+          <t>A 6365-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5077,10 +5082,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45761</v>
+        <v>46051</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5093,7 +5098,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5136,7 +5141,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 17980-2025</t>
+          <t>A 35587-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5150,10 +5155,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45761</v>
+        <v>45531</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5166,7 +5171,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5209,7 +5214,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 19282-2025</t>
+          <t>A 8924-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5219,14 +5224,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45769</v>
+        <v>44974</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5239,7 +5244,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.8</v>
+        <v>6.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5282,7 +5287,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 18438-2026</t>
+          <t>A 14533-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5296,10 +5301,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46127</v>
+        <v>46100</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5312,7 +5317,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5355,7 +5360,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 24286-2026</t>
+          <t>A 1901-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5369,10 +5374,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46169</v>
+        <v>45671</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5385,7 +5390,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.9</v>
+        <v>4.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5428,7 +5433,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 58970-2025</t>
+          <t>A 15747-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5442,10 +5447,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45987</v>
+        <v>46107</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5458,7 +5463,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5501,7 +5506,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 25522-2026</t>
+          <t>A 22794-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5515,10 +5520,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46177</v>
+        <v>45448</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5531,7 +5536,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>8.5</v>
+        <v>3.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5574,7 +5579,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 6335-2022</t>
+          <t>A 3430-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5588,10 +5593,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44600</v>
+        <v>46042</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5604,7 +5609,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5647,7 +5652,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 10196-2025</t>
+          <t>A 32620-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5661,10 +5666,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45719</v>
+        <v>45111</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5677,7 +5682,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5720,7 +5725,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 37907-2025</t>
+          <t>A 44196-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5734,10 +5739,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45880</v>
+        <v>45573</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5749,13 +5754,8 @@
           <t>SVALÖV</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>5.7</v>
+        <v>1.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5798,7 +5798,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 44112-2023</t>
+          <t>A 17731-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5808,14 +5808,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45188</v>
+        <v>45758</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5871,7 +5871,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 25832-2026</t>
+          <t>A 14543-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46178</v>
+        <v>45394</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>7.8</v>
+        <v>0.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5944,7 +5944,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 35911-2023</t>
+          <t>A 18926-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5958,10 +5958,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45148</v>
+        <v>46127</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6017,7 +6017,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 40470-2025</t>
+          <t>A 13273-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6027,14 +6027,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45895</v>
+        <v>45386</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.1</v>
+        <v>12.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6090,7 +6090,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 29337-2026</t>
+          <t>A 34810-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6104,10 +6104,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46202</v>
+        <v>45141</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6163,7 +6163,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 42588-2023</t>
+          <t>A 22792-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45176</v>
+        <v>45448</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 1901-2025</t>
+          <t>A 14546-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6250,10 +6250,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45671</v>
+        <v>45394</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4.2</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 1920-2025</t>
+          <t>A 62201-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6323,10 +6323,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45671</v>
+        <v>46006</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.3</v>
+        <v>22.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6382,7 +6382,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 30535-2026</t>
+          <t>A 18121-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6396,10 +6396,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46210</v>
+        <v>45761</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6455,7 +6455,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 30202-2026</t>
+          <t>A 16215-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6469,10 +6469,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46206</v>
+        <v>44670</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6528,7 +6528,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 43736-2023</t>
+          <t>A 15487-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45182</v>
+        <v>45747</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6601,7 +6601,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 9716-2022</t>
+          <t>A 4964-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44617</v>
+        <v>44593</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
         <v>44806</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 5190-2024</t>
+          <t>A 18438-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6761,10 +6761,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45330</v>
+        <v>46127</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6820,7 +6820,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 17731-2025</t>
+          <t>A 11633-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6830,14 +6830,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45758</v>
+        <v>45373</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.8</v>
+        <v>4.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6893,7 +6893,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 13791-2026</t>
+          <t>A 24286-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46097</v>
+        <v>46169</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6966,7 +6966,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 13787-2026</t>
+          <t>A 58970-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6980,10 +6980,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46097</v>
+        <v>45987</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 27380-2026</t>
+          <t>A 25522-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46189</v>
+        <v>46177</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.7</v>
+        <v>8.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7112,7 +7112,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 22792-2024</t>
+          <t>A 20170-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45448</v>
+        <v>45434</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7185,7 +7185,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 4964-2022</t>
+          <t>A 29337-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7199,10 +7199,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44593</v>
+        <v>46202</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7258,7 +7258,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 11177-2023</t>
+          <t>A 25832-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44987</v>
+        <v>46178</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.2</v>
+        <v>7.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7331,7 +7331,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 16215-2022</t>
+          <t>A 61620-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7345,10 +7345,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44670</v>
+        <v>44910</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7404,7 +7404,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 61620-2022</t>
+          <t>A 5190-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7418,10 +7418,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44910</v>
+        <v>45330</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7477,7 +7477,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 8924-2023</t>
+          <t>A 30202-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7491,10 +7491,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44974</v>
+        <v>46206</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>6.8</v>
+        <v>5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7550,7 +7550,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 497-2023</t>
+          <t>A 21774-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7564,10 +7564,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44930</v>
+        <v>45442</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7623,7 +7623,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 11633-2024</t>
+          <t>A 30535-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7637,10 +7637,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45373</v>
+        <v>46210</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4.9</v>
+        <v>0.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7696,7 +7696,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 11922-2023</t>
+          <t>A 62403-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44993</v>
+        <v>44923</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7769,7 +7769,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 14546-2024</t>
+          <t>A 43736-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45394</v>
+        <v>45182</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7842,7 +7842,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 32620-2023</t>
+          <t>A 42588-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7856,10 +7856,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45111</v>
+        <v>45176</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7915,7 +7915,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 1592-2024</t>
+          <t>A 15157-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7929,10 +7929,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45306</v>
+        <v>45016</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7988,7 +7988,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 4149-2022</t>
+          <t>A 497-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7998,14 +7998,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44588</v>
+        <v>44930</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8061,7 +8061,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 15487-2025</t>
+          <t>A 5184-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8075,10 +8075,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45747</v>
+        <v>45330</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8134,7 +8134,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 11101-2023</t>
+          <t>A 44107-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44986</v>
+        <v>45188</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8207,7 +8207,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 5184-2024</t>
+          <t>A 10196-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8221,10 +8221,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45330</v>
+        <v>45719</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8280,7 +8280,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 13273-2024</t>
+          <t>A 4149-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8290,14 +8290,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45386</v>
+        <v>44588</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>12.4</v>
+        <v>1.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8353,7 +8353,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 44196-2024</t>
+          <t>A 13245-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8367,10 +8367,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45573</v>
+        <v>45386</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.8</v>
+        <v>13</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 21556-2025</t>
+          <t>A 13791-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45782</v>
+        <v>46097</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8499,7 +8499,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 21541-2025</t>
+          <t>A 13787-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45782</v>
+        <v>46097</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8589,7 +8589,7 @@
         <v>45783</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 20047-2024</t>
+          <t>A 21541-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8659,10 +8659,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45434</v>
+        <v>45782</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8718,7 +8718,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 34808-2024</t>
+          <t>A 21556-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8732,10 +8732,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45526</v>
+        <v>45782</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8791,7 +8791,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 5167-2024</t>
+          <t>A 27380-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45330</v>
+        <v>46189</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>6.5</v>
+        <v>1.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8881,7 +8881,7 @@
         <v>45854</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>

--- a/Översikt SVALÖV.xlsx
+++ b/Översikt SVALÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45910</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 38522-2025</t>
+          <t>A 15475-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45884</v>
+        <v>45401</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -833,14 +833,14 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
@@ -848,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -857,10 +857,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -869,146 +869,146 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15475-2024 artfynd.xlsx", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15475-2024 karta.png", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15475-2024 georefererad karta.tif", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15475-2024 FSC-klagomål.docx", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15475-2024 FSC-klagomål mail.docx", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15475-2024 tillsynsbegäran.docx", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15475-2024 tillsynsbegäran mail.docx", "A 15475-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 38522-2025</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SVALÖV</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Skogsknipprot
 Stor häxört</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 38522-2025 artfynd.xlsx", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 38522-2025 karta.png", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 38522-2025 georefererad karta.tif", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 38522-2025 FSC-klagomål.docx", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 38522-2025 FSC-klagomål mail.docx", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 38522-2025 tillsynsbegäran.docx", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 38522-2025 tillsynsbegäran mail.docx", "A 38522-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 15475-2024</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45401</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SVALÖV</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15475-2024 artfynd.xlsx", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15475-2024 karta.png", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15475-2024 georefererad karta.tif", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15475-2024 FSC-klagomål.docx", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15475-2024 FSC-klagomål mail.docx", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15475-2024 tillsynsbegäran.docx", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15475-2024 tillsynsbegäran mail.docx", "A 15475-2024")</f>
         <v/>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
         <v>45645</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 8169-2024</t>
+          <t>A 15456-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45351</v>
+        <v>45401</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1160,10 +1160,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1178,7 +1178,7 @@
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1191,42 +1191,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Mjukdån</t>
+          <t>Lundticka</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 8169-2024 artfynd.xlsx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15456-2024 artfynd.xlsx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 8169-2024 karta.png", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15456-2024 karta.png", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 8169-2024 georefererad karta.tif", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15456-2024 georefererad karta.tif", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 8169-2024 FSC-klagomål.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15456-2024 FSC-klagomål.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 8169-2024 FSC-klagomål mail.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15456-2024 FSC-klagomål mail.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 8169-2024 tillsynsbegäran.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15456-2024 tillsynsbegäran.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 8169-2024 tillsynsbegäran mail.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15456-2024 tillsynsbegäran mail.docx", "A 15456-2024")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 11170-2023</t>
+          <t>A 8169-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44987</v>
+        <v>45351</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1265,13 +1265,13 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1283,7 +1283,7 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1292,46 +1292,46 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Korndådra</t>
+          <t>Mjukdån</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11170-2023 artfynd.xlsx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 8169-2024 artfynd.xlsx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11170-2023 karta.png", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 8169-2024 karta.png", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11170-2023 georefererad karta.tif", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 8169-2024 georefererad karta.tif", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11170-2023 FSC-klagomål.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 8169-2024 FSC-klagomål.docx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11170-2023 FSC-klagomål mail.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 8169-2024 FSC-klagomål mail.docx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11170-2023 tillsynsbegäran.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 8169-2024 tillsynsbegäran.docx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11170-2023 tillsynsbegäran mail.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 8169-2024 tillsynsbegäran mail.docx", "A 8169-2024")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 15456-2024</t>
+          <t>A 1577-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45401</v>
+        <v>45306</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.5</v>
+        <v>21.2</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1373,7 +1373,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1385,10 +1385,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1401,35 +1401,35 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Lundticka</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15456-2024 artfynd.xlsx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15456-2024 karta.png", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15456-2024 georefererad karta.tif", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15456-2024 FSC-klagomål.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15456-2024 FSC-klagomål mail.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15456-2024 tillsynsbegäran.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15456-2024 tillsynsbegäran mail.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
         <v>45434</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 52664-2023</t>
+          <t>A 11672-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45225</v>
+        <v>45373</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1571,31 +1571,31 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>6.4</v>
+        <v>13.9</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1607,46 +1607,46 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 52664-2023 artfynd.xlsx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11672-2024 artfynd.xlsx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 52664-2023 karta.png", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11672-2024 karta.png", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 52664-2023 georefererad karta.tif", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11672-2024 georefererad karta.tif", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 52664-2023 FSC-klagomål.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11672-2024 FSC-klagomål.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 52664-2023 FSC-klagomål mail.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11672-2024 FSC-klagomål mail.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 52664-2023 tillsynsbegäran.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11672-2024 tillsynsbegäran.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 52664-2023 tillsynsbegäran mail.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11672-2024 tillsynsbegäran mail.docx", "A 11672-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 11672-2024</t>
+          <t>A 52664-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1660,10 +1660,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45373</v>
+        <v>45225</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1676,16 +1676,16 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>13.9</v>
+        <v>6.4</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1700,7 +1700,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1712,46 +1712,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11672-2024 artfynd.xlsx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 52664-2023 artfynd.xlsx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11672-2024 karta.png", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 52664-2023 karta.png", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11672-2024 georefererad karta.tif", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 52664-2023 georefererad karta.tif", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11672-2024 FSC-klagomål.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 52664-2023 FSC-klagomål.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11672-2024 FSC-klagomål mail.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 52664-2023 FSC-klagomål mail.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11672-2024 tillsynsbegäran.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 52664-2023 tillsynsbegäran.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11672-2024 tillsynsbegäran mail.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 52664-2023 tillsynsbegäran mail.docx", "A 52664-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 54127-2025</t>
+          <t>A 11170-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45964</v>
+        <v>44987</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1781,22 +1781,22 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1808,7 +1808,7 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1821,46 +1821,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Korndådra</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 54127-2025 artfynd.xlsx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11170-2023 artfynd.xlsx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 54127-2025 karta.png", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11170-2023 karta.png", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 54127-2025 georefererad karta.tif", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11170-2023 georefererad karta.tif", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 54127-2025 FSC-klagomål.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11170-2023 FSC-klagomål.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 54127-2025 FSC-klagomål mail.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11170-2023 FSC-klagomål mail.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 54127-2025 tillsynsbegäran.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11170-2023 tillsynsbegäran.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 54127-2025 tillsynsbegäran mail.docx", "A 54127-2025")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/fåglar/A 54127-2025 prioriterade fågelarter.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11170-2023 tillsynsbegäran mail.docx", "A 11170-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 1577-2024</t>
+          <t>A 54127-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1874,10 +1870,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45306</v>
+        <v>45964</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1890,7 +1886,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>21.2</v>
+        <v>1.3</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1899,7 +1895,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1914,7 +1910,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1926,39 +1922,43 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 54127-2025 artfynd.xlsx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 54127-2025 karta.png", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 54127-2025 georefererad karta.tif", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 54127-2025 FSC-klagomål.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 54127-2025 FSC-klagomål mail.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 54127-2025 tillsynsbegäran.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 54127-2025 tillsynsbegäran mail.docx", "A 54127-2025")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/fåglar/A 54127-2025 prioriterade fågelarter.docx", "A 54127-2025")</f>
         <v/>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         <v>45218</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>44763</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44598</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44483</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44847</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44501</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>44831</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>44854</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 49032-2022</t>
+          <t>A 13245-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2595,10 +2595,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44860</v>
+        <v>45386</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.7</v>
+        <v>13</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 35911-2023</t>
+          <t>A 21774-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45148</v>
+        <v>45442</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 9716-2022</t>
+          <t>A 5167-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44617</v>
+        <v>45330</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>6.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2800,7 +2800,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 11101-2023</t>
+          <t>A 23747-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2814,10 +2814,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44986</v>
+        <v>45793</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 11177-2023</t>
+          <t>A 22794-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44987</v>
+        <v>45448</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 20047-2024</t>
+          <t>A 24513-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45434</v>
+        <v>45798</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3019,7 +3019,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 34808-2024</t>
+          <t>A 35587-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45526</v>
+        <v>45531</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3092,7 +3092,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 1592-2024</t>
+          <t>A 27310-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3106,10 +3106,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45306</v>
+        <v>45096</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3165,7 +3165,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 5167-2024</t>
+          <t>A 42706-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45330</v>
+        <v>45908</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>6.5</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3238,7 +3238,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 23747-2025</t>
+          <t>A 43425-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45793</v>
+        <v>45911</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3311,7 +3311,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 24513-2025</t>
+          <t>A 16667-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45798</v>
+        <v>45030</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.4</v>
+        <v>3.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3384,7 +3384,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 27310-2023</t>
+          <t>A 22063-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45096</v>
+        <v>45785</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10209-2023</t>
+          <t>A 47139-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44986</v>
+        <v>45929</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 42706-2025</t>
+          <t>A 17980-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45908</v>
+        <v>45761</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3603,7 +3603,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 43425-2025</t>
+          <t>A 19282-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3613,14 +3613,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45911</v>
+        <v>45769</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3676,7 +3676,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 47139-2025</t>
+          <t>A 8332-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45929</v>
+        <v>45708</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 22262-2023</t>
+          <t>A 14543-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45070</v>
+        <v>45394</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 22063-2025</t>
+          <t>A 5068-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45785</v>
+        <v>46049</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3895,7 +3895,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 6335-2022</t>
+          <t>A 59266-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44600</v>
+        <v>45988</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3968,7 +3968,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 17980-2025</t>
+          <t>A 20170-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3982,10 +3982,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45761</v>
+        <v>45434</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4041,7 +4041,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 16667-2023</t>
+          <t>A 37907-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45030</v>
+        <v>45880</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4070,8 +4070,13 @@
           <t>SVALÖV</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>3.8</v>
+        <v>5.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4114,7 +4119,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 19282-2025</t>
+          <t>A 62403-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4124,14 +4129,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45769</v>
+        <v>44923</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4144,7 +4149,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4187,7 +4192,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 1920-2025</t>
+          <t>A 40470-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4197,14 +4202,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45671</v>
+        <v>45895</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4217,7 +4222,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.3</v>
+        <v>0.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4260,7 +4265,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 8332-2025</t>
+          <t>A 43294-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4274,10 +4279,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45708</v>
+        <v>45910</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4290,7 +4295,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4333,7 +4338,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 43294-2025</t>
+          <t>A 6365-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4347,10 +4352,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45910</v>
+        <v>46051</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4363,7 +4368,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4406,7 +4411,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 37907-2025</t>
+          <t>A 15157-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4420,10 +4425,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45880</v>
+        <v>45016</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4435,13 +4440,8 @@
           <t>SVALÖV</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>5.7</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 40470-2025</t>
+          <t>A 11491-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4494,14 +4494,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45895</v>
+        <v>44991</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.1</v>
+        <v>2.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 44112-2023</t>
+          <t>A 43466-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45188</v>
+        <v>45911</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 11491-2023</t>
+          <t>A 10209-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44991</v>
+        <v>44986</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 11922-2023</t>
+          <t>A 43004-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44993</v>
+        <v>45909</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 5068-2026</t>
+          <t>A 44107-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46049</v>
+        <v>45188</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 43466-2025</t>
+          <t>A 14533-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45911</v>
+        <v>46100</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 59266-2025</t>
+          <t>A 15747-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45988</v>
+        <v>46107</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 43004-2025</t>
+          <t>A 22262-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45909</v>
+        <v>45070</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 6365-2026</t>
+          <t>A 3430-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46051</v>
+        <v>46042</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.9</v>
+        <v>5.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 35587-2024</t>
+          <t>A 49032-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5155,10 +5155,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45531</v>
+        <v>44860</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 8924-2023</t>
+          <t>A 18926-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44974</v>
+        <v>46127</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>6.8</v>
+        <v>1.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 14533-2026</t>
+          <t>A 18121-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46100</v>
+        <v>45761</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 1901-2025</t>
+          <t>A 34810-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45671</v>
+        <v>45141</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 15747-2026</t>
+          <t>A 62201-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46107</v>
+        <v>46006</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.4</v>
+        <v>22.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 22794-2024</t>
+          <t>A 6335-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45448</v>
+        <v>44600</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5579,7 +5579,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 3430-2026</t>
+          <t>A 10196-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46042</v>
+        <v>45719</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5.7</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 32620-2023</t>
+          <t>A 44112-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45111</v>
+        <v>45188</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5725,7 +5725,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 44196-2024</t>
+          <t>A 35911-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45573</v>
+        <v>45148</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5798,7 +5798,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 17731-2025</t>
+          <t>A 42588-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5808,14 +5808,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45758</v>
+        <v>45176</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5871,7 +5871,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 14543-2024</t>
+          <t>A 1901-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45394</v>
+        <v>45671</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5944,7 +5944,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 18926-2026</t>
+          <t>A 1920-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5958,10 +5958,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46127</v>
+        <v>45671</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6017,7 +6017,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 13273-2024</t>
+          <t>A 43736-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45386</v>
+        <v>45182</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>12.4</v>
+        <v>1.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6090,7 +6090,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 34810-2023</t>
+          <t>A 9716-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6104,10 +6104,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45141</v>
+        <v>44617</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6163,7 +6163,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 22792-2024</t>
+          <t>A 18438-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45448</v>
+        <v>46127</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 14546-2024</t>
+          <t>A 24286-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6250,10 +6250,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45394</v>
+        <v>46169</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 62201-2025</t>
+          <t>A 58970-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6323,10 +6323,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46006</v>
+        <v>45987</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>22.1</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6382,7 +6382,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 18121-2025</t>
+          <t>A 25522-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6396,10 +6396,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45761</v>
+        <v>46177</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.7</v>
+        <v>8.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6455,7 +6455,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 16215-2022</t>
+          <t>A 37354-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6469,10 +6469,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44670</v>
+        <v>44806</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6528,7 +6528,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 15487-2025</t>
+          <t>A 5190-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45747</v>
+        <v>45330</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6601,7 +6601,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 4964-2022</t>
+          <t>A 17731-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6611,14 +6611,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44593</v>
+        <v>45758</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6674,7 +6674,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 37354-2022</t>
+          <t>A 25832-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6688,10 +6688,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44806</v>
+        <v>46178</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.4</v>
+        <v>7.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6747,7 +6747,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 18438-2026</t>
+          <t>A 22792-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6761,10 +6761,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46127</v>
+        <v>45448</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6820,7 +6820,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 11633-2024</t>
+          <t>A 29337-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6834,10 +6834,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45373</v>
+        <v>46202</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.9</v>
+        <v>2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6893,7 +6893,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 24286-2026</t>
+          <t>A 4964-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46169</v>
+        <v>44593</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6966,7 +6966,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 58970-2025</t>
+          <t>A 30535-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6980,10 +6980,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45987</v>
+        <v>46210</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 25522-2026</t>
+          <t>A 30202-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46177</v>
+        <v>46206</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7112,7 +7112,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 20170-2024</t>
+          <t>A 11177-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45434</v>
+        <v>44987</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7185,7 +7185,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 29337-2026</t>
+          <t>A 16215-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7199,10 +7199,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46202</v>
+        <v>44670</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7258,7 +7258,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 25832-2026</t>
+          <t>A 61620-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46178</v>
+        <v>44910</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>7.8</v>
+        <v>1.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7331,7 +7331,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 61620-2022</t>
+          <t>A 8924-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7345,10 +7345,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44910</v>
+        <v>44974</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.5</v>
+        <v>6.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7404,7 +7404,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 5190-2024</t>
+          <t>A 497-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7418,10 +7418,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45330</v>
+        <v>44930</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7477,7 +7477,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 30202-2026</t>
+          <t>A 11633-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7491,10 +7491,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46206</v>
+        <v>45373</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7550,7 +7550,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 21774-2024</t>
+          <t>A 11922-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7564,10 +7564,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45442</v>
+        <v>44993</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7623,7 +7623,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 30535-2026</t>
+          <t>A 14546-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7637,10 +7637,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46210</v>
+        <v>45394</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7696,7 +7696,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 62403-2022</t>
+          <t>A 32620-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44923</v>
+        <v>45111</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7769,7 +7769,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 43736-2023</t>
+          <t>A 13791-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45182</v>
+        <v>46097</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7842,7 +7842,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 42588-2023</t>
+          <t>A 1592-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7856,10 +7856,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45176</v>
+        <v>45306</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7915,7 +7915,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 15157-2023</t>
+          <t>A 4149-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7925,14 +7925,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45016</v>
+        <v>44588</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7988,7 +7988,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 497-2023</t>
+          <t>A 13787-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8002,10 +8002,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44930</v>
+        <v>46097</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8061,7 +8061,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 5184-2024</t>
+          <t>A 15487-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8075,10 +8075,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45330</v>
+        <v>45747</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8134,7 +8134,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 44107-2023</t>
+          <t>A 27380-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45188</v>
+        <v>46189</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8207,7 +8207,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 10196-2025</t>
+          <t>A 11101-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8221,10 +8221,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45719</v>
+        <v>44986</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8280,7 +8280,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 4149-2022</t>
+          <t>A 5184-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8290,14 +8290,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44588</v>
+        <v>45330</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8353,7 +8353,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 13245-2024</t>
+          <t>A 13273-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8370,7 +8370,7 @@
         <v>45386</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>13</v>
+        <v>12.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 13791-2026</t>
+          <t>A 44196-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46097</v>
+        <v>45573</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8499,7 +8499,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 13787-2026</t>
+          <t>A 21556-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46097</v>
+        <v>45782</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8572,7 +8572,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 21814-2025</t>
+          <t>A 21541-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45783</v>
+        <v>45782</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8645,7 +8645,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 21541-2025</t>
+          <t>A 21814-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8659,10 +8659,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45782</v>
+        <v>45783</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8718,7 +8718,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 21556-2025</t>
+          <t>A 20047-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8732,10 +8732,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45782</v>
+        <v>45434</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8791,7 +8791,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 27380-2026</t>
+          <t>A 34808-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46189</v>
+        <v>45526</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8881,7 +8881,7 @@
         <v>45854</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>

--- a/Översikt SVALÖV.xlsx
+++ b/Översikt SVALÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45910</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>45401</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45884</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45645</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 15456-2024</t>
+          <t>A 1577-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45401</v>
+        <v>45306</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.5</v>
+        <v>21.2</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1163,7 +1163,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1191,42 +1191,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Lundticka</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15456-2024 artfynd.xlsx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15456-2024 karta.png", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15456-2024 georefererad karta.tif", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15456-2024 FSC-klagomål.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15456-2024 FSC-klagomål mail.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15456-2024 tillsynsbegäran.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15456-2024 tillsynsbegäran mail.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 8169-2024</t>
+          <t>A 15456-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45351</v>
+        <v>45401</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1265,10 +1265,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1283,7 +1283,7 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1296,42 +1296,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Mjukdån</t>
+          <t>Lundticka</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 8169-2024 artfynd.xlsx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15456-2024 artfynd.xlsx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 8169-2024 karta.png", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15456-2024 karta.png", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 8169-2024 georefererad karta.tif", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15456-2024 georefererad karta.tif", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 8169-2024 FSC-klagomål.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15456-2024 FSC-klagomål.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 8169-2024 FSC-klagomål mail.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15456-2024 FSC-klagomål mail.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 8169-2024 tillsynsbegäran.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15456-2024 tillsynsbegäran.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 8169-2024 tillsynsbegäran mail.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15456-2024 tillsynsbegäran mail.docx", "A 15456-2024")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 1577-2024</t>
+          <t>A 8169-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45306</v>
+        <v>45351</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1361,17 +1361,17 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>21.2</v>
+        <v>3.1</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
@@ -1385,7 +1385,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1401,42 +1401,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Mjukdån</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 8169-2024 artfynd.xlsx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 8169-2024 karta.png", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 8169-2024 georefererad karta.tif", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 8169-2024 FSC-klagomål.docx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 8169-2024 FSC-klagomål mail.docx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 8169-2024 tillsynsbegäran.docx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 8169-2024 tillsynsbegäran mail.docx", "A 8169-2024")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 20125-2024</t>
+          <t>A 11170-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45434</v>
+        <v>44987</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1466,23 +1466,23 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5.7</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
         <v>1</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
@@ -1490,10 +1490,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1502,46 +1502,46 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Korndådra</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 20125-2024 artfynd.xlsx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11170-2023 artfynd.xlsx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 20125-2024 karta.png", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11170-2023 karta.png", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 20125-2024 georefererad karta.tif", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11170-2023 georefererad karta.tif", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 20125-2024 FSC-klagomål.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11170-2023 FSC-klagomål.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 20125-2024 FSC-klagomål mail.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11170-2023 FSC-klagomål mail.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 20125-2024 tillsynsbegäran.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11170-2023 tillsynsbegäran.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 20125-2024 tillsynsbegäran mail.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11170-2023 tillsynsbegäran mail.docx", "A 11170-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 11672-2024</t>
+          <t>A 20125-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45373</v>
+        <v>45434</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1571,16 +1571,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>13.9</v>
+        <v>5.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1595,7 +1595,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1607,39 +1607,39 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11672-2024 artfynd.xlsx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 20125-2024 artfynd.xlsx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11672-2024 karta.png", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 20125-2024 karta.png", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11672-2024 georefererad karta.tif", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 20125-2024 georefererad karta.tif", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11672-2024 FSC-klagomål.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 20125-2024 FSC-klagomål.docx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11672-2024 FSC-klagomål mail.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 20125-2024 FSC-klagomål mail.docx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11672-2024 tillsynsbegäran.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 20125-2024 tillsynsbegäran.docx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11672-2024 tillsynsbegäran mail.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 20125-2024 tillsynsbegäran mail.docx", "A 20125-2024")</f>
         <v/>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
         <v>45225</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 11170-2023</t>
+          <t>A 11672-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44987</v>
+        <v>45373</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>13.9</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1790,13 +1790,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1808,7 +1808,7 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1821,35 +1821,35 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Korndådra</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11170-2023 artfynd.xlsx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11672-2024 artfynd.xlsx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11170-2023 karta.png", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11672-2024 karta.png", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11170-2023 georefererad karta.tif", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11672-2024 georefererad karta.tif", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11170-2023 FSC-klagomål.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11672-2024 FSC-klagomål.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11170-2023 FSC-klagomål mail.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11672-2024 FSC-klagomål mail.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11170-2023 tillsynsbegäran.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11672-2024 tillsynsbegäran.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11170-2023 tillsynsbegäran mail.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11672-2024 tillsynsbegäran mail.docx", "A 11672-2024")</f>
         <v/>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         <v>45964</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>45218</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>44763</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44598</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44483</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44847</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 61495-2021</t>
+          <t>A 42617-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2372,14 +2372,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44501</v>
+        <v>44831</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2435,7 +2435,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 42617-2022</t>
+          <t>A 47717-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44831</v>
+        <v>44854</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 47717-2022</t>
+          <t>A 61495-2021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2518,14 +2518,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44854</v>
+        <v>44501</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2581,7 +2581,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 13245-2024</t>
+          <t>A 8332-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2595,10 +2595,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45386</v>
+        <v>45708</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>13</v>
+        <v>0.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 21774-2024</t>
+          <t>A 44112-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45442</v>
+        <v>45188</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 5167-2024</t>
+          <t>A 15487-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45330</v>
+        <v>45747</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>6.5</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2800,7 +2800,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 23747-2025</t>
+          <t>A 4964-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2814,10 +2814,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45793</v>
+        <v>44593</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 22794-2024</t>
+          <t>A 37354-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45448</v>
+        <v>44806</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 24513-2025</t>
+          <t>A 49032-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45798</v>
+        <v>44860</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3019,7 +3019,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 35587-2024</t>
+          <t>A 11491-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45531</v>
+        <v>44991</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3092,7 +3092,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 27310-2023</t>
+          <t>A 497-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3106,10 +3106,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45096</v>
+        <v>44930</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3165,7 +3165,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 42706-2025</t>
+          <t>A 11922-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45908</v>
+        <v>44993</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3238,7 +3238,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 43425-2025</t>
+          <t>A 5184-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45911</v>
+        <v>45330</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3311,7 +3311,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 16667-2023</t>
+          <t>A 44107-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45030</v>
+        <v>45188</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3384,7 +3384,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 22063-2025</t>
+          <t>A 35911-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45785</v>
+        <v>45148</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 47139-2025</t>
+          <t>A 10196-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45929</v>
+        <v>45719</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 17980-2025</t>
+          <t>A 11633-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45761</v>
+        <v>45373</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3603,7 +3603,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 19282-2025</t>
+          <t>A 9716-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3613,14 +3613,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45769</v>
+        <v>44617</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3676,7 +3676,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 8332-2025</t>
+          <t>A 4149-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3686,14 +3686,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45708</v>
+        <v>44588</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 14543-2024</t>
+          <t>A 11101-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45394</v>
+        <v>44986</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 5068-2026</t>
+          <t>A 11177-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46049</v>
+        <v>44987</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3895,7 +3895,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 59266-2025</t>
+          <t>A 13245-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45988</v>
+        <v>45386</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.8</v>
+        <v>13</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3968,7 +3968,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 20170-2024</t>
+          <t>A 1592-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3982,10 +3982,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45434</v>
+        <v>45306</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4041,7 +4041,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 37907-2025</t>
+          <t>A 35587-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45880</v>
+        <v>45531</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4070,13 +4070,8 @@
           <t>SVALÖV</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>5.7</v>
+        <v>1.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4119,7 +4114,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 62403-2022</t>
+          <t>A 21814-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4133,10 +4128,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44923</v>
+        <v>45783</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4149,7 +4144,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4192,7 +4187,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 40470-2025</t>
+          <t>A 20170-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4202,14 +4197,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45895</v>
+        <v>45434</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4222,7 +4217,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4265,7 +4260,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 43294-2025</t>
+          <t>A 8924-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4279,10 +4274,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45910</v>
+        <v>44974</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4295,7 +4290,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.6</v>
+        <v>6.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4338,7 +4333,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 6365-2026</t>
+          <t>A 21541-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4352,10 +4347,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46051</v>
+        <v>45782</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4368,7 +4363,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4411,7 +4406,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 15157-2023</t>
+          <t>A 21556-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4425,10 +4420,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45016</v>
+        <v>45782</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4441,7 +4436,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4484,7 +4479,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 11491-2023</t>
+          <t>A 1901-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4498,10 +4493,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44991</v>
+        <v>45671</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4514,7 +4509,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4557,7 +4552,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 43466-2025</t>
+          <t>A 20047-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4571,10 +4566,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45911</v>
+        <v>45434</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4587,7 +4582,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4630,7 +4625,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 10209-2023</t>
+          <t>A 34808-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4644,10 +4639,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44986</v>
+        <v>45526</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4660,7 +4655,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4703,7 +4698,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 43004-2025</t>
+          <t>A 5167-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4717,10 +4712,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45909</v>
+        <v>45330</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4733,7 +4728,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.6</v>
+        <v>6.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4776,7 +4771,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 44107-2023</t>
+          <t>A 23747-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4790,10 +4785,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45188</v>
+        <v>45793</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4806,7 +4801,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4849,7 +4844,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 14533-2026</t>
+          <t>A 22794-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4863,10 +4858,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46100</v>
+        <v>45448</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4879,7 +4874,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4922,7 +4917,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 15747-2026</t>
+          <t>A 32620-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4936,10 +4931,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46107</v>
+        <v>45111</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4995,7 +4990,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 22262-2023</t>
+          <t>A 10209-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5009,10 +5004,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45070</v>
+        <v>44986</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5025,7 +5020,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5068,7 +5063,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 3430-2026</t>
+          <t>A 24513-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5082,10 +5077,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46042</v>
+        <v>45798</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5098,7 +5093,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>5.7</v>
+        <v>0.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5141,7 +5136,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 49032-2022</t>
+          <t>A 27310-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5155,10 +5150,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44860</v>
+        <v>45096</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5171,7 +5166,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5214,7 +5209,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 18926-2026</t>
+          <t>A 44196-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5228,10 +5223,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46127</v>
+        <v>45573</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5244,7 +5239,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5287,7 +5282,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 18121-2025</t>
+          <t>A 17731-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5297,14 +5292,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45761</v>
+        <v>45758</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5317,7 +5312,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5360,7 +5355,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 34810-2023</t>
+          <t>A 14543-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5374,10 +5369,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45141</v>
+        <v>45394</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5390,7 +5385,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5433,7 +5428,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 62201-2025</t>
+          <t>A 61620-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5447,10 +5442,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46006</v>
+        <v>44910</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5463,7 +5458,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>22.1</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5506,7 +5501,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 6335-2022</t>
+          <t>A 5190-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5520,10 +5515,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44600</v>
+        <v>45330</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5536,7 +5531,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5579,7 +5574,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 10196-2025</t>
+          <t>A 13273-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5593,10 +5588,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45719</v>
+        <v>45386</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5609,7 +5604,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>12.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5652,7 +5647,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 44112-2023</t>
+          <t>A 21774-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5666,10 +5661,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45188</v>
+        <v>45442</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5682,7 +5677,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5725,7 +5720,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 35911-2023</t>
+          <t>A 62403-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5739,10 +5734,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45148</v>
+        <v>44923</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5755,7 +5750,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5798,7 +5793,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 42588-2023</t>
+          <t>A 22262-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5812,10 +5807,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45176</v>
+        <v>45070</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5871,7 +5866,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 1901-2025</t>
+          <t>A 22792-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5885,10 +5880,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45671</v>
+        <v>45448</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5901,7 +5896,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5944,7 +5939,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 1920-2025</t>
+          <t>A 6335-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5958,10 +5953,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45671</v>
+        <v>44600</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5974,7 +5969,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6034,7 +6029,7 @@
         <v>45182</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6090,7 +6085,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 9716-2022</t>
+          <t>A 42588-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6104,10 +6099,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44617</v>
+        <v>45176</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6120,7 +6115,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6163,7 +6158,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 18438-2026</t>
+          <t>A 15157-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6177,10 +6172,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46127</v>
+        <v>45016</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6193,7 +6188,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6236,7 +6231,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 24286-2026</t>
+          <t>A 22063-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6250,10 +6245,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46169</v>
+        <v>45785</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6266,7 +6261,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6309,7 +6304,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 58970-2025</t>
+          <t>A 14546-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6323,10 +6318,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45987</v>
+        <v>45394</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6382,7 +6377,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 25522-2026</t>
+          <t>A 17980-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6396,10 +6391,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46177</v>
+        <v>45761</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6412,7 +6407,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>8.5</v>
+        <v>3.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6455,7 +6450,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 37354-2022</t>
+          <t>A 18121-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6469,10 +6464,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44806</v>
+        <v>45761</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6485,7 +6480,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6528,7 +6523,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 5190-2024</t>
+          <t>A 16215-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6542,10 +6537,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45330</v>
+        <v>44670</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6558,7 +6553,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6601,7 +6596,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 17731-2025</t>
+          <t>A 19282-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6615,10 +6610,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45758</v>
+        <v>45769</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6674,7 +6669,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 25832-2026</t>
+          <t>A 16667-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6688,10 +6683,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46178</v>
+        <v>45030</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6704,7 +6699,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>7.8</v>
+        <v>3.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6747,7 +6742,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 22792-2024</t>
+          <t>A 1920-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6761,10 +6756,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45448</v>
+        <v>45671</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6777,7 +6772,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6820,7 +6815,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 29337-2026</t>
+          <t>A 37907-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6834,10 +6829,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46202</v>
+        <v>45880</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6849,8 +6844,13 @@
           <t>SVALÖV</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>2</v>
+        <v>5.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6893,7 +6893,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 4964-2022</t>
+          <t>A 40470-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6903,14 +6903,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44593</v>
+        <v>45895</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6966,7 +6966,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 30535-2026</t>
+          <t>A 42706-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6980,10 +6980,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46210</v>
+        <v>45908</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 30202-2026</t>
+          <t>A 43425-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46206</v>
+        <v>45911</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7112,7 +7112,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 11177-2023</t>
+          <t>A 43294-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44987</v>
+        <v>45910</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7185,7 +7185,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 16215-2022</t>
+          <t>A 47139-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7199,10 +7199,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44670</v>
+        <v>45929</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7258,7 +7258,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 61620-2022</t>
+          <t>A 43466-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44910</v>
+        <v>45911</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7331,7 +7331,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 8924-2023</t>
+          <t>A 43004-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7345,10 +7345,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44974</v>
+        <v>45909</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>6.8</v>
+        <v>1.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7404,7 +7404,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 497-2023</t>
+          <t>A 5068-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7418,10 +7418,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44930</v>
+        <v>46049</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7477,7 +7477,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 11633-2024</t>
+          <t>A 59266-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7491,10 +7491,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45373</v>
+        <v>45988</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4.9</v>
+        <v>1.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7550,7 +7550,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 11922-2023</t>
+          <t>A 6365-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7564,10 +7564,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44993</v>
+        <v>46051</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7623,7 +7623,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 14546-2024</t>
+          <t>A 14533-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7637,10 +7637,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45394</v>
+        <v>46100</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7696,7 +7696,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 32620-2023</t>
+          <t>A 15747-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45111</v>
+        <v>46107</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 13791-2026</t>
+          <t>A 3430-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46097</v>
+        <v>46042</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>5.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7842,7 +7842,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 1592-2024</t>
+          <t>A 18926-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7856,10 +7856,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45306</v>
+        <v>46127</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7915,7 +7915,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 4149-2022</t>
+          <t>A 34810-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7925,14 +7925,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44588</v>
+        <v>45141</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.1</v>
+        <v>7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7988,7 +7988,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 13787-2026</t>
+          <t>A 62201-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8002,10 +8002,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46097</v>
+        <v>46006</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.7</v>
+        <v>22.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8061,7 +8061,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 15487-2025</t>
+          <t>A 18438-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8075,10 +8075,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45747</v>
+        <v>46127</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8134,7 +8134,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 27380-2026</t>
+          <t>A 24286-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46189</v>
+        <v>46169</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8207,7 +8207,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 11101-2023</t>
+          <t>A 58970-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8221,10 +8221,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44986</v>
+        <v>45987</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8280,7 +8280,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 5184-2024</t>
+          <t>A 25522-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8294,10 +8294,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45330</v>
+        <v>46177</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.2</v>
+        <v>8.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8353,7 +8353,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 13273-2024</t>
+          <t>A 29337-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8367,10 +8367,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45386</v>
+        <v>46202</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>12.4</v>
+        <v>2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 44196-2024</t>
+          <t>A 25832-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45573</v>
+        <v>46178</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.8</v>
+        <v>7.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8499,7 +8499,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 21556-2025</t>
+          <t>A 30202-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45782</v>
+        <v>46206</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8572,7 +8572,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 21541-2025</t>
+          <t>A 30535-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45782</v>
+        <v>46210</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8645,7 +8645,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 21814-2025</t>
+          <t>A 13791-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8659,10 +8659,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45783</v>
+        <v>46097</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8718,7 +8718,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 20047-2024</t>
+          <t>A 13787-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8732,10 +8732,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45434</v>
+        <v>46097</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8791,7 +8791,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 34808-2024</t>
+          <t>A 27380-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45526</v>
+        <v>46189</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8881,7 +8881,7 @@
         <v>45854</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>

--- a/Översikt SVALÖV.xlsx
+++ b/Översikt SVALÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45910</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>45401</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45884</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45645</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 1577-2024</t>
+          <t>A 15456-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45306</v>
+        <v>45401</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1151,20 +1151,20 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>21.2</v>
+        <v>2.5</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1191,42 +1191,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Lundticka</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15456-2024 artfynd.xlsx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15456-2024 karta.png", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15456-2024 georefererad karta.tif", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15456-2024 FSC-klagomål.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15456-2024 FSC-klagomål mail.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15456-2024 tillsynsbegäran.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15456-2024 tillsynsbegäran mail.docx", "A 15456-2024")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 15456-2024</t>
+          <t>A 8169-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45401</v>
+        <v>45351</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1265,10 +1265,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1283,7 +1283,7 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1296,42 +1296,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Lundticka</t>
+          <t>Mjukdån</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15456-2024 artfynd.xlsx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 8169-2024 artfynd.xlsx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15456-2024 karta.png", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 8169-2024 karta.png", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15456-2024 georefererad karta.tif", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 8169-2024 georefererad karta.tif", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15456-2024 FSC-klagomål.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 8169-2024 FSC-klagomål.docx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15456-2024 FSC-klagomål mail.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 8169-2024 FSC-klagomål mail.docx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15456-2024 tillsynsbegäran.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 8169-2024 tillsynsbegäran.docx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15456-2024 tillsynsbegäran mail.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 8169-2024 tillsynsbegäran mail.docx", "A 8169-2024")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 8169-2024</t>
+          <t>A 1577-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45351</v>
+        <v>45306</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1361,16 +1361,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>3.1</v>
+        <v>21.2</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1401,42 +1401,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Mjukdån</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 8169-2024 artfynd.xlsx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 8169-2024 karta.png", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 8169-2024 georefererad karta.tif", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 8169-2024 FSC-klagomål.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 8169-2024 FSC-klagomål mail.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 8169-2024 tillsynsbegäran.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 8169-2024 tillsynsbegäran mail.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 11170-2023</t>
+          <t>A 20125-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44987</v>
+        <v>45434</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>5.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1481,7 +1481,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1490,10 +1490,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1502,46 +1502,46 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Korndådra</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11170-2023 artfynd.xlsx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 20125-2024 artfynd.xlsx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11170-2023 karta.png", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 20125-2024 karta.png", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11170-2023 georefererad karta.tif", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 20125-2024 georefererad karta.tif", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11170-2023 FSC-klagomål.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 20125-2024 FSC-klagomål.docx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11170-2023 FSC-klagomål mail.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 20125-2024 FSC-klagomål mail.docx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11170-2023 tillsynsbegäran.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 20125-2024 tillsynsbegäran.docx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11170-2023 tillsynsbegäran mail.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 20125-2024 tillsynsbegäran mail.docx", "A 20125-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 20125-2024</t>
+          <t>A 11672-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45434</v>
+        <v>45373</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1571,17 +1571,17 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>5.7</v>
+        <v>13.9</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1607,39 +1607,39 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 20125-2024 artfynd.xlsx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11672-2024 artfynd.xlsx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 20125-2024 karta.png", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11672-2024 karta.png", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 20125-2024 georefererad karta.tif", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11672-2024 georefererad karta.tif", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 20125-2024 FSC-klagomål.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11672-2024 FSC-klagomål.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 20125-2024 FSC-klagomål mail.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11672-2024 FSC-klagomål mail.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 20125-2024 tillsynsbegäran.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11672-2024 tillsynsbegäran.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 20125-2024 tillsynsbegäran mail.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11672-2024 tillsynsbegäran mail.docx", "A 11672-2024")</f>
         <v/>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
         <v>45225</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 11672-2024</t>
+          <t>A 54127-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45373</v>
+        <v>45964</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>13.9</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1821,42 +1821,46 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11672-2024 artfynd.xlsx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 54127-2025 artfynd.xlsx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11672-2024 karta.png", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 54127-2025 karta.png", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11672-2024 georefererad karta.tif", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 54127-2025 georefererad karta.tif", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11672-2024 FSC-klagomål.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 54127-2025 FSC-klagomål.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11672-2024 FSC-klagomål mail.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 54127-2025 FSC-klagomål mail.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11672-2024 tillsynsbegäran.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 54127-2025 tillsynsbegäran.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11672-2024 tillsynsbegäran mail.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 54127-2025 tillsynsbegäran mail.docx", "A 54127-2025")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/fåglar/A 54127-2025 prioriterade fågelarter.docx", "A 54127-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 54127-2025</t>
+          <t>A 11170-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1870,10 +1874,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45964</v>
+        <v>44987</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1886,22 +1890,22 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
         <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1913,7 +1917,7 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1926,39 +1930,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Korndådra</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 54127-2025 artfynd.xlsx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11170-2023 artfynd.xlsx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 54127-2025 karta.png", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11170-2023 karta.png", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 54127-2025 georefererad karta.tif", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11170-2023 georefererad karta.tif", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 54127-2025 FSC-klagomål.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11170-2023 FSC-klagomål.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 54127-2025 FSC-klagomål mail.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11170-2023 FSC-klagomål mail.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 54127-2025 tillsynsbegäran.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11170-2023 tillsynsbegäran.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 54127-2025 tillsynsbegäran mail.docx", "A 54127-2025")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/fåglar/A 54127-2025 prioriterade fågelarter.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11170-2023 tillsynsbegäran mail.docx", "A 11170-2023")</f>
         <v/>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         <v>45218</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>44763</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44598</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44483</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44847</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 42617-2022</t>
+          <t>A 61495-2021</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2372,14 +2372,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44831</v>
+        <v>44501</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2435,7 +2435,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 47717-2022</t>
+          <t>A 42617-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44854</v>
+        <v>44831</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 61495-2021</t>
+          <t>A 47717-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2518,14 +2518,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44501</v>
+        <v>44854</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2581,7 +2581,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 8332-2025</t>
+          <t>A 13245-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2595,10 +2595,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45708</v>
+        <v>45386</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.5</v>
+        <v>13</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 44112-2023</t>
+          <t>A 5167-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45188</v>
+        <v>45330</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.5</v>
+        <v>6.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 15487-2025</t>
+          <t>A 21774-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45747</v>
+        <v>45442</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2800,7 +2800,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 4964-2022</t>
+          <t>A 23747-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2814,10 +2814,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44593</v>
+        <v>45793</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 37354-2022</t>
+          <t>A 22794-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44806</v>
+        <v>45448</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 49032-2022</t>
+          <t>A 5068-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44860</v>
+        <v>46049</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3019,7 +3019,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 11491-2023</t>
+          <t>A 35587-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44991</v>
+        <v>45531</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3092,7 +3092,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 497-2023</t>
+          <t>A 59266-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3106,10 +3106,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44930</v>
+        <v>45988</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3165,7 +3165,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 11922-2023</t>
+          <t>A 42706-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44993</v>
+        <v>45908</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3238,7 +3238,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 5184-2024</t>
+          <t>A 24513-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45330</v>
+        <v>45798</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3311,7 +3311,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 44107-2023</t>
+          <t>A 43425-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45188</v>
+        <v>45911</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3384,7 +3384,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 35911-2023</t>
+          <t>A 6365-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45148</v>
+        <v>46051</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10196-2025</t>
+          <t>A 27310-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45719</v>
+        <v>45096</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 11633-2024</t>
+          <t>A 47139-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45373</v>
+        <v>45929</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.9</v>
+        <v>1.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3603,7 +3603,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 9716-2022</t>
+          <t>A 16667-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44617</v>
+        <v>45030</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3676,7 +3676,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 4149-2022</t>
+          <t>A 8332-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3686,14 +3686,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44588</v>
+        <v>45708</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 11101-2023</t>
+          <t>A 14533-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44986</v>
+        <v>46100</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 11177-2023</t>
+          <t>A 14543-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44987</v>
+        <v>45394</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3895,7 +3895,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 13245-2024</t>
+          <t>A 15747-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45386</v>
+        <v>46107</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>13</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3968,7 +3968,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 1592-2024</t>
+          <t>A 43294-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3982,10 +3982,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45306</v>
+        <v>45910</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4041,7 +4041,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 35587-2024</t>
+          <t>A 3430-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45531</v>
+        <v>46042</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.6</v>
+        <v>5.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 21814-2025</t>
+          <t>A 20170-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45783</v>
+        <v>45434</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4187,7 +4187,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 20170-2024</t>
+          <t>A 62403-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4201,10 +4201,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45434</v>
+        <v>44923</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4260,7 +4260,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 8924-2023</t>
+          <t>A 18926-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4274,10 +4274,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44974</v>
+        <v>46127</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>6.8</v>
+        <v>1.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4333,7 +4333,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 21541-2025</t>
+          <t>A 15157-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4347,10 +4347,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45782</v>
+        <v>45016</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4406,7 +4406,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 21556-2025</t>
+          <t>A 11491-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45782</v>
+        <v>44991</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4479,7 +4479,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 1901-2025</t>
+          <t>A 34810-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4493,10 +4493,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45671</v>
+        <v>45141</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4552,7 +4552,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 20047-2024</t>
+          <t>A 43466-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4566,10 +4566,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45434</v>
+        <v>45911</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4625,7 +4625,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 34808-2024</t>
+          <t>A 43004-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45526</v>
+        <v>45909</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4698,7 +4698,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 5167-2024</t>
+          <t>A 10209-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45330</v>
+        <v>44986</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>6.5</v>
+        <v>1.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4771,7 +4771,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 23747-2025</t>
+          <t>A 62201-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4785,10 +4785,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45793</v>
+        <v>46006</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.6</v>
+        <v>22.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4844,7 +4844,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 22794-2024</t>
+          <t>A 44107-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4858,10 +4858,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45448</v>
+        <v>45188</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4917,7 +4917,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 32620-2023</t>
+          <t>A 22063-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4931,10 +4931,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45111</v>
+        <v>45785</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4990,7 +4990,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 10209-2023</t>
+          <t>A 17980-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5004,10 +5004,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44986</v>
+        <v>45761</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5063,7 +5063,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 24513-2025</t>
+          <t>A 19282-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5073,14 +5073,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45798</v>
+        <v>45769</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5136,7 +5136,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 27310-2023</t>
+          <t>A 22262-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5150,10 +5150,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45096</v>
+        <v>45070</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5209,7 +5209,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 44196-2024</t>
+          <t>A 37907-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45573</v>
+        <v>45880</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5238,8 +5238,13 @@
           <t>SVALÖV</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>1.8</v>
+        <v>5.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5282,7 +5287,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 17731-2025</t>
+          <t>A 40470-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5296,10 +5301,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45758</v>
+        <v>45895</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5312,7 +5317,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5355,7 +5360,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 14543-2024</t>
+          <t>A 49032-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5369,10 +5374,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45394</v>
+        <v>44860</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5385,7 +5390,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5428,7 +5433,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 61620-2022</t>
+          <t>A 18121-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5442,10 +5447,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44910</v>
+        <v>45761</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5458,7 +5463,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5501,7 +5506,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 5190-2024</t>
+          <t>A 18438-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5515,10 +5520,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45330</v>
+        <v>46127</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5531,7 +5536,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5574,7 +5579,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 13273-2024</t>
+          <t>A 24286-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5588,10 +5593,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45386</v>
+        <v>46169</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5604,7 +5609,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>12.4</v>
+        <v>0.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5647,7 +5652,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 21774-2024</t>
+          <t>A 58970-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5661,10 +5666,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45442</v>
+        <v>45987</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5677,7 +5682,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5720,7 +5725,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 62403-2022</t>
+          <t>A 6335-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5734,10 +5739,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44923</v>
+        <v>44600</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5750,7 +5755,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5793,7 +5798,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 22262-2023</t>
+          <t>A 25522-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5807,10 +5812,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45070</v>
+        <v>46177</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5823,7 +5828,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.1</v>
+        <v>8.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5866,7 +5871,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 22792-2024</t>
+          <t>A 10196-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5880,10 +5885,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45448</v>
+        <v>45719</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5939,7 +5944,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 6335-2022</t>
+          <t>A 44112-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5953,10 +5958,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44600</v>
+        <v>45188</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5969,7 +5974,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6012,7 +6017,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 43736-2023</t>
+          <t>A 35911-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6026,10 +6031,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45182</v>
+        <v>45148</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6042,7 +6047,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6102,7 +6107,7 @@
         <v>45176</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6158,7 +6163,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 15157-2023</t>
+          <t>A 1901-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6172,10 +6177,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45016</v>
+        <v>45671</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6188,7 +6193,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6231,7 +6236,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 22063-2025</t>
+          <t>A 1920-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6245,10 +6250,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45785</v>
+        <v>45671</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6261,7 +6266,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6304,7 +6309,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 14546-2024</t>
+          <t>A 43736-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6318,10 +6323,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45394</v>
+        <v>45182</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6334,7 +6339,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6377,7 +6382,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 17980-2025</t>
+          <t>A 9716-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6391,10 +6396,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45761</v>
+        <v>44617</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6407,7 +6412,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6450,7 +6455,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 18121-2025</t>
+          <t>A 25832-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6464,10 +6469,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45761</v>
+        <v>46178</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6480,7 +6485,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.7</v>
+        <v>7.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6523,7 +6528,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 16215-2022</t>
+          <t>A 29337-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6537,10 +6542,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44670</v>
+        <v>46202</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6553,7 +6558,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6596,7 +6601,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 19282-2025</t>
+          <t>A 30535-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6606,14 +6611,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45769</v>
+        <v>46210</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6669,7 +6674,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 16667-2023</t>
+          <t>A 30202-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6683,10 +6688,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45030</v>
+        <v>46206</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6699,7 +6704,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6742,7 +6747,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 1920-2025</t>
+          <t>A 37354-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6756,10 +6761,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45671</v>
+        <v>44806</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6772,7 +6777,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6815,7 +6820,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 37907-2025</t>
+          <t>A 5190-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6829,10 +6834,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45880</v>
+        <v>45330</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6844,13 +6849,8 @@
           <t>SVALÖV</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>5.7</v>
+        <v>2.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6893,7 +6893,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 40470-2025</t>
+          <t>A 17731-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45895</v>
+        <v>45758</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6966,7 +6966,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 42706-2025</t>
+          <t>A 22792-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6980,10 +6980,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45908</v>
+        <v>45448</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 43425-2025</t>
+          <t>A 4964-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45911</v>
+        <v>44593</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7112,7 +7112,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 43294-2025</t>
+          <t>A 11177-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45910</v>
+        <v>44987</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7185,7 +7185,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 47139-2025</t>
+          <t>A 13791-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7199,10 +7199,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45929</v>
+        <v>46097</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7258,7 +7258,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 43466-2025</t>
+          <t>A 16215-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45911</v>
+        <v>44670</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7331,7 +7331,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 43004-2025</t>
+          <t>A 61620-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7345,10 +7345,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45909</v>
+        <v>44910</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7404,7 +7404,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 5068-2026</t>
+          <t>A 13787-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7418,10 +7418,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46049</v>
+        <v>46097</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7477,7 +7477,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 59266-2025</t>
+          <t>A 27380-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7491,10 +7491,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45988</v>
+        <v>46189</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7550,7 +7550,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 6365-2026</t>
+          <t>A 8924-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7564,10 +7564,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46051</v>
+        <v>44974</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.9</v>
+        <v>6.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7623,7 +7623,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 14533-2026</t>
+          <t>A 497-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7637,10 +7637,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46100</v>
+        <v>44930</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7696,7 +7696,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 15747-2026</t>
+          <t>A 11633-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46107</v>
+        <v>45373</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.4</v>
+        <v>4.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7769,7 +7769,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 3430-2026</t>
+          <t>A 11922-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46042</v>
+        <v>44993</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>5.7</v>
+        <v>0.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7842,7 +7842,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 18926-2026</t>
+          <t>A 14546-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7856,10 +7856,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46127</v>
+        <v>45394</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7915,7 +7915,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 34810-2023</t>
+          <t>A 32620-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7929,10 +7929,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45141</v>
+        <v>45111</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>7</v>
+        <v>1.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7988,7 +7988,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 62201-2025</t>
+          <t>A 1592-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8002,10 +8002,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46006</v>
+        <v>45306</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>22.1</v>
+        <v>2.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8061,7 +8061,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 18438-2026</t>
+          <t>A 4149-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8071,14 +8071,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46127</v>
+        <v>44588</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8134,7 +8134,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 24286-2026</t>
+          <t>A 15487-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46169</v>
+        <v>45747</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 58970-2025</t>
+          <t>A 11101-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8221,10 +8221,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45987</v>
+        <v>44986</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8280,7 +8280,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 25522-2026</t>
+          <t>A 5184-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8294,10 +8294,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46177</v>
+        <v>45330</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>8.5</v>
+        <v>2.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8353,7 +8353,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 29337-2026</t>
+          <t>A 13273-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8367,10 +8367,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46202</v>
+        <v>45386</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2</v>
+        <v>12.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 25832-2026</t>
+          <t>A 44196-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46178</v>
+        <v>45573</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>7.8</v>
+        <v>1.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8499,7 +8499,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 30202-2026</t>
+          <t>A 21556-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46206</v>
+        <v>45782</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8572,7 +8572,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 30535-2026</t>
+          <t>A 21541-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46210</v>
+        <v>45782</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8645,7 +8645,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 13791-2026</t>
+          <t>A 21814-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8659,10 +8659,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46097</v>
+        <v>45783</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8718,7 +8718,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 13787-2026</t>
+          <t>A 20047-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8732,10 +8732,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46097</v>
+        <v>45434</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8791,7 +8791,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 27380-2026</t>
+          <t>A 34808-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46189</v>
+        <v>45526</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8881,7 +8881,7 @@
         <v>45854</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>

--- a/Översikt SVALÖV.xlsx
+++ b/Översikt SVALÖV.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE109"/>
+  <dimension ref="A1:AE112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45910</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 15475-2024</t>
+          <t>A 38522-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45401</v>
+        <v>45884</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.7</v>
+        <v>2.6</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -848,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -857,10 +857,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -869,146 +869,146 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Skogsknipprot
+Stor häxört</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 38522-2025 artfynd.xlsx", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 38522-2025 karta.png", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 38522-2025 georefererad karta.tif", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 38522-2025 FSC-klagomål.docx", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 38522-2025 FSC-klagomål mail.docx", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 38522-2025 tillsynsbegäran.docx", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 38522-2025 tillsynsbegäran mail.docx", "A 38522-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 15475-2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45401</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SVALÖV</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>1</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Ask
 Strutbräken</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15475-2024 artfynd.xlsx", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15475-2024 karta.png", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15475-2024 georefererad karta.tif", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15475-2024 FSC-klagomål.docx", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15475-2024 FSC-klagomål mail.docx", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15475-2024 tillsynsbegäran.docx", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15475-2024 tillsynsbegäran mail.docx", "A 15475-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 38522-2025</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45884</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SVALÖV</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Skogsknipprot
-Stor häxört</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 38522-2025 artfynd.xlsx", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 38522-2025 karta.png", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 38522-2025 georefererad karta.tif", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 38522-2025 FSC-klagomål.docx", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 38522-2025 FSC-klagomål mail.docx", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 38522-2025 tillsynsbegäran.docx", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 38522-2025 tillsynsbegäran mail.docx", "A 38522-2025")</f>
         <v/>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
         <v>45645</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 15456-2024</t>
+          <t>A 11170-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45401</v>
+        <v>44987</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1187,39 +1187,39 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Lundticka</t>
+          <t>Korndådra</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15456-2024 artfynd.xlsx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11170-2023 artfynd.xlsx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15456-2024 karta.png", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11170-2023 karta.png", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15456-2024 georefererad karta.tif", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11170-2023 georefererad karta.tif", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15456-2024 FSC-klagomål.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11170-2023 FSC-klagomål.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15456-2024 FSC-klagomål mail.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11170-2023 FSC-klagomål mail.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15456-2024 tillsynsbegäran.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11170-2023 tillsynsbegäran.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15456-2024 tillsynsbegäran mail.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11170-2023 tillsynsbegäran mail.docx", "A 11170-2023")</f>
         <v/>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
         <v>45351</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 1577-2024</t>
+          <t>A 15456-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45306</v>
+        <v>45401</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1361,20 +1361,20 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>21.2</v>
+        <v>2.5</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
@@ -1385,10 +1385,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1401,42 +1401,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Lundticka</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15456-2024 artfynd.xlsx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15456-2024 karta.png", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15456-2024 georefererad karta.tif", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15456-2024 FSC-klagomål.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15456-2024 FSC-klagomål mail.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15456-2024 tillsynsbegäran.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15456-2024 tillsynsbegäran mail.docx", "A 15456-2024")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 20125-2024</t>
+          <t>A 54127-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45434</v>
+        <v>45964</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1466,17 +1466,17 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5.7</v>
+        <v>1.3</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
@@ -1490,7 +1490,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1502,46 +1502,50 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 20125-2024 artfynd.xlsx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 54127-2025 artfynd.xlsx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 20125-2024 karta.png", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 54127-2025 karta.png", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 20125-2024 georefererad karta.tif", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 54127-2025 georefererad karta.tif", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 20125-2024 FSC-klagomål.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 54127-2025 FSC-klagomål.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 20125-2024 FSC-klagomål mail.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 54127-2025 FSC-klagomål mail.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 20125-2024 tillsynsbegäran.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 54127-2025 tillsynsbegäran.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 20125-2024 tillsynsbegäran mail.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 54127-2025 tillsynsbegäran mail.docx", "A 54127-2025")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/fåglar/A 54127-2025 prioriterade fågelarter.docx", "A 54127-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 11672-2024</t>
+          <t>A 20125-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1555,10 +1559,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45373</v>
+        <v>45434</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1571,16 +1575,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>13.9</v>
+        <v>5.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1595,7 +1599,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1607,39 +1611,39 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11672-2024 artfynd.xlsx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 20125-2024 artfynd.xlsx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11672-2024 karta.png", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 20125-2024 karta.png", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11672-2024 georefererad karta.tif", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 20125-2024 georefererad karta.tif", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11672-2024 FSC-klagomål.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 20125-2024 FSC-klagomål.docx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11672-2024 FSC-klagomål mail.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 20125-2024 FSC-klagomål mail.docx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11672-2024 tillsynsbegäran.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 20125-2024 tillsynsbegäran.docx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11672-2024 tillsynsbegäran mail.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 20125-2024 tillsynsbegäran mail.docx", "A 20125-2024")</f>
         <v/>
       </c>
     </row>
@@ -1663,7 +1667,7 @@
         <v>45225</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1751,7 +1755,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 54127-2025</t>
+          <t>A 11672-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1765,10 +1769,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45964</v>
+        <v>45373</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1781,10 +1785,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>13.9</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1821,46 +1825,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 54127-2025 artfynd.xlsx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11672-2024 artfynd.xlsx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 54127-2025 karta.png", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11672-2024 karta.png", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 54127-2025 georefererad karta.tif", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11672-2024 georefererad karta.tif", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 54127-2025 FSC-klagomål.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11672-2024 FSC-klagomål.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 54127-2025 FSC-klagomål mail.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11672-2024 FSC-klagomål mail.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 54127-2025 tillsynsbegäran.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11672-2024 tillsynsbegäran.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 54127-2025 tillsynsbegäran mail.docx", "A 54127-2025")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/fåglar/A 54127-2025 prioriterade fågelarter.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11672-2024 tillsynsbegäran mail.docx", "A 11672-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 11170-2023</t>
+          <t>A 1577-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44987</v>
+        <v>45306</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.9</v>
+        <v>21.2</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1905,7 +1905,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1914,10 +1914,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1926,39 +1926,39 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Korndådra</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11170-2023 artfynd.xlsx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11170-2023 karta.png", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11170-2023 georefererad karta.tif", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11170-2023 FSC-klagomål.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11170-2023 FSC-klagomål mail.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11170-2023 tillsynsbegäran.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11170-2023 tillsynsbegäran mail.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         <v>45218</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>44763</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44598</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44483</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44847</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44501</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>44831</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>44854</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 13245-2024</t>
+          <t>A 49032-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2595,10 +2595,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45386</v>
+        <v>44860</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>13</v>
+        <v>3.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 5167-2024</t>
+          <t>A 35911-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45330</v>
+        <v>45148</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>6.5</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 21774-2024</t>
+          <t>A 9716-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45442</v>
+        <v>44617</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2800,7 +2800,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 23747-2025</t>
+          <t>A 11101-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2814,10 +2814,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45793</v>
+        <v>44986</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 22794-2024</t>
+          <t>A 11177-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45448</v>
+        <v>44987</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 5068-2026</t>
+          <t>A 20047-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46049</v>
+        <v>45434</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3019,7 +3019,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 35587-2024</t>
+          <t>A 1592-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45531</v>
+        <v>45306</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3092,7 +3092,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 59266-2025</t>
+          <t>A 34808-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3106,10 +3106,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45988</v>
+        <v>45526</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3165,7 +3165,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 42706-2025</t>
+          <t>A 5167-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45908</v>
+        <v>45330</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>6.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3238,7 +3238,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 24513-2025</t>
+          <t>A 10209-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45798</v>
+        <v>44986</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3311,7 +3311,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 43425-2025</t>
+          <t>A 23747-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45911</v>
+        <v>45793</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3384,7 +3384,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 6365-2026</t>
+          <t>A 42706-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46051</v>
+        <v>45908</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 27310-2023</t>
+          <t>A 43425-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45096</v>
+        <v>45911</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 47139-2025</t>
+          <t>A 24513-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45929</v>
+        <v>45798</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3603,7 +3603,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 16667-2023</t>
+          <t>A 5068-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45030</v>
+        <v>46049</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3676,7 +3676,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 8332-2025</t>
+          <t>A 27310-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45708</v>
+        <v>45096</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 14533-2026</t>
+          <t>A 59266-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46100</v>
+        <v>45988</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 14543-2024</t>
+          <t>A 22262-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45394</v>
+        <v>45070</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3895,7 +3895,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 15747-2026</t>
+          <t>A 6335-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46107</v>
+        <v>44600</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3968,7 +3968,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 43294-2025</t>
+          <t>A 47139-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3982,10 +3982,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45910</v>
+        <v>45929</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4041,7 +4041,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 3430-2026</t>
+          <t>A 6365-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46042</v>
+        <v>46051</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.7</v>
+        <v>2.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 20170-2024</t>
+          <t>A 16667-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45434</v>
+        <v>45030</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4187,7 +4187,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 62403-2022</t>
+          <t>A 1920-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4201,10 +4201,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44923</v>
+        <v>45671</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4260,7 +4260,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 18926-2026</t>
+          <t>A 8332-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4274,10 +4274,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46127</v>
+        <v>45708</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4333,7 +4333,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 15157-2023</t>
+          <t>A 44112-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4347,10 +4347,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45016</v>
+        <v>45188</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4406,7 +4406,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 11491-2023</t>
+          <t>A 43294-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44991</v>
+        <v>45910</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4479,7 +4479,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 34810-2023</t>
+          <t>A 11491-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4493,10 +4493,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45141</v>
+        <v>44991</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>7</v>
+        <v>2.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4552,7 +4552,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 43466-2025</t>
+          <t>A 14533-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4566,10 +4566,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45911</v>
+        <v>46100</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4625,7 +4625,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 43004-2025</t>
+          <t>A 11922-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45909</v>
+        <v>44993</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4698,7 +4698,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 10209-2023</t>
+          <t>A 15747-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44986</v>
+        <v>46107</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4771,7 +4771,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 62201-2025</t>
+          <t>A 3430-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4785,10 +4785,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46006</v>
+        <v>46042</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>22.1</v>
+        <v>5.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4844,7 +4844,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 44107-2023</t>
+          <t>A 43466-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4858,10 +4858,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45188</v>
+        <v>45911</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4917,7 +4917,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 22063-2025</t>
+          <t>A 43004-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4931,10 +4931,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45785</v>
+        <v>45909</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4990,7 +4990,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 17980-2025</t>
+          <t>A 22063-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5004,10 +5004,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45761</v>
+        <v>45785</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5063,7 +5063,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 19282-2025</t>
+          <t>A 17980-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5073,14 +5073,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45769</v>
+        <v>45761</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5136,7 +5136,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 22262-2023</t>
+          <t>A 34810-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5150,10 +5150,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45070</v>
+        <v>45141</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5209,7 +5209,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 37907-2025</t>
+          <t>A 35587-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45880</v>
+        <v>45531</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5238,13 +5238,8 @@
           <t>SVALÖV</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>5.7</v>
+        <v>1.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5287,7 +5282,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 40470-2025</t>
+          <t>A 19282-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5301,10 +5296,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45895</v>
+        <v>45769</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5317,7 +5312,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5360,7 +5355,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 49032-2022</t>
+          <t>A 8924-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5374,10 +5369,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44860</v>
+        <v>44974</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5390,7 +5385,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.7</v>
+        <v>6.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5433,7 +5428,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 18121-2025</t>
+          <t>A 62201-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5447,10 +5442,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45761</v>
+        <v>46006</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5463,7 +5458,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.7</v>
+        <v>22.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5506,7 +5501,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 18438-2026</t>
+          <t>A 1901-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5520,10 +5515,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46127</v>
+        <v>45671</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5536,7 +5531,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5579,7 +5574,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 24286-2026</t>
+          <t>A 22794-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5593,10 +5588,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46169</v>
+        <v>45448</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5609,7 +5604,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5652,7 +5647,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 58970-2025</t>
+          <t>A 32620-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5666,10 +5661,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45987</v>
+        <v>45111</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5682,7 +5677,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5725,7 +5720,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 6335-2022</t>
+          <t>A 44196-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5739,10 +5734,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44600</v>
+        <v>45573</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5755,7 +5750,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5798,7 +5793,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 25522-2026</t>
+          <t>A 17731-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5808,14 +5803,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46177</v>
+        <v>45758</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5828,7 +5823,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>8.5</v>
+        <v>0.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5871,7 +5866,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 10196-2025</t>
+          <t>A 14543-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5885,10 +5880,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45719</v>
+        <v>45394</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5901,7 +5896,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5944,7 +5939,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 44112-2023</t>
+          <t>A 13273-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5958,10 +5953,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45188</v>
+        <v>45386</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5974,7 +5969,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.5</v>
+        <v>12.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6017,7 +6012,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 35911-2023</t>
+          <t>A 22792-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6031,10 +6026,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45148</v>
+        <v>45448</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6047,7 +6042,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6090,7 +6085,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 42588-2023</t>
+          <t>A 14546-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6104,10 +6099,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45176</v>
+        <v>45394</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6120,7 +6115,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6163,7 +6158,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 1901-2025</t>
+          <t>A 18438-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6177,10 +6172,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45671</v>
+        <v>46127</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6193,7 +6188,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6236,7 +6231,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 1920-2025</t>
+          <t>A 18121-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6250,10 +6245,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45671</v>
+        <v>45761</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6266,7 +6261,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6309,7 +6304,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 43736-2023</t>
+          <t>A 16215-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6323,10 +6318,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45182</v>
+        <v>44670</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6339,7 +6334,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6382,7 +6377,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 9716-2022</t>
+          <t>A 24286-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6396,10 +6391,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44617</v>
+        <v>46169</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6412,7 +6407,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6455,7 +6450,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 25832-2026</t>
+          <t>A 37907-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6469,10 +6464,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46178</v>
+        <v>45880</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6484,8 +6479,13 @@
           <t>SVALÖV</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>7.8</v>
+        <v>5.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6528,7 +6528,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 29337-2026</t>
+          <t>A 40470-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6538,14 +6538,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46202</v>
+        <v>45895</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6601,7 +6601,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 30535-2026</t>
+          <t>A 58970-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46210</v>
+        <v>45987</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6674,7 +6674,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 30202-2026</t>
+          <t>A 25522-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6688,10 +6688,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46206</v>
+        <v>46177</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6747,7 +6747,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 37354-2022</t>
+          <t>A 15487-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6761,10 +6761,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44806</v>
+        <v>45747</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6820,7 +6820,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 5190-2024</t>
+          <t>A 4964-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6834,10 +6834,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45330</v>
+        <v>44593</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6893,7 +6893,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 17731-2025</t>
+          <t>A 37354-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6903,14 +6903,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45758</v>
+        <v>44806</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6966,7 +6966,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 22792-2024</t>
+          <t>A 29337-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6980,10 +6980,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45448</v>
+        <v>46202</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 4964-2022</t>
+          <t>A 25832-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44593</v>
+        <v>46178</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.5</v>
+        <v>7.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7112,7 +7112,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 11177-2023</t>
+          <t>A 30202-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44987</v>
+        <v>46206</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7185,7 +7185,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 13791-2026</t>
+          <t>A 30535-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7199,10 +7199,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46097</v>
+        <v>46210</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7258,7 +7258,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 16215-2022</t>
+          <t>A 11633-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44670</v>
+        <v>45373</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.9</v>
+        <v>4.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7331,7 +7331,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 61620-2022</t>
+          <t>A 20170-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7345,10 +7345,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44910</v>
+        <v>45434</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7404,7 +7404,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 13787-2026</t>
+          <t>A 13791-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7421,7 +7421,7 @@
         <v>46097</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7477,7 +7477,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 27380-2026</t>
+          <t>A 13787-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7491,10 +7491,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46189</v>
+        <v>46097</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7550,7 +7550,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 8924-2023</t>
+          <t>A 27380-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7564,10 +7564,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44974</v>
+        <v>46189</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>6.8</v>
+        <v>1.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7623,7 +7623,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 497-2023</t>
+          <t>A 61620-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7637,10 +7637,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44930</v>
+        <v>44910</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7696,7 +7696,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 11633-2024</t>
+          <t>A 5190-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45373</v>
+        <v>45330</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4.9</v>
+        <v>2.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7769,7 +7769,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 11922-2023</t>
+          <t>A 21774-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44993</v>
+        <v>45442</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7842,7 +7842,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 14546-2024</t>
+          <t>A 62403-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7856,10 +7856,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45394</v>
+        <v>44923</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7915,7 +7915,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 32620-2023</t>
+          <t>A 43736-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7929,10 +7929,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45111</v>
+        <v>45182</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7988,7 +7988,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 1592-2024</t>
+          <t>A 42588-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8002,10 +8002,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45306</v>
+        <v>45176</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8061,7 +8061,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 4149-2022</t>
+          <t>A 15157-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8071,14 +8071,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44588</v>
+        <v>45016</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8134,7 +8134,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 15487-2025</t>
+          <t>A 40917-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45747</v>
+        <v>46297</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.9</v>
+        <v>8.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8207,7 +8207,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 11101-2023</t>
+          <t>A 40895-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8221,10 +8221,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44986</v>
+        <v>46297</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8280,7 +8280,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 5184-2024</t>
+          <t>A 40882-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8294,10 +8294,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45330</v>
+        <v>46297</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8353,7 +8353,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 13273-2024</t>
+          <t>A 40910-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8367,10 +8367,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45386</v>
+        <v>46297</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>12.4</v>
+        <v>3.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 44196-2024</t>
+          <t>A 497-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45573</v>
+        <v>44930</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8499,7 +8499,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 21556-2025</t>
+          <t>A 5184-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45782</v>
+        <v>45330</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8572,7 +8572,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 21541-2025</t>
+          <t>A 44107-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45782</v>
+        <v>45188</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8645,7 +8645,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 21814-2025</t>
+          <t>A 10196-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8659,10 +8659,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45783</v>
+        <v>45719</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8718,7 +8718,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 20047-2024</t>
+          <t>A 4149-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8728,14 +8728,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45434</v>
+        <v>44588</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8791,7 +8791,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 34808-2024</t>
+          <t>A 13245-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45526</v>
+        <v>45386</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.6</v>
+        <v>13</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8861,78 +8861,297 @@
       </c>
       <c r="V108" s="2" t="inlineStr"/>
     </row>
-    <row r="109">
+    <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
+          <t>A 21814-2025</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D109" s="1" t="n">
+        <v>45783</v>
+      </c>
+      <c r="E109" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>SVALÖV</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" t="n">
+        <v>0</v>
+      </c>
+      <c r="T109" t="n">
+        <v>0</v>
+      </c>
+      <c r="U109" t="n">
+        <v>0</v>
+      </c>
+      <c r="V109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110" ht="15" customHeight="1">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>A 21541-2025</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D110" s="1" t="n">
+        <v>45782</v>
+      </c>
+      <c r="E110" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>SVALÖV</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" t="n">
+        <v>0</v>
+      </c>
+      <c r="T110" t="n">
+        <v>0</v>
+      </c>
+      <c r="U110" t="n">
+        <v>0</v>
+      </c>
+      <c r="V110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111" ht="15" customHeight="1">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>A 21556-2025</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D111" s="1" t="n">
+        <v>45782</v>
+      </c>
+      <c r="E111" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>SVALÖV</t>
+        </is>
+      </c>
+      <c r="I111" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>0</v>
+      </c>
+      <c r="R111" t="n">
+        <v>0</v>
+      </c>
+      <c r="S111" t="n">
+        <v>0</v>
+      </c>
+      <c r="T111" t="n">
+        <v>0</v>
+      </c>
+      <c r="U111" t="n">
+        <v>0</v>
+      </c>
+      <c r="V111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
           <t>S 2185-2025</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B112" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C112" t="inlineStr">
         <is>
           <t>Skogsbilväg</t>
         </is>
       </c>
-      <c r="D109" s="1" t="n">
+      <c r="D112" s="1" t="n">
         <v>45854</v>
       </c>
-      <c r="E109" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>SVALÖV</t>
-        </is>
-      </c>
-      <c r="I109" t="n">
+      <c r="E112" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>SVALÖV</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
         <v>0.1</v>
       </c>
-      <c r="J109" t="n">
-        <v>0</v>
-      </c>
-      <c r="K109" t="n">
-        <v>0</v>
-      </c>
-      <c r="L109" t="n">
-        <v>0</v>
-      </c>
-      <c r="M109" t="n">
-        <v>0</v>
-      </c>
-      <c r="N109" t="n">
-        <v>0</v>
-      </c>
-      <c r="O109" t="n">
-        <v>0</v>
-      </c>
-      <c r="P109" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
-      <c r="R109" t="n">
-        <v>0</v>
-      </c>
-      <c r="S109" t="n">
-        <v>0</v>
-      </c>
-      <c r="T109" t="n">
-        <v>0</v>
-      </c>
-      <c r="U109" t="n">
-        <v>0</v>
-      </c>
-      <c r="V109" s="2" t="inlineStr"/>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0</v>
+      </c>
+      <c r="N112" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>0</v>
+      </c>
+      <c r="R112" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" t="n">
+        <v>0</v>
+      </c>
+      <c r="T112" t="n">
+        <v>0</v>
+      </c>
+      <c r="U112" t="n">
+        <v>0</v>
+      </c>
+      <c r="V112" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt SVALÖV.xlsx
+++ b/Översikt SVALÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45910</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>45884</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45401</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45645</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>44987</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>45351</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>45401</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>45964</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>45434</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>45225</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>45373</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>45306</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>45218</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>44763</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44598</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44483</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44847</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44501</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>44831</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>44854</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>44860</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>45148</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>44617</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>44986</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>44987</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>45434</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>45306</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>45526</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45330</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>44986</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>45793</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>45908</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>45911</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>45798</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>46049</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>45096</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>45988</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>45070</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>44600</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>45929</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>46051</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>45030</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>45671</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>45708</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>45188</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>45910</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>44991</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>46100</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>44993</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>46107</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>46042</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>45911</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>45909</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>45785</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>45761</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>45141</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>45531</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         <v>45769</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         <v>44974</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>46006</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>45671</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>45448</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>45111</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>45573</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         <v>45758</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>45394</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>45386</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>45448</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>45394</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>46127</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>45761</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>44670</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>46169</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>45880</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>45895</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>45987</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>46177</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>45747</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>44593</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>44806</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>46202</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>46178</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         <v>46206</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>46210</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>45373</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         <v>45434</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>46097</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>46097</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>46189</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>44910</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         <v>45330</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         <v>45442</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>44923</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         <v>45182</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>45176</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>45016</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>46297</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         <v>46297</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>46297</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>46297</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>44930</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>45330</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8589,7 +8589,7 @@
         <v>45188</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>45719</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>44588</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>45386</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>45783</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>45782</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         <v>45782</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>45854</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>

--- a/Översikt SVALÖV.xlsx
+++ b/Översikt SVALÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45910</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>45884</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45401</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45645</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>44987</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>45351</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>45401</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>45964</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>45434</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>45225</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>45373</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>45306</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>45218</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>44763</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44598</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44483</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44847</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44501</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>44831</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>44854</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>44860</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>45148</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>44617</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>44986</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>44987</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>45434</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>45306</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>45526</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45330</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>44986</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>45793</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>45908</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>45911</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>45798</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>46049</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>45096</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>45988</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>45070</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>44600</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>45929</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>46051</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>45030</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>45671</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>45708</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>45188</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>45910</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>44991</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>46100</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>44993</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>46107</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>46042</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>45911</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>45909</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>45785</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>45761</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>45141</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>45531</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         <v>45769</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         <v>44974</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>46006</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>45671</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>45448</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>45111</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>45573</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         <v>45758</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>45394</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>45386</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>45448</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>45394</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>46127</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>45761</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>44670</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>46169</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>45880</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>45895</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>45987</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>46177</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>45747</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>44593</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>44806</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>46202</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>46178</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         <v>46206</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>46210</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>45373</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         <v>45434</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>46097</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>46097</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>46189</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>44910</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         <v>45330</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         <v>45442</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>44923</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         <v>45182</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>45176</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>45016</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>46297</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         <v>46297</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>46297</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>46297</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>44930</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>45330</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8589,7 +8589,7 @@
         <v>45188</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>45719</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>44588</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>45386</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>45783</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>45782</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         <v>45782</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>45854</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>

--- a/Översikt SVALÖV.xlsx
+++ b/Översikt SVALÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45910</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 38522-2025</t>
+          <t>A 15475-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45884</v>
+        <v>45401</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -833,14 +833,14 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
@@ -848,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -857,10 +857,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -869,146 +869,146 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15475-2024 artfynd.xlsx", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15475-2024 karta.png", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15475-2024 georefererad karta.tif", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15475-2024 FSC-klagomål.docx", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15475-2024 FSC-klagomål mail.docx", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15475-2024 tillsynsbegäran.docx", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15475-2024 tillsynsbegäran mail.docx", "A 15475-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 38522-2025</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SVALÖV</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Skogsknipprot
 Stor häxört</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 38522-2025 artfynd.xlsx", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 38522-2025 karta.png", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 38522-2025 georefererad karta.tif", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 38522-2025 FSC-klagomål.docx", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 38522-2025 FSC-klagomål mail.docx", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 38522-2025 tillsynsbegäran.docx", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 38522-2025 tillsynsbegäran mail.docx", "A 38522-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 15475-2024</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45401</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SVALÖV</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15475-2024 artfynd.xlsx", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15475-2024 karta.png", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15475-2024 georefererad karta.tif", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15475-2024 FSC-klagomål.docx", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15475-2024 FSC-klagomål mail.docx", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15475-2024 tillsynsbegäran.docx", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15475-2024 tillsynsbegäran mail.docx", "A 15475-2024")</f>
         <v/>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
         <v>45645</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 11170-2023</t>
+          <t>A 15456-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44987</v>
+        <v>45401</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1187,46 +1187,46 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Korndådra</t>
+          <t>Lundticka</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11170-2023 artfynd.xlsx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15456-2024 artfynd.xlsx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11170-2023 karta.png", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15456-2024 karta.png", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11170-2023 georefererad karta.tif", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15456-2024 georefererad karta.tif", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11170-2023 FSC-klagomål.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15456-2024 FSC-klagomål.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11170-2023 FSC-klagomål mail.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15456-2024 FSC-klagomål mail.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11170-2023 tillsynsbegäran.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15456-2024 tillsynsbegäran.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11170-2023 tillsynsbegäran mail.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15456-2024 tillsynsbegäran mail.docx", "A 15456-2024")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 8169-2024</t>
+          <t>A 1577-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45351</v>
+        <v>45306</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1256,16 +1256,16 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.1</v>
+        <v>21.2</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1280,7 +1280,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1296,42 +1296,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Mjukdån</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 8169-2024 artfynd.xlsx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 8169-2024 karta.png", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 8169-2024 georefererad karta.tif", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 8169-2024 FSC-klagomål.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 8169-2024 FSC-klagomål mail.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 8169-2024 tillsynsbegäran.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 8169-2024 tillsynsbegäran mail.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 15456-2024</t>
+          <t>A 20125-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45401</v>
+        <v>45434</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1361,19 +1361,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.5</v>
+        <v>5.7</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1385,10 +1385,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1401,42 +1401,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Lundticka</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15456-2024 artfynd.xlsx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 20125-2024 artfynd.xlsx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15456-2024 karta.png", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 20125-2024 karta.png", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15456-2024 georefererad karta.tif", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 20125-2024 georefererad karta.tif", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15456-2024 FSC-klagomål.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 20125-2024 FSC-klagomål.docx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15456-2024 FSC-klagomål mail.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 20125-2024 FSC-klagomål mail.docx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15456-2024 tillsynsbegäran.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 20125-2024 tillsynsbegäran.docx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15456-2024 tillsynsbegäran mail.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 20125-2024 tillsynsbegäran mail.docx", "A 20125-2024")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 54127-2025</t>
+          <t>A 11672-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45964</v>
+        <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.3</v>
+        <v>13.9</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1506,46 +1506,42 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 54127-2025 artfynd.xlsx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11672-2024 artfynd.xlsx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 54127-2025 karta.png", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11672-2024 karta.png", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 54127-2025 georefererad karta.tif", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11672-2024 georefererad karta.tif", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 54127-2025 FSC-klagomål.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11672-2024 FSC-klagomål.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 54127-2025 FSC-klagomål mail.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11672-2024 FSC-klagomål mail.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 54127-2025 tillsynsbegäran.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11672-2024 tillsynsbegäran.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 54127-2025 tillsynsbegäran mail.docx", "A 54127-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/fåglar/A 54127-2025 prioriterade fågelarter.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11672-2024 tillsynsbegäran mail.docx", "A 11672-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 20125-2024</t>
+          <t>A 52664-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1559,10 +1555,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45434</v>
+        <v>45225</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1575,10 +1571,10 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
@@ -1615,42 +1611,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 20125-2024 artfynd.xlsx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 52664-2023 artfynd.xlsx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 20125-2024 karta.png", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 52664-2023 karta.png", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 20125-2024 georefererad karta.tif", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 52664-2023 georefererad karta.tif", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 20125-2024 FSC-klagomål.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 52664-2023 FSC-klagomål.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 20125-2024 FSC-klagomål mail.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 52664-2023 FSC-klagomål mail.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 20125-2024 tillsynsbegäran.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 52664-2023 tillsynsbegäran.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 20125-2024 tillsynsbegäran mail.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 52664-2023 tillsynsbegäran mail.docx", "A 52664-2023")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 52664-2023</t>
+          <t>A 11170-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1664,10 +1660,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45225</v>
+        <v>44987</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1680,34 +1676,34 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>6.4</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>1</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1716,46 +1712,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Korndådra</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 52664-2023 artfynd.xlsx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11170-2023 artfynd.xlsx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 52664-2023 karta.png", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11170-2023 karta.png", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 52664-2023 georefererad karta.tif", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11170-2023 georefererad karta.tif", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 52664-2023 FSC-klagomål.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11170-2023 FSC-klagomål.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 52664-2023 FSC-klagomål mail.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11170-2023 FSC-klagomål mail.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 52664-2023 tillsynsbegäran.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11170-2023 tillsynsbegäran.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 52664-2023 tillsynsbegäran mail.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11170-2023 tillsynsbegäran mail.docx", "A 11170-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 11672-2024</t>
+          <t>A 54127-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1769,10 +1765,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45373</v>
+        <v>45964</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1785,10 +1781,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>13.9</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1825,42 +1821,46 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11672-2024 artfynd.xlsx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 54127-2025 artfynd.xlsx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11672-2024 karta.png", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 54127-2025 karta.png", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11672-2024 georefererad karta.tif", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 54127-2025 georefererad karta.tif", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11672-2024 FSC-klagomål.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 54127-2025 FSC-klagomål.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11672-2024 FSC-klagomål mail.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 54127-2025 FSC-klagomål mail.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11672-2024 tillsynsbegäran.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 54127-2025 tillsynsbegäran.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11672-2024 tillsynsbegäran mail.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 54127-2025 tillsynsbegäran mail.docx", "A 54127-2025")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/fåglar/A 54127-2025 prioriterade fågelarter.docx", "A 54127-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 1577-2024</t>
+          <t>A 8169-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45306</v>
+        <v>45351</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1890,17 +1890,17 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>21.2</v>
+        <v>3.1</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1930,35 +1930,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Mjukdån</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 8169-2024 artfynd.xlsx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 8169-2024 karta.png", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 8169-2024 georefererad karta.tif", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 8169-2024 FSC-klagomål.docx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 8169-2024 FSC-klagomål mail.docx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 8169-2024 tillsynsbegäran.docx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 8169-2024 tillsynsbegäran mail.docx", "A 8169-2024")</f>
         <v/>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         <v>45218</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>44763</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44598</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44483</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44847</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44501</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>44831</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>44854</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 49032-2022</t>
+          <t>A 13245-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2595,10 +2595,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44860</v>
+        <v>45386</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.7</v>
+        <v>13</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 35911-2023</t>
+          <t>A 21774-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45148</v>
+        <v>45442</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 9716-2022</t>
+          <t>A 22794-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44617</v>
+        <v>45448</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2800,7 +2800,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 11101-2023</t>
+          <t>A 35587-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2814,10 +2814,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44986</v>
+        <v>45531</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 11177-2023</t>
+          <t>A 16667-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44987</v>
+        <v>45030</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 20047-2024</t>
+          <t>A 5068-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45434</v>
+        <v>46049</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3019,7 +3019,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 1592-2024</t>
+          <t>A 59266-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45306</v>
+        <v>45988</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3092,7 +3092,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 34808-2024</t>
+          <t>A 22063-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3106,10 +3106,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45526</v>
+        <v>45785</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3165,7 +3165,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 5167-2024</t>
+          <t>A 17980-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45330</v>
+        <v>45761</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>6.5</v>
+        <v>3.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3238,7 +3238,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 10209-2023</t>
+          <t>A 19282-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3248,14 +3248,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44986</v>
+        <v>45769</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3311,7 +3311,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 23747-2025</t>
+          <t>A 42706-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45793</v>
+        <v>45908</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3384,7 +3384,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 42706-2025</t>
+          <t>A 8332-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45908</v>
+        <v>45708</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>45911</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 24513-2025</t>
+          <t>A 14543-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45798</v>
+        <v>45394</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3603,7 +3603,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 5068-2026</t>
+          <t>A 20170-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46049</v>
+        <v>45434</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3676,7 +3676,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 27310-2023</t>
+          <t>A 37907-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45096</v>
+        <v>45880</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3705,8 +3705,13 @@
           <t>SVALÖV</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>2.5</v>
+        <v>5.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3749,7 +3754,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 59266-2025</t>
+          <t>A 40470-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3759,14 +3764,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45988</v>
+        <v>45895</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3779,7 +3784,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.8</v>
+        <v>0.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3822,7 +3827,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 22262-2023</t>
+          <t>A 62403-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3836,10 +3841,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45070</v>
+        <v>44923</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3852,7 +3857,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3895,7 +3900,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 6335-2022</t>
+          <t>A 47139-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3909,10 +3914,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44600</v>
+        <v>45929</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3925,7 +3930,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3968,7 +3973,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 47139-2025</t>
+          <t>A 6365-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3982,10 +3987,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45929</v>
+        <v>46051</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3998,7 +4003,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4041,7 +4046,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 6365-2026</t>
+          <t>A 15157-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4055,10 +4060,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46051</v>
+        <v>45016</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4071,7 +4076,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4114,7 +4119,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 16667-2023</t>
+          <t>A 11491-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4128,10 +4133,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45030</v>
+        <v>44991</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4144,7 +4149,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4187,7 +4192,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 1920-2025</t>
+          <t>A 10209-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4201,10 +4206,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45671</v>
+        <v>44986</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4217,7 +4222,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4260,7 +4265,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 8332-2025</t>
+          <t>A 43294-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4274,10 +4279,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45708</v>
+        <v>45910</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4290,7 +4295,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4333,7 +4338,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 44112-2023</t>
+          <t>A 44107-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4350,7 +4355,7 @@
         <v>45188</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4363,7 +4368,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4406,7 +4411,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 43294-2025</t>
+          <t>A 14533-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4420,10 +4425,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45910</v>
+        <v>46100</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4436,7 +4441,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4479,7 +4484,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 11491-2023</t>
+          <t>A 15747-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4493,10 +4498,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44991</v>
+        <v>46107</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4509,7 +4514,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4552,7 +4557,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 14533-2026</t>
+          <t>A 3430-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4566,10 +4571,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46100</v>
+        <v>46042</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4582,7 +4587,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.2</v>
+        <v>5.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4625,7 +4630,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 11922-2023</t>
+          <t>A 22262-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4639,10 +4644,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44993</v>
+        <v>45070</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4655,7 +4660,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4698,7 +4703,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 15747-2026</t>
+          <t>A 43466-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4712,10 +4717,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46107</v>
+        <v>45911</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4728,7 +4733,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>4.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4771,7 +4776,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 3430-2026</t>
+          <t>A 49032-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4785,10 +4790,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46042</v>
+        <v>44860</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4801,7 +4806,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5.7</v>
+        <v>3.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4844,7 +4849,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 43466-2025</t>
+          <t>A 43004-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4858,10 +4863,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45911</v>
+        <v>45909</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4874,7 +4879,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.5</v>
+        <v>1.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4917,7 +4922,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 43004-2025</t>
+          <t>A 34810-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4931,10 +4936,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45909</v>
+        <v>45141</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4947,7 +4952,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.6</v>
+        <v>7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4990,7 +4995,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 22063-2025</t>
+          <t>A 18121-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5004,10 +5009,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45785</v>
+        <v>45761</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5020,7 +5025,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5063,7 +5068,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 17980-2025</t>
+          <t>A 62201-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5077,10 +5082,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45761</v>
+        <v>46006</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5093,7 +5098,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.4</v>
+        <v>22.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5136,7 +5141,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 34810-2023</t>
+          <t>A 6335-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5150,10 +5155,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45141</v>
+        <v>44600</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5166,7 +5171,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5209,7 +5214,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 35587-2024</t>
+          <t>A 10196-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5223,10 +5228,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45531</v>
+        <v>45719</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5239,7 +5244,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5282,7 +5287,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 19282-2025</t>
+          <t>A 44112-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5292,14 +5297,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45769</v>
+        <v>45188</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5312,7 +5317,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5355,7 +5360,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 8924-2023</t>
+          <t>A 35911-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5369,10 +5374,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44974</v>
+        <v>45148</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5385,7 +5390,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>6.8</v>
+        <v>0.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5428,7 +5433,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 62201-2025</t>
+          <t>A 18438-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5442,10 +5447,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46006</v>
+        <v>46127</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5458,7 +5463,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>22.1</v>
+        <v>1.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5501,7 +5506,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 1901-2025</t>
+          <t>A 42588-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5515,10 +5520,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45671</v>
+        <v>45176</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5531,7 +5536,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5574,7 +5579,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 22794-2024</t>
+          <t>A 1901-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5588,10 +5593,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45448</v>
+        <v>45671</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5604,7 +5609,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5647,7 +5652,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 32620-2023</t>
+          <t>A 1920-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5661,10 +5666,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45111</v>
+        <v>45671</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5677,7 +5682,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5720,7 +5725,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 44196-2024</t>
+          <t>A 43736-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5734,10 +5739,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45573</v>
+        <v>45182</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5750,7 +5755,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5793,7 +5798,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 17731-2025</t>
+          <t>A 24286-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5803,14 +5808,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45758</v>
+        <v>46169</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5823,7 +5828,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5866,7 +5871,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 14543-2024</t>
+          <t>A 58970-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5880,10 +5885,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45394</v>
+        <v>45987</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5896,7 +5901,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5939,7 +5944,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 13273-2024</t>
+          <t>A 9716-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5953,10 +5958,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45386</v>
+        <v>44617</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5969,7 +5974,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>12.4</v>
+        <v>0.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6012,7 +6017,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 22792-2024</t>
+          <t>A 25522-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6026,10 +6031,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45448</v>
+        <v>46177</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6042,7 +6047,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.5</v>
+        <v>8.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6085,7 +6090,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 14546-2024</t>
+          <t>A 37354-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6099,10 +6104,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45394</v>
+        <v>44806</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6115,7 +6120,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6158,7 +6163,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 18438-2026</t>
+          <t>A 5190-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6172,10 +6177,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46127</v>
+        <v>45330</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6188,7 +6193,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6231,7 +6236,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 18121-2025</t>
+          <t>A 25832-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6245,10 +6250,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45761</v>
+        <v>46178</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6261,7 +6266,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.7</v>
+        <v>7.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6304,7 +6309,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 16215-2022</t>
+          <t>A 17731-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6314,14 +6319,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44670</v>
+        <v>45758</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6334,7 +6339,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6377,7 +6382,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 24286-2026</t>
+          <t>A 29337-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6391,10 +6396,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46169</v>
+        <v>46202</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6407,7 +6412,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6450,7 +6455,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 37907-2025</t>
+          <t>A 30535-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6464,10 +6469,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45880</v>
+        <v>46210</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6479,13 +6484,8 @@
           <t>SVALÖV</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>5.7</v>
+        <v>0.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6528,7 +6528,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 40470-2025</t>
+          <t>A 30202-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6538,14 +6538,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45895</v>
+        <v>46206</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.1</v>
+        <v>5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6601,7 +6601,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 58970-2025</t>
+          <t>A 22792-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45987</v>
+        <v>45448</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6674,7 +6674,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 25522-2026</t>
+          <t>A 4964-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6688,10 +6688,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46177</v>
+        <v>44593</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6747,7 +6747,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 15487-2025</t>
+          <t>A 11177-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6761,10 +6761,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45747</v>
+        <v>44987</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6820,7 +6820,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 4964-2022</t>
+          <t>A 16215-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6834,10 +6834,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44593</v>
+        <v>44670</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6893,7 +6893,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 37354-2022</t>
+          <t>A 61620-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44806</v>
+        <v>44910</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6966,7 +6966,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 29337-2026</t>
+          <t>A 8924-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6980,10 +6980,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46202</v>
+        <v>44974</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2</v>
+        <v>6.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 25832-2026</t>
+          <t>A 497-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46178</v>
+        <v>44930</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>7.8</v>
+        <v>0.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7112,7 +7112,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 30202-2026</t>
+          <t>A 11633-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46206</v>
+        <v>45373</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7185,7 +7185,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 30535-2026</t>
+          <t>A 13791-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7199,10 +7199,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46210</v>
+        <v>46097</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7258,7 +7258,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 11633-2024</t>
+          <t>A 11922-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45373</v>
+        <v>44993</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4.9</v>
+        <v>0.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7331,7 +7331,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 20170-2024</t>
+          <t>A 13787-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7345,10 +7345,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45434</v>
+        <v>46097</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7404,7 +7404,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 13791-2026</t>
+          <t>A 14546-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7418,10 +7418,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46097</v>
+        <v>45394</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 13787-2026</t>
+          <t>A 32620-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7491,10 +7491,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46097</v>
+        <v>45111</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7567,7 +7567,7 @@
         <v>46189</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 61620-2022</t>
+          <t>A 1592-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7637,10 +7637,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44910</v>
+        <v>45306</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7696,7 +7696,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 5190-2024</t>
+          <t>A 4149-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7706,14 +7706,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45330</v>
+        <v>44588</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7769,7 +7769,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 21774-2024</t>
+          <t>A 15487-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45442</v>
+        <v>45747</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7842,7 +7842,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 62403-2022</t>
+          <t>A 11101-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7856,10 +7856,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44923</v>
+        <v>44986</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7915,7 +7915,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 43736-2023</t>
+          <t>A 5184-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7929,10 +7929,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45182</v>
+        <v>45330</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7988,7 +7988,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 42588-2023</t>
+          <t>A 13273-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8002,10 +8002,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45176</v>
+        <v>45386</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.1</v>
+        <v>12.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8061,7 +8061,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 15157-2023</t>
+          <t>A 44196-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8075,10 +8075,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45016</v>
+        <v>45573</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8134,7 +8134,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 40917-2026</t>
+          <t>A 21556-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46297</v>
+        <v>45782</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>8.1</v>
+        <v>1.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8207,7 +8207,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 40895-2026</t>
+          <t>A 21541-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8221,10 +8221,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46297</v>
+        <v>45782</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8280,7 +8280,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 40882-2026</t>
+          <t>A 21814-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8294,10 +8294,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46297</v>
+        <v>45783</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8353,7 +8353,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 40910-2026</t>
+          <t>A 20047-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8367,10 +8367,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46297</v>
+        <v>45434</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 497-2023</t>
+          <t>A 40882-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44930</v>
+        <v>46297</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8499,7 +8499,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 5184-2024</t>
+          <t>A 40917-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45330</v>
+        <v>46297</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.2</v>
+        <v>8.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8572,7 +8572,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 44107-2023</t>
+          <t>A 34808-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45188</v>
+        <v>45526</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8645,7 +8645,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 10196-2025</t>
+          <t>A 40910-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8659,10 +8659,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45719</v>
+        <v>46297</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8718,7 +8718,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 4149-2022</t>
+          <t>A 5167-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8728,14 +8728,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44588</v>
+        <v>45330</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.1</v>
+        <v>6.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8791,7 +8791,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 13245-2024</t>
+          <t>A 23747-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45386</v>
+        <v>45793</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>13</v>
+        <v>2.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8864,7 +8864,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 21814-2025</t>
+          <t>A 40895-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8878,10 +8878,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45783</v>
+        <v>46297</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8937,7 +8937,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 21541-2025</t>
+          <t>A 24513-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8951,10 +8951,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45782</v>
+        <v>45798</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.1</v>
+        <v>0.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9010,7 +9010,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 21556-2025</t>
+          <t>A 27310-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9024,10 +9024,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45782</v>
+        <v>45096</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9040,7 +9040,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9100,7 +9100,7 @@
         <v>45854</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>

--- a/Översikt SVALÖV.xlsx
+++ b/Översikt SVALÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45910</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 15475-2024</t>
+          <t>A 38522-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45401</v>
+        <v>45884</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.7</v>
+        <v>2.6</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -848,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -857,10 +857,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -869,259 +869,259 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Skogsknipprot
+Stor häxört</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 38522-2025 artfynd.xlsx", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 38522-2025 karta.png", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 38522-2025 georefererad karta.tif", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 38522-2025 FSC-klagomål.docx", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 38522-2025 FSC-klagomål mail.docx", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 38522-2025 tillsynsbegäran.docx", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 38522-2025 tillsynsbegäran mail.docx", "A 38522-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 61064-2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45645</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SVALÖV</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 61064-2024 artfynd.xlsx", "A 61064-2024")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 61064-2024 karta.png", "A 61064-2024")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 61064-2024 georefererad karta.tif", "A 61064-2024")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 61064-2024 FSC-klagomål.docx", "A 61064-2024")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 61064-2024 FSC-klagomål mail.docx", "A 61064-2024")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 61064-2024 tillsynsbegäran.docx", "A 61064-2024")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 61064-2024 tillsynsbegäran mail.docx", "A 61064-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 15475-2024</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45401</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>SVALÖV</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Ask
 Strutbräken</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15475-2024 artfynd.xlsx", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15475-2024 karta.png", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15475-2024 georefererad karta.tif", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15475-2024 FSC-klagomål.docx", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15475-2024 FSC-klagomål mail.docx", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15475-2024 tillsynsbegäran.docx", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15475-2024 tillsynsbegäran mail.docx", "A 15475-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 38522-2025</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45884</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SVALÖV</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Skogsknipprot
-Stor häxört</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 38522-2025 artfynd.xlsx", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 38522-2025 karta.png", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 38522-2025 georefererad karta.tif", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 38522-2025 FSC-klagomål.docx", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 38522-2025 FSC-klagomål mail.docx", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 38522-2025 tillsynsbegäran.docx", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 38522-2025 tillsynsbegäran mail.docx", "A 38522-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 61064-2024</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45645</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>SVALÖV</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 61064-2024 artfynd.xlsx", "A 61064-2024")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 61064-2024 karta.png", "A 61064-2024")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 61064-2024 georefererad karta.tif", "A 61064-2024")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 61064-2024 FSC-klagomål.docx", "A 61064-2024")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 61064-2024 FSC-klagomål mail.docx", "A 61064-2024")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 61064-2024 tillsynsbegäran.docx", "A 61064-2024")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 61064-2024 tillsynsbegäran mail.docx", "A 61064-2024")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 15456-2024</t>
+          <t>A 11170-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45401</v>
+        <v>44987</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1187,46 +1187,46 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Lundticka</t>
+          <t>Korndådra</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15456-2024 artfynd.xlsx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11170-2023 artfynd.xlsx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15456-2024 karta.png", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11170-2023 karta.png", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15456-2024 georefererad karta.tif", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11170-2023 georefererad karta.tif", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15456-2024 FSC-klagomål.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11170-2023 FSC-klagomål.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15456-2024 FSC-klagomål mail.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11170-2023 FSC-klagomål mail.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15456-2024 tillsynsbegäran.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11170-2023 tillsynsbegäran.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15456-2024 tillsynsbegäran mail.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11170-2023 tillsynsbegäran mail.docx", "A 11170-2023")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 1577-2024</t>
+          <t>A 15456-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45306</v>
+        <v>45401</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1256,20 +1256,20 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>21.2</v>
+        <v>2.5</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
@@ -1280,10 +1280,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1296,42 +1296,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Lundticka</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15456-2024 artfynd.xlsx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15456-2024 karta.png", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15456-2024 georefererad karta.tif", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15456-2024 FSC-klagomål.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15456-2024 FSC-klagomål mail.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15456-2024 tillsynsbegäran.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15456-2024 tillsynsbegäran mail.docx", "A 15456-2024")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 20125-2024</t>
+          <t>A 54127-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45434</v>
+        <v>45964</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1361,17 +1361,17 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.7</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
@@ -1385,7 +1385,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1397,46 +1397,50 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 20125-2024 artfynd.xlsx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 54127-2025 artfynd.xlsx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 20125-2024 karta.png", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 54127-2025 karta.png", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 20125-2024 georefererad karta.tif", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 54127-2025 georefererad karta.tif", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 20125-2024 FSC-klagomål.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 54127-2025 FSC-klagomål.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 20125-2024 FSC-klagomål mail.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 54127-2025 FSC-klagomål mail.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 20125-2024 tillsynsbegäran.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 54127-2025 tillsynsbegäran.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 20125-2024 tillsynsbegäran mail.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 54127-2025 tillsynsbegäran mail.docx", "A 54127-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/fåglar/A 54127-2025 prioriterade fågelarter.docx", "A 54127-2025")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 11672-2024</t>
+          <t>A 20125-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1450,10 +1454,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45373</v>
+        <v>45434</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1466,16 +1470,16 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>13.9</v>
+        <v>5.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1490,7 +1494,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1502,39 +1506,39 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11672-2024 artfynd.xlsx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 20125-2024 artfynd.xlsx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11672-2024 karta.png", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 20125-2024 karta.png", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11672-2024 georefererad karta.tif", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 20125-2024 georefererad karta.tif", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11672-2024 FSC-klagomål.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 20125-2024 FSC-klagomål.docx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11672-2024 FSC-klagomål mail.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 20125-2024 FSC-klagomål mail.docx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11672-2024 tillsynsbegäran.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 20125-2024 tillsynsbegäran.docx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11672-2024 tillsynsbegäran mail.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 20125-2024 tillsynsbegäran mail.docx", "A 20125-2024")</f>
         <v/>
       </c>
     </row>
@@ -1558,7 +1562,7 @@
         <v>45225</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1646,7 +1650,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 11170-2023</t>
+          <t>A 11672-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1660,10 +1664,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44987</v>
+        <v>45373</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1676,7 +1680,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.9</v>
+        <v>13.9</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1685,13 +1689,13 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1703,7 +1707,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1716,42 +1720,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Korndådra</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11170-2023 artfynd.xlsx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11672-2024 artfynd.xlsx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11170-2023 karta.png", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11672-2024 karta.png", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11170-2023 georefererad karta.tif", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11672-2024 georefererad karta.tif", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11170-2023 FSC-klagomål.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11672-2024 FSC-klagomål.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11170-2023 FSC-klagomål mail.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11672-2024 FSC-klagomål mail.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11170-2023 tillsynsbegäran.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11672-2024 tillsynsbegäran.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11170-2023 tillsynsbegäran mail.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11672-2024 tillsynsbegäran mail.docx", "A 11672-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 54127-2025</t>
+          <t>A 1577-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1765,10 +1769,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45964</v>
+        <v>45306</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1781,7 +1785,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>21.2</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1790,7 +1794,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1805,7 +1809,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1817,43 +1821,39 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 54127-2025 artfynd.xlsx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 54127-2025 karta.png", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 54127-2025 georefererad karta.tif", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 54127-2025 FSC-klagomål.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 54127-2025 FSC-klagomål mail.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 54127-2025 tillsynsbegäran.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 54127-2025 tillsynsbegäran mail.docx", "A 54127-2025")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/fåglar/A 54127-2025 prioriterade fågelarter.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
         <v>45351</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>45218</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>44763</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44598</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44483</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44847</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44501</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>44831</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>44854</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 13245-2024</t>
+          <t>A 49032-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2595,10 +2595,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45386</v>
+        <v>44860</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>13</v>
+        <v>3.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 21774-2024</t>
+          <t>A 35911-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45442</v>
+        <v>45148</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 22794-2024</t>
+          <t>A 11101-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45448</v>
+        <v>44986</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2800,7 +2800,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 35587-2024</t>
+          <t>A 9716-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2814,10 +2814,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45531</v>
+        <v>44617</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 16667-2023</t>
+          <t>A 11177-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45030</v>
+        <v>44987</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 5068-2026</t>
+          <t>A 1592-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46049</v>
+        <v>45306</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3019,7 +3019,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 59266-2025</t>
+          <t>A 10209-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45988</v>
+        <v>44986</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3092,7 +3092,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 22063-2025</t>
+          <t>A 27310-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3106,10 +3106,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45785</v>
+        <v>45096</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3165,7 +3165,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 17980-2025</t>
+          <t>A 22262-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45761</v>
+        <v>45070</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3238,7 +3238,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 19282-2025</t>
+          <t>A 6335-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3248,14 +3248,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45769</v>
+        <v>44600</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3311,7 +3311,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 42706-2025</t>
+          <t>A 16667-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45908</v>
+        <v>45030</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3384,7 +3384,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 8332-2025</t>
+          <t>A 5068-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45708</v>
+        <v>46049</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 43425-2025</t>
+          <t>A 59266-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45911</v>
+        <v>45988</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 14543-2024</t>
+          <t>A 42706-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45394</v>
+        <v>45908</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3603,7 +3603,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 20170-2024</t>
+          <t>A 6365-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45434</v>
+        <v>46051</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3676,7 +3676,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 37907-2025</t>
+          <t>A 1920-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45880</v>
+        <v>45671</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3705,13 +3705,8 @@
           <t>SVALÖV</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>5.7</v>
+        <v>2.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3754,7 +3749,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 40470-2025</t>
+          <t>A 43425-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3764,14 +3759,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45895</v>
+        <v>45911</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3784,7 +3779,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.1</v>
+        <v>2.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3827,7 +3822,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 62403-2022</t>
+          <t>A 8332-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3841,10 +3836,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44923</v>
+        <v>45708</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3857,7 +3852,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3900,7 +3895,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 47139-2025</t>
+          <t>A 44112-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3914,10 +3909,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45929</v>
+        <v>45188</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3930,7 +3925,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3973,7 +3968,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 6365-2026</t>
+          <t>A 47139-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3987,10 +3982,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46051</v>
+        <v>45929</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4003,7 +3998,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4046,7 +4041,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 15157-2023</t>
+          <t>A 11491-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4060,10 +4055,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45016</v>
+        <v>44991</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4076,7 +4071,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4119,7 +4114,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 11491-2023</t>
+          <t>A 22063-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4133,10 +4128,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44991</v>
+        <v>45785</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4149,7 +4144,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4192,7 +4187,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 10209-2023</t>
+          <t>A 11922-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4206,10 +4201,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44986</v>
+        <v>44993</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4222,7 +4217,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4265,7 +4260,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 43294-2025</t>
+          <t>A 14533-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4279,10 +4274,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45910</v>
+        <v>46100</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4295,7 +4290,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4338,7 +4333,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 44107-2023</t>
+          <t>A 17980-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4352,10 +4347,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45188</v>
+        <v>45761</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4368,7 +4363,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4411,7 +4406,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 14533-2026</t>
+          <t>A 15747-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4425,10 +4420,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46100</v>
+        <v>46107</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4441,7 +4436,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4484,7 +4479,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 15747-2026</t>
+          <t>A 19282-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4494,14 +4489,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46107</v>
+        <v>45769</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4514,7 +4509,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4574,7 +4569,7 @@
         <v>46042</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4630,7 +4625,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 22262-2023</t>
+          <t>A 37907-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4644,10 +4639,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45070</v>
+        <v>45880</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4659,8 +4654,13 @@
           <t>SVALÖV</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>1.1</v>
+        <v>5.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 43466-2025</t>
+          <t>A 40470-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4713,14 +4713,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45911</v>
+        <v>45895</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.5</v>
+        <v>0.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 49032-2022</t>
+          <t>A 43294-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44860</v>
+        <v>45910</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 43004-2025</t>
+          <t>A 34810-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45909</v>
+        <v>45141</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.6</v>
+        <v>7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 34810-2023</t>
+          <t>A 62201-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45141</v>
+        <v>46006</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>7</v>
+        <v>22.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 18121-2025</t>
+          <t>A 43466-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45761</v>
+        <v>45911</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 62201-2025</t>
+          <t>A 43004-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46006</v>
+        <v>45909</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>22.1</v>
+        <v>1.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 6335-2022</t>
+          <t>A 18438-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5155,10 +5155,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44600</v>
+        <v>46127</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 10196-2025</t>
+          <t>A 24286-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45719</v>
+        <v>46169</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 44112-2023</t>
+          <t>A 35587-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45188</v>
+        <v>45531</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 35911-2023</t>
+          <t>A 58970-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45148</v>
+        <v>45987</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 18438-2026</t>
+          <t>A 25522-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46127</v>
+        <v>46177</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.6</v>
+        <v>8.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 42588-2023</t>
+          <t>A 8924-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45176</v>
+        <v>44974</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>6.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5596,7 +5596,7 @@
         <v>45671</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 1920-2025</t>
+          <t>A 22794-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45671</v>
+        <v>45448</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5725,7 +5725,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 43736-2023</t>
+          <t>A 32620-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45182</v>
+        <v>45111</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5798,7 +5798,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 24286-2026</t>
+          <t>A 44196-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46169</v>
+        <v>45573</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5871,7 +5871,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 58970-2025</t>
+          <t>A 17731-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5881,14 +5881,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45987</v>
+        <v>45758</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5944,7 +5944,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 9716-2022</t>
+          <t>A 14543-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5958,10 +5958,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44617</v>
+        <v>45394</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 25522-2026</t>
+          <t>A 13273-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46177</v>
+        <v>45386</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>8.5</v>
+        <v>12.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6090,7 +6090,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 37354-2022</t>
+          <t>A 29337-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6104,10 +6104,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44806</v>
+        <v>46202</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6163,7 +6163,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 5190-2024</t>
+          <t>A 25832-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45330</v>
+        <v>46178</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.1</v>
+        <v>7.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 25832-2026</t>
+          <t>A 30202-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6250,10 +6250,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46178</v>
+        <v>46206</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>7.8</v>
+        <v>5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 17731-2025</t>
+          <t>A 30535-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6319,14 +6319,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45758</v>
+        <v>46210</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 29337-2026</t>
+          <t>A 22792-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6396,10 +6396,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46202</v>
+        <v>45448</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6455,7 +6455,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 30535-2026</t>
+          <t>A 14546-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6469,10 +6469,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46210</v>
+        <v>45394</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6528,7 +6528,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 30202-2026</t>
+          <t>A 18121-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46206</v>
+        <v>45761</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6601,7 +6601,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 22792-2024</t>
+          <t>A 16215-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45448</v>
+        <v>44670</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6674,7 +6674,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 4964-2022</t>
+          <t>A 15487-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6688,10 +6688,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44593</v>
+        <v>45747</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6747,7 +6747,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 11177-2023</t>
+          <t>A 4964-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6761,10 +6761,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44987</v>
+        <v>44593</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6820,7 +6820,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 16215-2022</t>
+          <t>A 37354-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6834,10 +6834,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44670</v>
+        <v>44806</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6893,7 +6893,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 61620-2022</t>
+          <t>A 11633-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44910</v>
+        <v>45373</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.5</v>
+        <v>4.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6966,7 +6966,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 8924-2023</t>
+          <t>A 13791-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6980,10 +6980,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44974</v>
+        <v>46097</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>6.8</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 497-2023</t>
+          <t>A 13787-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44930</v>
+        <v>46097</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7112,7 +7112,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 11633-2024</t>
+          <t>A 27380-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45373</v>
+        <v>46189</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.9</v>
+        <v>1.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7185,7 +7185,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 13791-2026</t>
+          <t>A 20170-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7199,10 +7199,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46097</v>
+        <v>45434</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7258,7 +7258,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 11922-2023</t>
+          <t>A 61620-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44993</v>
+        <v>44910</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7331,7 +7331,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 13787-2026</t>
+          <t>A 5190-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7345,10 +7345,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46097</v>
+        <v>45330</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7404,7 +7404,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 14546-2024</t>
+          <t>A 40917-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7418,10 +7418,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45394</v>
+        <v>46297</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>8.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7477,7 +7477,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 32620-2023</t>
+          <t>A 40895-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7491,10 +7491,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45111</v>
+        <v>46297</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7550,7 +7550,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 27380-2026</t>
+          <t>A 40882-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7564,10 +7564,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46189</v>
+        <v>46297</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7623,7 +7623,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 1592-2024</t>
+          <t>A 40910-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7637,10 +7637,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45306</v>
+        <v>46297</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7696,7 +7696,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 4149-2022</t>
+          <t>A 21774-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7706,14 +7706,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44588</v>
+        <v>45442</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7769,7 +7769,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 15487-2025</t>
+          <t>A 62403-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45747</v>
+        <v>44923</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7842,7 +7842,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 11101-2023</t>
+          <t>A 43736-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7856,10 +7856,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44986</v>
+        <v>45182</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7915,7 +7915,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 5184-2024</t>
+          <t>A 42588-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7929,10 +7929,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45330</v>
+        <v>45176</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7988,7 +7988,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 13273-2024</t>
+          <t>A 15157-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8002,10 +8002,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45386</v>
+        <v>45016</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>12.4</v>
+        <v>2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8061,7 +8061,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 44196-2024</t>
+          <t>A 497-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8075,10 +8075,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45573</v>
+        <v>44930</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8134,7 +8134,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 21556-2025</t>
+          <t>A 5184-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45782</v>
+        <v>45330</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8207,7 +8207,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 21541-2025</t>
+          <t>A 44107-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8221,10 +8221,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45782</v>
+        <v>45188</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8280,7 +8280,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 21814-2025</t>
+          <t>A 10196-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8294,10 +8294,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45783</v>
+        <v>45719</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8353,7 +8353,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 20047-2024</t>
+          <t>A 4149-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8363,14 +8363,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45434</v>
+        <v>44588</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 40882-2026</t>
+          <t>A 13245-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46297</v>
+        <v>45386</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8499,7 +8499,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 40917-2026</t>
+          <t>A 21814-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46297</v>
+        <v>45783</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>8.1</v>
+        <v>2.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8572,7 +8572,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 34808-2024</t>
+          <t>A 21541-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45526</v>
+        <v>45782</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8645,7 +8645,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 40910-2026</t>
+          <t>A 21556-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8659,10 +8659,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46297</v>
+        <v>45782</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8718,7 +8718,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 5167-2024</t>
+          <t>A 20047-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8732,10 +8732,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45330</v>
+        <v>45434</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>6.5</v>
+        <v>2.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8791,7 +8791,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 23747-2025</t>
+          <t>A 34808-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45793</v>
+        <v>45526</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8864,7 +8864,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 40895-2026</t>
+          <t>A 5167-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8878,10 +8878,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46297</v>
+        <v>45330</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.7</v>
+        <v>6.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8937,7 +8937,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 24513-2025</t>
+          <t>A 23747-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8951,10 +8951,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45798</v>
+        <v>45793</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9010,7 +9010,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 27310-2023</t>
+          <t>A 24513-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9024,10 +9024,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45096</v>
+        <v>45798</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9040,7 +9040,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9100,7 +9100,7 @@
         <v>45854</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>

--- a/Översikt SVALÖV.xlsx
+++ b/Översikt SVALÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45910</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 38522-2025</t>
+          <t>A 15475-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45884</v>
+        <v>45401</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -833,14 +833,14 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
@@ -848,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -857,10 +857,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -869,259 +869,259 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15475-2024 artfynd.xlsx", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15475-2024 karta.png", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15475-2024 georefererad karta.tif", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15475-2024 FSC-klagomål.docx", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15475-2024 FSC-klagomål mail.docx", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15475-2024 tillsynsbegäran.docx", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15475-2024 tillsynsbegäran mail.docx", "A 15475-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 38522-2025</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SVALÖV</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Skogsknipprot
 Stor häxört</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 38522-2025 artfynd.xlsx", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 38522-2025 karta.png", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 38522-2025 georefererad karta.tif", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 38522-2025 FSC-klagomål.docx", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 38522-2025 FSC-klagomål mail.docx", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 38522-2025 tillsynsbegäran.docx", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 38522-2025 tillsynsbegäran mail.docx", "A 38522-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>A 61064-2024</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
         <v>45645</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SVALÖV</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
+      <c r="E6" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>SVALÖV</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>5.6</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K6" t="n">
         <v>1</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>1</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R6" t="n">
         <v>1</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S6" t="n">
         <v>2</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T6" t="n">
         <v>2</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Ask
 Skogsknipprot</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 61064-2024 artfynd.xlsx", "A 61064-2024")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 61064-2024 karta.png", "A 61064-2024")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 61064-2024 georefererad karta.tif", "A 61064-2024")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 61064-2024 FSC-klagomål.docx", "A 61064-2024")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 61064-2024 FSC-klagomål mail.docx", "A 61064-2024")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 61064-2024 tillsynsbegäran.docx", "A 61064-2024")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 61064-2024 tillsynsbegäran mail.docx", "A 61064-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 15475-2024</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45401</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>SVALÖV</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15475-2024 artfynd.xlsx", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15475-2024 karta.png", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15475-2024 georefererad karta.tif", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15475-2024 FSC-klagomål.docx", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15475-2024 FSC-klagomål mail.docx", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15475-2024 tillsynsbegäran.docx", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15475-2024 tillsynsbegäran mail.docx", "A 15475-2024")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 11170-2023</t>
+          <t>A 15456-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44987</v>
+        <v>45401</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1187,46 +1187,46 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Korndådra</t>
+          <t>Lundticka</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11170-2023 artfynd.xlsx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15456-2024 artfynd.xlsx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11170-2023 karta.png", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15456-2024 karta.png", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11170-2023 georefererad karta.tif", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15456-2024 georefererad karta.tif", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11170-2023 FSC-klagomål.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15456-2024 FSC-klagomål.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11170-2023 FSC-klagomål mail.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15456-2024 FSC-klagomål mail.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11170-2023 tillsynsbegäran.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15456-2024 tillsynsbegäran.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11170-2023 tillsynsbegäran mail.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15456-2024 tillsynsbegäran mail.docx", "A 15456-2024")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 15456-2024</t>
+          <t>A 8169-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45401</v>
+        <v>45351</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1265,10 +1265,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1283,7 +1283,7 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1296,42 +1296,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Lundticka</t>
+          <t>Mjukdån</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15456-2024 artfynd.xlsx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 8169-2024 artfynd.xlsx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15456-2024 karta.png", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 8169-2024 karta.png", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15456-2024 georefererad karta.tif", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 8169-2024 georefererad karta.tif", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15456-2024 FSC-klagomål.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 8169-2024 FSC-klagomål.docx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15456-2024 FSC-klagomål mail.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 8169-2024 FSC-klagomål mail.docx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15456-2024 tillsynsbegäran.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 8169-2024 tillsynsbegäran.docx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15456-2024 tillsynsbegäran mail.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 8169-2024 tillsynsbegäran mail.docx", "A 8169-2024")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 54127-2025</t>
+          <t>A 1577-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45964</v>
+        <v>45306</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>21.2</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1370,7 +1370,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1397,43 +1397,39 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 54127-2025 artfynd.xlsx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 54127-2025 karta.png", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 54127-2025 georefererad karta.tif", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 54127-2025 FSC-klagomål.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 54127-2025 FSC-klagomål mail.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 54127-2025 tillsynsbegäran.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 54127-2025 tillsynsbegäran mail.docx", "A 54127-2025")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/fåglar/A 54127-2025 prioriterade fågelarter.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
     </row>
@@ -1457,7 +1453,7 @@
         <v>45434</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1545,7 +1541,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 52664-2023</t>
+          <t>A 11672-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1559,10 +1555,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45225</v>
+        <v>45373</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1575,31 +1571,31 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>6.4</v>
+        <v>13.9</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1611,46 +1607,46 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 52664-2023 artfynd.xlsx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11672-2024 artfynd.xlsx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 52664-2023 karta.png", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11672-2024 karta.png", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 52664-2023 georefererad karta.tif", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11672-2024 georefererad karta.tif", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 52664-2023 FSC-klagomål.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11672-2024 FSC-klagomål.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 52664-2023 FSC-klagomål mail.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11672-2024 FSC-klagomål mail.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 52664-2023 tillsynsbegäran.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11672-2024 tillsynsbegäran.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 52664-2023 tillsynsbegäran mail.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11672-2024 tillsynsbegäran mail.docx", "A 11672-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 11672-2024</t>
+          <t>A 52664-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1664,10 +1660,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45373</v>
+        <v>45225</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1680,16 +1676,16 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>13.9</v>
+        <v>6.4</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1704,7 +1700,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1716,46 +1712,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11672-2024 artfynd.xlsx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 52664-2023 artfynd.xlsx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11672-2024 karta.png", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 52664-2023 karta.png", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11672-2024 georefererad karta.tif", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 52664-2023 georefererad karta.tif", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11672-2024 FSC-klagomål.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 52664-2023 FSC-klagomål.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11672-2024 FSC-klagomål mail.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 52664-2023 FSC-klagomål mail.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11672-2024 tillsynsbegäran.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 52664-2023 tillsynsbegäran.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11672-2024 tillsynsbegäran mail.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 52664-2023 tillsynsbegäran mail.docx", "A 52664-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 1577-2024</t>
+          <t>A 11170-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1769,10 +1765,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45306</v>
+        <v>44987</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1785,23 +1781,23 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>21.2</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
@@ -1809,10 +1805,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1821,46 +1817,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Korndådra</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11170-2023 artfynd.xlsx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11170-2023 karta.png", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11170-2023 georefererad karta.tif", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11170-2023 FSC-klagomål.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11170-2023 FSC-klagomål mail.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11170-2023 tillsynsbegäran.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11170-2023 tillsynsbegäran mail.docx", "A 11170-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 8169-2024</t>
+          <t>A 54127-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1874,10 +1870,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45351</v>
+        <v>45964</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1890,10 +1886,10 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1926,39 +1922,43 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Mjukdån</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 8169-2024 artfynd.xlsx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 54127-2025 artfynd.xlsx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 8169-2024 karta.png", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 54127-2025 karta.png", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 8169-2024 georefererad karta.tif", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 54127-2025 georefererad karta.tif", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 8169-2024 FSC-klagomål.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 54127-2025 FSC-klagomål.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 8169-2024 FSC-klagomål mail.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 54127-2025 FSC-klagomål mail.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 8169-2024 tillsynsbegäran.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 54127-2025 tillsynsbegäran.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 8169-2024 tillsynsbegäran mail.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 54127-2025 tillsynsbegäran mail.docx", "A 54127-2025")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/fåglar/A 54127-2025 prioriterade fågelarter.docx", "A 54127-2025")</f>
         <v/>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         <v>45218</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>44763</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44598</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44483</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44847</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44501</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>44831</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>44854</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 49032-2022</t>
+          <t>A 44107-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2595,10 +2595,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44860</v>
+        <v>45188</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 35911-2023</t>
+          <t>A 44196-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45148</v>
+        <v>45573</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 11101-2023</t>
+          <t>A 22262-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44986</v>
+        <v>45070</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2800,7 +2800,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 9716-2022</t>
+          <t>A 13245-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2814,10 +2814,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44617</v>
+        <v>45386</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>13</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 11177-2023</t>
+          <t>A 21556-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44987</v>
+        <v>45782</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 1592-2024</t>
+          <t>A 21541-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45306</v>
+        <v>45782</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3019,7 +3019,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 10209-2023</t>
+          <t>A 21814-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44986</v>
+        <v>45783</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3092,7 +3092,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 27310-2023</t>
+          <t>A 49032-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3106,10 +3106,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45096</v>
+        <v>44860</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3165,7 +3165,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 22262-2023</t>
+          <t>A 20047-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45070</v>
+        <v>45434</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3238,7 +3238,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 6335-2022</t>
+          <t>A 34808-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44600</v>
+        <v>45526</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3311,7 +3311,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 16667-2023</t>
+          <t>A 5167-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45030</v>
+        <v>45330</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.8</v>
+        <v>6.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3384,7 +3384,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 5068-2026</t>
+          <t>A 18121-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46049</v>
+        <v>45761</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 59266-2025</t>
+          <t>A 21774-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45988</v>
+        <v>45442</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 42706-2025</t>
+          <t>A 23747-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45908</v>
+        <v>45793</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3603,7 +3603,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 6365-2026</t>
+          <t>A 24513-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46051</v>
+        <v>45798</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.9</v>
+        <v>0.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3676,7 +3676,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 1920-2025</t>
+          <t>A 42706-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45671</v>
+        <v>45908</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 43425-2025</t>
+          <t>A 27310-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45911</v>
+        <v>45096</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 8332-2025</t>
+          <t>A 43425-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45708</v>
+        <v>45911</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3895,7 +3895,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 44112-2023</t>
+          <t>A 22794-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45188</v>
+        <v>45448</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3985,7 +3985,7 @@
         <v>45929</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 11491-2023</t>
+          <t>A 35587-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44991</v>
+        <v>45531</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 22063-2025</t>
+          <t>A 6335-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45785</v>
+        <v>44600</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4187,7 +4187,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 11922-2023</t>
+          <t>A 22063-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4201,10 +4201,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44993</v>
+        <v>45785</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4260,7 +4260,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 14533-2026</t>
+          <t>A 16667-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4274,10 +4274,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46100</v>
+        <v>45030</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4333,7 +4333,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 17980-2025</t>
+          <t>A 10196-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4347,10 +4347,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45761</v>
+        <v>45719</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4406,7 +4406,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 15747-2026</t>
+          <t>A 17980-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46107</v>
+        <v>45761</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
         <v>45769</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 3430-2026</t>
+          <t>A 44112-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4566,10 +4566,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46042</v>
+        <v>45188</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>5.7</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4625,7 +4625,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 37907-2025</t>
+          <t>A 35911-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45880</v>
+        <v>45148</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4654,13 +4654,8 @@
           <t>SVALÖV</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>5.7</v>
+        <v>0.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4703,7 +4698,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 40470-2025</t>
+          <t>A 43294-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4713,14 +4708,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45895</v>
+        <v>45910</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4733,7 +4728,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.1</v>
+        <v>2.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4776,7 +4771,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 43294-2025</t>
+          <t>A 37907-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4790,10 +4785,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45910</v>
+        <v>45880</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4805,8 +4800,13 @@
           <t>SVALÖV</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>2.6</v>
+        <v>5.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 34810-2023</t>
+          <t>A 42588-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45141</v>
+        <v>45176</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>7</v>
+        <v>1.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 62201-2025</t>
+          <t>A 40470-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4932,14 +4932,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46006</v>
+        <v>45895</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>22.1</v>
+        <v>0.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 43466-2025</t>
+          <t>A 1901-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45911</v>
+        <v>45671</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 43004-2025</t>
+          <t>A 1920-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45909</v>
+        <v>45671</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 18438-2026</t>
+          <t>A 43736-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5155,10 +5155,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46127</v>
+        <v>45182</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 24286-2026</t>
+          <t>A 8332-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46169</v>
+        <v>45708</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 35587-2024</t>
+          <t>A 14543-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45531</v>
+        <v>45394</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 58970-2025</t>
+          <t>A 62201-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45987</v>
+        <v>46006</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>22.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 25522-2026</t>
+          <t>A 9716-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46177</v>
+        <v>44617</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>8.5</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 8924-2023</t>
+          <t>A 20170-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44974</v>
+        <v>45434</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>6.8</v>
+        <v>0.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5579,7 +5579,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 1901-2025</t>
+          <t>A 62403-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45671</v>
+        <v>44923</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 22794-2024</t>
+          <t>A 43466-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45448</v>
+        <v>45911</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5725,7 +5725,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 32620-2023</t>
+          <t>A 43004-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45111</v>
+        <v>45909</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5798,7 +5798,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 44196-2024</t>
+          <t>A 15157-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45573</v>
+        <v>45016</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5871,7 +5871,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 17731-2025</t>
+          <t>A 11491-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5881,14 +5881,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45758</v>
+        <v>44991</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5944,7 +5944,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 14543-2024</t>
+          <t>A 18438-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5958,10 +5958,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45394</v>
+        <v>46127</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6017,7 +6017,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 13273-2024</t>
+          <t>A 37354-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45386</v>
+        <v>44806</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>12.4</v>
+        <v>1.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6090,7 +6090,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 29337-2026</t>
+          <t>A 24286-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6104,10 +6104,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46202</v>
+        <v>46169</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6163,7 +6163,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 25832-2026</t>
+          <t>A 58970-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46178</v>
+        <v>45987</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>7.8</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 30202-2026</t>
+          <t>A 5190-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6250,10 +6250,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46206</v>
+        <v>45330</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 30535-2026</t>
+          <t>A 10209-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6323,10 +6323,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46210</v>
+        <v>44986</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6382,7 +6382,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 22792-2024</t>
+          <t>A 17731-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6392,14 +6392,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45448</v>
+        <v>45758</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6455,7 +6455,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 14546-2024</t>
+          <t>A 25522-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6469,10 +6469,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45394</v>
+        <v>46177</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>8.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6528,7 +6528,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 18121-2025</t>
+          <t>A 5068-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45761</v>
+        <v>46049</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6601,7 +6601,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 16215-2022</t>
+          <t>A 59266-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44670</v>
+        <v>45988</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6674,7 +6674,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 15487-2025</t>
+          <t>A 22792-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6688,10 +6688,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45747</v>
+        <v>45448</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6747,7 +6747,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 4964-2022</t>
+          <t>A 6365-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6761,10 +6761,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44593</v>
+        <v>46051</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6820,7 +6820,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 37354-2022</t>
+          <t>A 4964-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6834,10 +6834,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44806</v>
+        <v>44593</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6893,7 +6893,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 11633-2024</t>
+          <t>A 11177-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45373</v>
+        <v>44987</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.9</v>
+        <v>1.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6966,7 +6966,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 13791-2026</t>
+          <t>A 16215-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6980,10 +6980,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46097</v>
+        <v>44670</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 13787-2026</t>
+          <t>A 25832-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46097</v>
+        <v>46178</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.7</v>
+        <v>7.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7112,7 +7112,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 27380-2026</t>
+          <t>A 61620-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46189</v>
+        <v>44910</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7185,7 +7185,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 20170-2024</t>
+          <t>A 29337-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7199,10 +7199,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45434</v>
+        <v>46202</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7258,7 +7258,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 61620-2022</t>
+          <t>A 30535-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44910</v>
+        <v>46210</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7331,7 +7331,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 5190-2024</t>
+          <t>A 30202-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7345,10 +7345,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45330</v>
+        <v>46206</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7404,7 +7404,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 40917-2026</t>
+          <t>A 8924-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7418,10 +7418,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46297</v>
+        <v>44974</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>8.1</v>
+        <v>6.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7477,7 +7477,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 40895-2026</t>
+          <t>A 14533-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7491,10 +7491,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46297</v>
+        <v>46100</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7550,7 +7550,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 40882-2026</t>
+          <t>A 15747-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7564,10 +7564,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46297</v>
+        <v>46107</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7623,7 +7623,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 40910-2026</t>
+          <t>A 497-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7637,10 +7637,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46297</v>
+        <v>44930</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7696,7 +7696,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 21774-2024</t>
+          <t>A 3430-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45442</v>
+        <v>46042</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.6</v>
+        <v>5.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7769,7 +7769,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 62403-2022</t>
+          <t>A 11633-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44923</v>
+        <v>45373</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.2</v>
+        <v>4.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7842,7 +7842,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 43736-2023</t>
+          <t>A 11922-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7856,10 +7856,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45182</v>
+        <v>44993</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7915,7 +7915,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 42588-2023</t>
+          <t>A 14546-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7929,10 +7929,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45176</v>
+        <v>45394</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7988,7 +7988,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 15157-2023</t>
+          <t>A 32620-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8002,10 +8002,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45016</v>
+        <v>45111</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8061,7 +8061,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 497-2023</t>
+          <t>A 34810-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8075,10 +8075,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44930</v>
+        <v>45141</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.8</v>
+        <v>7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8134,7 +8134,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 5184-2024</t>
+          <t>A 1592-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45330</v>
+        <v>45306</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 44107-2023</t>
+          <t>A 4149-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8217,14 +8217,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45188</v>
+        <v>44588</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8280,7 +8280,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 10196-2025</t>
+          <t>A 15487-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8294,10 +8294,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45719</v>
+        <v>45747</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8353,7 +8353,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 4149-2022</t>
+          <t>A 11101-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8363,14 +8363,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44588</v>
+        <v>44986</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 13245-2024</t>
+          <t>A 5184-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45386</v>
+        <v>45330</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>13</v>
+        <v>2.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8499,7 +8499,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 21814-2025</t>
+          <t>A 13273-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45783</v>
+        <v>45386</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.4</v>
+        <v>12.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8572,7 +8572,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 21541-2025</t>
+          <t>A 13791-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45782</v>
+        <v>46097</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8645,7 +8645,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 21556-2025</t>
+          <t>A 13787-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8659,10 +8659,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45782</v>
+        <v>46097</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8718,7 +8718,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 20047-2024</t>
+          <t>A 40882-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8732,10 +8732,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45434</v>
+        <v>46297</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8791,7 +8791,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 34808-2024</t>
+          <t>A 40917-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45526</v>
+        <v>46297</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.6</v>
+        <v>8.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8864,7 +8864,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 5167-2024</t>
+          <t>A 40910-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8878,10 +8878,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45330</v>
+        <v>46297</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>6.5</v>
+        <v>3.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8937,7 +8937,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 23747-2025</t>
+          <t>A 40895-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8951,10 +8951,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45793</v>
+        <v>46297</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9010,7 +9010,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 24513-2025</t>
+          <t>A 27380-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9024,10 +9024,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45798</v>
+        <v>46189</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9040,7 +9040,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9100,7 +9100,7 @@
         <v>45854</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>

--- a/Översikt SVALÖV.xlsx
+++ b/Översikt SVALÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45910</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 15475-2024</t>
+          <t>A 38522-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45401</v>
+        <v>45884</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.7</v>
+        <v>2.6</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -848,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -857,10 +857,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -869,146 +869,146 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Skogsknipprot
+Stor häxört</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 38522-2025 artfynd.xlsx", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 38522-2025 karta.png", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 38522-2025 georefererad karta.tif", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 38522-2025 FSC-klagomål.docx", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 38522-2025 FSC-klagomål mail.docx", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 38522-2025 tillsynsbegäran.docx", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 38522-2025 tillsynsbegäran mail.docx", "A 38522-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 15475-2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45401</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SVALÖV</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>1</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Ask
 Strutbräken</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15475-2024 artfynd.xlsx", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15475-2024 karta.png", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15475-2024 georefererad karta.tif", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15475-2024 FSC-klagomål.docx", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15475-2024 FSC-klagomål mail.docx", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15475-2024 tillsynsbegäran.docx", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15475-2024 tillsynsbegäran mail.docx", "A 15475-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 38522-2025</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45884</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SVALÖV</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Skogsknipprot
-Stor häxört</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 38522-2025 artfynd.xlsx", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 38522-2025 karta.png", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 38522-2025 georefererad karta.tif", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 38522-2025 FSC-klagomål.docx", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 38522-2025 FSC-klagomål mail.docx", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 38522-2025 tillsynsbegäran.docx", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 38522-2025 tillsynsbegäran mail.docx", "A 38522-2025")</f>
         <v/>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
         <v>45645</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 15456-2024</t>
+          <t>A 11170-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45401</v>
+        <v>44987</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1187,46 +1187,46 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Lundticka</t>
+          <t>Korndådra</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15456-2024 artfynd.xlsx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11170-2023 artfynd.xlsx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15456-2024 karta.png", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11170-2023 karta.png", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15456-2024 georefererad karta.tif", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11170-2023 georefererad karta.tif", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15456-2024 FSC-klagomål.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11170-2023 FSC-klagomål.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15456-2024 FSC-klagomål mail.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11170-2023 FSC-klagomål mail.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15456-2024 tillsynsbegäran.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11170-2023 tillsynsbegäran.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15456-2024 tillsynsbegäran mail.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11170-2023 tillsynsbegäran mail.docx", "A 11170-2023")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 8169-2024</t>
+          <t>A 15456-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45351</v>
+        <v>45401</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1265,10 +1265,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1283,7 +1283,7 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1296,42 +1296,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Mjukdån</t>
+          <t>Lundticka</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 8169-2024 artfynd.xlsx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15456-2024 artfynd.xlsx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 8169-2024 karta.png", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15456-2024 karta.png", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 8169-2024 georefererad karta.tif", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15456-2024 georefererad karta.tif", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 8169-2024 FSC-klagomål.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15456-2024 FSC-klagomål.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 8169-2024 FSC-klagomål mail.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15456-2024 FSC-klagomål mail.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 8169-2024 tillsynsbegäran.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15456-2024 tillsynsbegäran.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 8169-2024 tillsynsbegäran mail.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15456-2024 tillsynsbegäran mail.docx", "A 15456-2024")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 1577-2024</t>
+          <t>A 20125-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45306</v>
+        <v>45434</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>21.2</v>
+        <v>5.7</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1401,42 +1401,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 20125-2024 artfynd.xlsx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 20125-2024 karta.png", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 20125-2024 georefererad karta.tif", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 20125-2024 FSC-klagomål.docx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 20125-2024 FSC-klagomål mail.docx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 20125-2024 tillsynsbegäran.docx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 20125-2024 tillsynsbegäran mail.docx", "A 20125-2024")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 20125-2024</t>
+          <t>A 52664-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45434</v>
+        <v>45225</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
@@ -1506,35 +1506,35 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 20125-2024 artfynd.xlsx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 52664-2023 artfynd.xlsx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 20125-2024 karta.png", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 52664-2023 karta.png", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 20125-2024 georefererad karta.tif", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 52664-2023 georefererad karta.tif", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 20125-2024 FSC-klagomål.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 52664-2023 FSC-klagomål.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 20125-2024 FSC-klagomål mail.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 52664-2023 FSC-klagomål mail.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 20125-2024 tillsynsbegäran.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 52664-2023 tillsynsbegäran.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 20125-2024 tillsynsbegäran mail.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 52664-2023 tillsynsbegäran mail.docx", "A 52664-2023")</f>
         <v/>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
         <v>45373</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 52664-2023</t>
+          <t>A 54127-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1660,10 +1660,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45225</v>
+        <v>45964</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1676,17 +1676,17 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>6.4</v>
+        <v>1.3</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
       </c>
       <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
@@ -1700,7 +1700,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1712,46 +1712,50 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 52664-2023 artfynd.xlsx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 54127-2025 artfynd.xlsx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 52664-2023 karta.png", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 54127-2025 karta.png", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 52664-2023 georefererad karta.tif", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 54127-2025 georefererad karta.tif", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 52664-2023 FSC-klagomål.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 54127-2025 FSC-klagomål.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 52664-2023 FSC-klagomål mail.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 54127-2025 FSC-klagomål mail.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 52664-2023 tillsynsbegäran.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 54127-2025 tillsynsbegäran.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 52664-2023 tillsynsbegäran mail.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 54127-2025 tillsynsbegäran mail.docx", "A 54127-2025")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/fåglar/A 54127-2025 prioriterade fågelarter.docx", "A 54127-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 11170-2023</t>
+          <t>A 1577-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1765,10 +1769,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44987</v>
+        <v>45306</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1781,10 +1785,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>21.2</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1796,7 +1800,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1805,10 +1809,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1817,46 +1821,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Korndådra</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11170-2023 artfynd.xlsx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11170-2023 karta.png", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11170-2023 georefererad karta.tif", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11170-2023 FSC-klagomål.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11170-2023 FSC-klagomål mail.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11170-2023 tillsynsbegäran.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11170-2023 tillsynsbegäran mail.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 54127-2025</t>
+          <t>A 8169-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1870,10 +1874,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45964</v>
+        <v>45351</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1886,10 +1890,10 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1922,43 +1926,39 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Mjukdån</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 54127-2025 artfynd.xlsx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 8169-2024 artfynd.xlsx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 54127-2025 karta.png", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 8169-2024 karta.png", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 54127-2025 georefererad karta.tif", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 8169-2024 georefererad karta.tif", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 54127-2025 FSC-klagomål.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 8169-2024 FSC-klagomål.docx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 54127-2025 FSC-klagomål mail.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 8169-2024 FSC-klagomål mail.docx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 54127-2025 tillsynsbegäran.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 8169-2024 tillsynsbegäran.docx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 54127-2025 tillsynsbegäran mail.docx", "A 54127-2025")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/fåglar/A 54127-2025 prioriterade fågelarter.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 8169-2024 tillsynsbegäran mail.docx", "A 8169-2024")</f>
         <v/>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         <v>45218</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>44763</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44598</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44483</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44847</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44501</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>44831</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>44854</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 44107-2023</t>
+          <t>A 49032-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2595,10 +2595,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45188</v>
+        <v>44860</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 44196-2024</t>
+          <t>A 35911-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45573</v>
+        <v>45148</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 22262-2023</t>
+          <t>A 9716-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45070</v>
+        <v>44617</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2800,7 +2800,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 13245-2024</t>
+          <t>A 11101-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2814,10 +2814,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45386</v>
+        <v>44986</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>13</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 21556-2025</t>
+          <t>A 1592-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45782</v>
+        <v>45306</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 21541-2025</t>
+          <t>A 11177-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45782</v>
+        <v>44987</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3019,7 +3019,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 21814-2025</t>
+          <t>A 10209-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45783</v>
+        <v>44986</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3092,7 +3092,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 49032-2022</t>
+          <t>A 6335-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3106,10 +3106,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44860</v>
+        <v>44600</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3165,7 +3165,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 20047-2024</t>
+          <t>A 22262-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45434</v>
+        <v>45070</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3238,7 +3238,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 34808-2024</t>
+          <t>A 16667-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45526</v>
+        <v>45030</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3311,7 +3311,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 5167-2024</t>
+          <t>A 1920-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45330</v>
+        <v>45671</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>6.5</v>
+        <v>2.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3384,7 +3384,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 18121-2025</t>
+          <t>A 17980-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3401,7 +3401,7 @@
         <v>45761</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 21774-2024</t>
+          <t>A 8332-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45442</v>
+        <v>45708</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 23747-2025</t>
+          <t>A 19282-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3540,14 +3540,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45793</v>
+        <v>45769</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3603,7 +3603,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 24513-2025</t>
+          <t>A 44112-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45798</v>
+        <v>45188</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3676,7 +3676,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 42706-2025</t>
+          <t>A 11491-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45908</v>
+        <v>44991</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 27310-2023</t>
+          <t>A 11922-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45096</v>
+        <v>44993</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 43425-2025</t>
+          <t>A 37907-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45911</v>
+        <v>45880</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3851,8 +3851,13 @@
           <t>SVALÖV</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>2.1</v>
+        <v>5.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3895,7 +3900,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 22794-2024</t>
+          <t>A 40470-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3905,14 +3910,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45448</v>
+        <v>45895</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3925,7 +3930,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.8</v>
+        <v>0.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3968,7 +3973,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 47139-2025</t>
+          <t>A 42706-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3982,10 +3987,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45929</v>
+        <v>45908</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3998,7 +4003,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4041,7 +4046,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 35587-2024</t>
+          <t>A 43425-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4055,10 +4060,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45531</v>
+        <v>45911</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4071,7 +4076,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4114,7 +4119,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 6335-2022</t>
+          <t>A 14533-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4128,10 +4133,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44600</v>
+        <v>46100</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4144,7 +4149,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4187,7 +4192,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 22063-2025</t>
+          <t>A 47139-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4201,10 +4206,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45785</v>
+        <v>45929</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4217,7 +4222,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4260,7 +4265,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 16667-2023</t>
+          <t>A 15747-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4274,10 +4279,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45030</v>
+        <v>46107</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4290,7 +4295,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4333,7 +4338,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 10196-2025</t>
+          <t>A 3430-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4347,10 +4352,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45719</v>
+        <v>46042</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4363,7 +4368,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>5.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4406,7 +4411,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 17980-2025</t>
+          <t>A 35587-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4420,10 +4425,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45761</v>
+        <v>45531</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4436,7 +4441,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4479,7 +4484,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 19282-2025</t>
+          <t>A 8924-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4489,14 +4494,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45769</v>
+        <v>44974</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4509,7 +4514,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.8</v>
+        <v>6.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4552,7 +4557,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 44112-2023</t>
+          <t>A 1901-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4566,10 +4571,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45188</v>
+        <v>45671</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4582,7 +4587,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>4.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4625,7 +4630,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 35911-2023</t>
+          <t>A 43294-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4639,10 +4644,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45148</v>
+        <v>45910</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4655,7 +4660,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4698,7 +4703,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 43294-2025</t>
+          <t>A 22794-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4712,10 +4717,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45910</v>
+        <v>45448</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4728,7 +4733,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4771,7 +4776,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 37907-2025</t>
+          <t>A 32620-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4785,10 +4790,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45880</v>
+        <v>45111</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4800,13 +4805,8 @@
           <t>SVALÖV</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>5.7</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 42588-2023</t>
+          <t>A 44196-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45176</v>
+        <v>45573</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 40470-2025</t>
+          <t>A 17731-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45895</v>
+        <v>45758</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 1901-2025</t>
+          <t>A 14543-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45671</v>
+        <v>45394</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.2</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 1920-2025</t>
+          <t>A 13273-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45671</v>
+        <v>45386</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.3</v>
+        <v>12.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 43736-2023</t>
+          <t>A 43466-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5155,10 +5155,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45182</v>
+        <v>45911</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 8332-2025</t>
+          <t>A 43004-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45708</v>
+        <v>45909</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 14543-2024</t>
+          <t>A 34810-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45394</v>
+        <v>45141</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 62201-2025</t>
+          <t>A 22792-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46006</v>
+        <v>45448</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>22.1</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 9716-2022</t>
+          <t>A 14546-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44617</v>
+        <v>45394</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 20170-2024</t>
+          <t>A 62201-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45434</v>
+        <v>46006</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>22.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5579,7 +5579,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 62403-2022</t>
+          <t>A 18121-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44923</v>
+        <v>45761</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 43466-2025</t>
+          <t>A 16215-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45911</v>
+        <v>44670</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5725,7 +5725,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 43004-2025</t>
+          <t>A 5068-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45909</v>
+        <v>46049</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5798,7 +5798,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 15157-2023</t>
+          <t>A 59266-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45016</v>
+        <v>45988</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5871,7 +5871,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 11491-2023</t>
+          <t>A 15487-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44991</v>
+        <v>45747</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5944,7 +5944,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 18438-2026</t>
+          <t>A 4964-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5958,10 +5958,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46127</v>
+        <v>44593</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6034,7 +6034,7 @@
         <v>44806</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 24286-2026</t>
+          <t>A 6365-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6104,10 +6104,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46169</v>
+        <v>46051</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6163,7 +6163,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 58970-2025</t>
+          <t>A 11633-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45987</v>
+        <v>45373</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>4.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 5190-2024</t>
+          <t>A 18438-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6250,10 +6250,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45330</v>
+        <v>46127</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 10209-2023</t>
+          <t>A 24286-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6323,10 +6323,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44986</v>
+        <v>46169</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6382,7 +6382,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 17731-2025</t>
+          <t>A 20170-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6392,14 +6392,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45758</v>
+        <v>45434</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6455,7 +6455,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 25522-2026</t>
+          <t>A 58970-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6469,10 +6469,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46177</v>
+        <v>45987</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>8.5</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6528,7 +6528,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 5068-2026</t>
+          <t>A 25522-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46049</v>
+        <v>46177</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.5</v>
+        <v>8.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6601,7 +6601,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 59266-2025</t>
+          <t>A 61620-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45988</v>
+        <v>44910</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6674,7 +6674,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 22792-2024</t>
+          <t>A 5190-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6688,10 +6688,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45448</v>
+        <v>45330</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6747,7 +6747,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 6365-2026</t>
+          <t>A 21774-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6761,10 +6761,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46051</v>
+        <v>45442</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6820,7 +6820,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 4964-2022</t>
+          <t>A 62403-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6834,10 +6834,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44593</v>
+        <v>44923</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6893,7 +6893,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 11177-2023</t>
+          <t>A 29337-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44987</v>
+        <v>46202</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6966,7 +6966,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 16215-2022</t>
+          <t>A 25832-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6980,10 +6980,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44670</v>
+        <v>46178</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.9</v>
+        <v>7.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 25832-2026</t>
+          <t>A 43736-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46178</v>
+        <v>45182</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>7.8</v>
+        <v>1.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7112,7 +7112,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 61620-2022</t>
+          <t>A 42588-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44910</v>
+        <v>45176</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7185,7 +7185,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 29337-2026</t>
+          <t>A 15157-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7199,10 +7199,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46202</v>
+        <v>45016</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 30535-2026</t>
+          <t>A 30202-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46210</v>
+        <v>46206</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7331,7 +7331,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 30202-2026</t>
+          <t>A 30535-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7345,10 +7345,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46206</v>
+        <v>46210</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7404,7 +7404,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 8924-2023</t>
+          <t>A 497-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7418,10 +7418,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44974</v>
+        <v>44930</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>6.8</v>
+        <v>0.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7477,7 +7477,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 14533-2026</t>
+          <t>A 5184-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7491,10 +7491,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46100</v>
+        <v>45330</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7550,7 +7550,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 15747-2026</t>
+          <t>A 44107-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7564,10 +7564,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46107</v>
+        <v>45188</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7623,7 +7623,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 497-2023</t>
+          <t>A 10196-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7637,10 +7637,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44930</v>
+        <v>45719</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7696,7 +7696,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 3430-2026</t>
+          <t>A 4149-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7706,14 +7706,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46042</v>
+        <v>44588</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>5.7</v>
+        <v>1.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7769,7 +7769,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 11633-2024</t>
+          <t>A 13245-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45373</v>
+        <v>45386</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>4.9</v>
+        <v>13</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7842,7 +7842,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 11922-2023</t>
+          <t>A 13791-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7856,10 +7856,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44993</v>
+        <v>46097</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7915,7 +7915,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 14546-2024</t>
+          <t>A 13787-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7929,10 +7929,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45394</v>
+        <v>46097</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7988,7 +7988,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 32620-2023</t>
+          <t>A 21814-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8002,10 +8002,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45111</v>
+        <v>45783</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8061,7 +8061,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 34810-2023</t>
+          <t>A 21541-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8075,10 +8075,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45141</v>
+        <v>45782</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>7</v>
+        <v>3.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8134,7 +8134,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 1592-2024</t>
+          <t>A 21556-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45306</v>
+        <v>45782</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8207,7 +8207,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 4149-2022</t>
+          <t>A 20047-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8217,14 +8217,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44588</v>
+        <v>45434</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8280,7 +8280,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 15487-2025</t>
+          <t>A 34808-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8294,10 +8294,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45747</v>
+        <v>45526</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8353,7 +8353,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 11101-2023</t>
+          <t>A 5167-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8367,10 +8367,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44986</v>
+        <v>45330</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.5</v>
+        <v>6.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 5184-2024</t>
+          <t>A 23747-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45330</v>
+        <v>45793</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8499,7 +8499,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 13273-2024</t>
+          <t>A 24513-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45386</v>
+        <v>45798</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>12.4</v>
+        <v>0.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8572,7 +8572,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 13791-2026</t>
+          <t>A 27310-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46097</v>
+        <v>45096</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8645,7 +8645,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 13787-2026</t>
+          <t>A 22063-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8659,10 +8659,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46097</v>
+        <v>45785</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8718,7 +8718,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 40882-2026</t>
+          <t>A 40917-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8735,7 +8735,7 @@
         <v>46297</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2</v>
+        <v>8.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8791,7 +8791,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 40917-2026</t>
+          <t>A 40895-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8808,7 +8808,7 @@
         <v>46297</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>8.1</v>
+        <v>0.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8864,7 +8864,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 40910-2026</t>
+          <t>A 40882-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8881,7 +8881,7 @@
         <v>46297</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8937,7 +8937,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 40895-2026</t>
+          <t>A 40910-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8954,7 +8954,7 @@
         <v>46297</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
         <v>46189</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>45854</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>

--- a/Översikt SVALÖV.xlsx
+++ b/Översikt SVALÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45910</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 38522-2025</t>
+          <t>A 15475-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45884</v>
+        <v>45401</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -833,14 +833,14 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
@@ -848,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -857,10 +857,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -869,146 +869,146 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15475-2024 artfynd.xlsx", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15475-2024 karta.png", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15475-2024 georefererad karta.tif", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15475-2024 FSC-klagomål.docx", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15475-2024 FSC-klagomål mail.docx", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15475-2024 tillsynsbegäran.docx", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15475-2024 tillsynsbegäran mail.docx", "A 15475-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 38522-2025</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SVALÖV</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Skogsknipprot
 Stor häxört</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 38522-2025 artfynd.xlsx", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 38522-2025 karta.png", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 38522-2025 georefererad karta.tif", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 38522-2025 FSC-klagomål.docx", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 38522-2025 FSC-klagomål mail.docx", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 38522-2025 tillsynsbegäran.docx", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 38522-2025 tillsynsbegäran mail.docx", "A 38522-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 15475-2024</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45401</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SVALÖV</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15475-2024 artfynd.xlsx", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15475-2024 karta.png", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15475-2024 georefererad karta.tif", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15475-2024 FSC-klagomål.docx", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15475-2024 FSC-klagomål mail.docx", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15475-2024 tillsynsbegäran.docx", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15475-2024 tillsynsbegäran mail.docx", "A 15475-2024")</f>
         <v/>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
         <v>45645</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 11170-2023</t>
+          <t>A 15456-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44987</v>
+        <v>45401</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1187,46 +1187,46 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Korndådra</t>
+          <t>Lundticka</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11170-2023 artfynd.xlsx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15456-2024 artfynd.xlsx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11170-2023 karta.png", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15456-2024 karta.png", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11170-2023 georefererad karta.tif", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15456-2024 georefererad karta.tif", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11170-2023 FSC-klagomål.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15456-2024 FSC-klagomål.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11170-2023 FSC-klagomål mail.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15456-2024 FSC-klagomål mail.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11170-2023 tillsynsbegäran.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15456-2024 tillsynsbegäran.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11170-2023 tillsynsbegäran mail.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15456-2024 tillsynsbegäran mail.docx", "A 15456-2024")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 15456-2024</t>
+          <t>A 1577-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45401</v>
+        <v>45306</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.5</v>
+        <v>21.2</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1268,7 +1268,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1280,10 +1280,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1296,35 +1296,35 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Lundticka</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15456-2024 artfynd.xlsx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15456-2024 karta.png", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15456-2024 georefererad karta.tif", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15456-2024 FSC-klagomål.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15456-2024 FSC-klagomål mail.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15456-2024 tillsynsbegäran.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15456-2024 tillsynsbegäran mail.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
         <v>45434</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 52664-2023</t>
+          <t>A 8169-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45225</v>
+        <v>45351</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1466,31 +1466,31 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>6.4</v>
+        <v>3.1</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1506,35 +1506,35 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Mjukdån</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 52664-2023 artfynd.xlsx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 8169-2024 artfynd.xlsx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 52664-2023 karta.png", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 8169-2024 karta.png", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 52664-2023 georefererad karta.tif", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 8169-2024 georefererad karta.tif", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 52664-2023 FSC-klagomål.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 8169-2024 FSC-klagomål.docx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 52664-2023 FSC-klagomål mail.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 8169-2024 FSC-klagomål mail.docx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 52664-2023 tillsynsbegäran.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 8169-2024 tillsynsbegäran.docx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 52664-2023 tillsynsbegäran mail.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 8169-2024 tillsynsbegäran mail.docx", "A 8169-2024")</f>
         <v/>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
         <v>45373</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 54127-2025</t>
+          <t>A 52664-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1660,10 +1660,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45964</v>
+        <v>45225</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1676,16 +1676,16 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.3</v>
+        <v>6.4</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1700,7 +1700,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1712,50 +1712,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 54127-2025 artfynd.xlsx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 52664-2023 artfynd.xlsx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 54127-2025 karta.png", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 52664-2023 karta.png", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 54127-2025 georefererad karta.tif", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 52664-2023 georefererad karta.tif", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 54127-2025 FSC-klagomål.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 52664-2023 FSC-klagomål.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 54127-2025 FSC-klagomål mail.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 52664-2023 FSC-klagomål mail.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 54127-2025 tillsynsbegäran.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 52664-2023 tillsynsbegäran.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 54127-2025 tillsynsbegäran mail.docx", "A 54127-2025")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/fåglar/A 54127-2025 prioriterade fågelarter.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 52664-2023 tillsynsbegäran mail.docx", "A 52664-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 1577-2024</t>
+          <t>A 11170-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1769,10 +1765,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45306</v>
+        <v>44987</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1785,23 +1781,23 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>21.2</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
@@ -1809,10 +1805,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1821,46 +1817,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Korndådra</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11170-2023 artfynd.xlsx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11170-2023 karta.png", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11170-2023 georefererad karta.tif", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11170-2023 FSC-klagomål.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11170-2023 FSC-klagomål mail.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11170-2023 tillsynsbegäran.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11170-2023 tillsynsbegäran mail.docx", "A 11170-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 8169-2024</t>
+          <t>A 54127-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1874,10 +1870,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45351</v>
+        <v>45964</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1890,10 +1886,10 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1926,39 +1922,43 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Mjukdån</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 8169-2024 artfynd.xlsx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 54127-2025 artfynd.xlsx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 8169-2024 karta.png", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 54127-2025 karta.png", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 8169-2024 georefererad karta.tif", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 54127-2025 georefererad karta.tif", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 8169-2024 FSC-klagomål.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 54127-2025 FSC-klagomål.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 8169-2024 FSC-klagomål mail.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 54127-2025 FSC-klagomål mail.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 8169-2024 tillsynsbegäran.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 54127-2025 tillsynsbegäran.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 8169-2024 tillsynsbegäran mail.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 54127-2025 tillsynsbegäran mail.docx", "A 54127-2025")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/fåglar/A 54127-2025 prioriterade fågelarter.docx", "A 54127-2025")</f>
         <v/>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         <v>45218</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>44763</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44598</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44483</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44847</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44501</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>44831</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>44854</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 49032-2022</t>
+          <t>A 14546-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2595,10 +2595,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44860</v>
+        <v>45394</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 35911-2023</t>
+          <t>A 32620-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45148</v>
+        <v>45111</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 9716-2022</t>
+          <t>A 18121-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44617</v>
+        <v>45761</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2800,7 +2800,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 11101-2023</t>
+          <t>A 21774-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2814,10 +2814,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44986</v>
+        <v>45442</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 1592-2024</t>
+          <t>A 13245-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45306</v>
+        <v>45386</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.2</v>
+        <v>13</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 11177-2023</t>
+          <t>A 1592-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44987</v>
+        <v>45306</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3019,7 +3019,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 10209-2023</t>
+          <t>A 4149-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3029,14 +3029,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44986</v>
+        <v>44588</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3092,7 +3092,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 6335-2022</t>
+          <t>A 15487-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3106,10 +3106,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44600</v>
+        <v>45747</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3165,7 +3165,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 22262-2023</t>
+          <t>A 22794-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45070</v>
+        <v>45448</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3238,7 +3238,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 16667-2023</t>
+          <t>A 11101-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45030</v>
+        <v>44986</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3311,7 +3311,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 1920-2025</t>
+          <t>A 5184-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45671</v>
+        <v>45330</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3384,7 +3384,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 17980-2025</t>
+          <t>A 13273-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45761</v>
+        <v>45386</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.4</v>
+        <v>12.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 8332-2025</t>
+          <t>A 35587-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45708</v>
+        <v>45531</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 19282-2025</t>
+          <t>A 44196-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3540,14 +3540,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45769</v>
+        <v>45573</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3603,7 +3603,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 44112-2023</t>
+          <t>A 42706-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45188</v>
+        <v>45908</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 11491-2023</t>
+          <t>A 6335-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44991</v>
+        <v>44600</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 11922-2023</t>
+          <t>A 43425-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44993</v>
+        <v>45911</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 37907-2025</t>
+          <t>A 21556-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45880</v>
+        <v>45782</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3851,13 +3851,8 @@
           <t>SVALÖV</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>5.7</v>
+        <v>1.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3900,7 +3895,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 40470-2025</t>
+          <t>A 21541-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3910,14 +3905,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45895</v>
+        <v>45782</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3930,7 +3925,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.1</v>
+        <v>3.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3973,7 +3968,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 42706-2025</t>
+          <t>A 21814-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3987,10 +3982,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45908</v>
+        <v>45783</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4003,7 +3998,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4046,7 +4041,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 43425-2025</t>
+          <t>A 16667-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4060,10 +4055,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45911</v>
+        <v>45030</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4076,7 +4071,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4119,7 +4114,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 14533-2026</t>
+          <t>A 20047-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4133,10 +4128,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46100</v>
+        <v>45434</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4149,7 +4144,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4192,7 +4187,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 47139-2025</t>
+          <t>A 34808-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4206,10 +4201,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45929</v>
+        <v>45526</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4222,7 +4217,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4265,7 +4260,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 15747-2026</t>
+          <t>A 5167-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4279,10 +4274,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46107</v>
+        <v>45330</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4295,7 +4290,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>6.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4338,7 +4333,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 3430-2026</t>
+          <t>A 10196-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4352,10 +4347,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46042</v>
+        <v>45719</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4368,7 +4363,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>5.7</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4411,7 +4406,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 35587-2024</t>
+          <t>A 47139-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4425,10 +4420,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45531</v>
+        <v>45929</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4441,7 +4436,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4484,7 +4479,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 8924-2023</t>
+          <t>A 44112-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4498,10 +4493,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44974</v>
+        <v>45188</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4514,7 +4509,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>6.8</v>
+        <v>0.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4557,7 +4552,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 1901-2025</t>
+          <t>A 23747-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4571,10 +4566,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45671</v>
+        <v>45793</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4587,7 +4582,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4630,7 +4625,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 43294-2025</t>
+          <t>A 35911-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4644,10 +4639,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45910</v>
+        <v>45148</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4660,7 +4655,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4703,7 +4698,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 22794-2024</t>
+          <t>A 24513-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4717,10 +4712,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45448</v>
+        <v>45798</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4733,7 +4728,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.8</v>
+        <v>0.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4776,7 +4771,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 32620-2023</t>
+          <t>A 8332-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4790,10 +4785,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45111</v>
+        <v>45708</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4806,7 +4801,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4849,7 +4844,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 44196-2024</t>
+          <t>A 27310-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4863,10 +4858,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45573</v>
+        <v>45096</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4879,7 +4874,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4922,7 +4917,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 17731-2025</t>
+          <t>A 14543-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4932,14 +4927,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45758</v>
+        <v>45394</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4952,7 +4947,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4995,7 +4990,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 14543-2024</t>
+          <t>A 42588-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5009,10 +5004,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45394</v>
+        <v>45176</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5025,7 +5020,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5068,7 +5063,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 13273-2024</t>
+          <t>A 1901-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5082,10 +5077,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45386</v>
+        <v>45671</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5098,7 +5093,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>12.4</v>
+        <v>4.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5141,7 +5136,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 43466-2025</t>
+          <t>A 1920-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5155,10 +5150,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45911</v>
+        <v>45671</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5171,7 +5166,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5214,7 +5209,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 43004-2025</t>
+          <t>A 43736-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5228,10 +5223,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45909</v>
+        <v>45182</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5244,7 +5239,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5287,7 +5282,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 34810-2023</t>
+          <t>A 20170-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5301,10 +5296,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45141</v>
+        <v>45434</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5317,7 +5312,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>7</v>
+        <v>0.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5360,7 +5355,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 22792-2024</t>
+          <t>A 9716-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5374,10 +5369,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45448</v>
+        <v>44617</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5390,7 +5385,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5433,7 +5428,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 14546-2024</t>
+          <t>A 62403-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5447,10 +5442,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45394</v>
+        <v>44923</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5463,7 +5458,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5506,7 +5501,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 62201-2025</t>
+          <t>A 15157-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5520,10 +5515,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46006</v>
+        <v>45016</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5536,7 +5531,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>22.1</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5579,7 +5574,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 18121-2025</t>
+          <t>A 22063-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5593,10 +5588,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45761</v>
+        <v>45785</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5609,7 +5604,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5652,7 +5647,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 16215-2022</t>
+          <t>A 11491-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5666,10 +5661,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44670</v>
+        <v>44991</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5682,7 +5677,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5725,7 +5720,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 5068-2026</t>
+          <t>A 43294-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5739,10 +5734,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46049</v>
+        <v>45910</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5755,7 +5750,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5798,7 +5793,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 59266-2025</t>
+          <t>A 17980-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5812,10 +5807,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45988</v>
+        <v>45761</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5828,7 +5823,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5871,7 +5866,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 15487-2025</t>
+          <t>A 19282-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5881,14 +5876,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45747</v>
+        <v>45769</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5901,7 +5896,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5944,7 +5939,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 4964-2022</t>
+          <t>A 10209-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5958,10 +5953,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44593</v>
+        <v>44986</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5974,7 +5969,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6034,7 +6029,7 @@
         <v>44806</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6090,7 +6085,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 6365-2026</t>
+          <t>A 5190-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6104,10 +6099,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46051</v>
+        <v>45330</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6120,7 +6115,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6163,7 +6158,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 11633-2024</t>
+          <t>A 17731-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6173,14 +6168,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45373</v>
+        <v>45758</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6193,7 +6188,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.9</v>
+        <v>0.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6236,7 +6231,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 18438-2026</t>
+          <t>A 44107-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6250,10 +6245,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46127</v>
+        <v>45188</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6266,7 +6261,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6309,7 +6304,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 24286-2026</t>
+          <t>A 37907-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6323,10 +6318,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46169</v>
+        <v>45880</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6338,8 +6333,13 @@
           <t>SVALÖV</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>0.9</v>
+        <v>5.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6382,7 +6382,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 20170-2024</t>
+          <t>A 40470-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6392,14 +6392,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45434</v>
+        <v>45895</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6455,7 +6455,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 58970-2025</t>
+          <t>A 14533-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6469,10 +6469,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45987</v>
+        <v>46100</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6528,7 +6528,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 25522-2026</t>
+          <t>A 22262-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46177</v>
+        <v>45070</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>8.5</v>
+        <v>1.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6601,7 +6601,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 61620-2022</t>
+          <t>A 15747-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44910</v>
+        <v>46107</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6674,7 +6674,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 5190-2024</t>
+          <t>A 22792-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6688,10 +6688,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45330</v>
+        <v>45448</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6747,7 +6747,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 21774-2024</t>
+          <t>A 49032-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6761,10 +6761,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45442</v>
+        <v>44860</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6820,7 +6820,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 62403-2022</t>
+          <t>A 3430-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6834,10 +6834,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44923</v>
+        <v>46042</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.2</v>
+        <v>5.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6893,7 +6893,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 29337-2026</t>
+          <t>A 43466-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46202</v>
+        <v>45911</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6966,7 +6966,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 25832-2026</t>
+          <t>A 43004-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6980,10 +6980,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46178</v>
+        <v>45909</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>7.8</v>
+        <v>1.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 43736-2023</t>
+          <t>A 4964-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45182</v>
+        <v>44593</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7112,7 +7112,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 42588-2023</t>
+          <t>A 11177-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45176</v>
+        <v>44987</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7185,7 +7185,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 15157-2023</t>
+          <t>A 16215-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7199,10 +7199,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45016</v>
+        <v>44670</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7258,7 +7258,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 30202-2026</t>
+          <t>A 61620-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46206</v>
+        <v>44910</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7331,7 +7331,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 30535-2026</t>
+          <t>A 34810-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7345,10 +7345,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46210</v>
+        <v>45141</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.8</v>
+        <v>7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7404,7 +7404,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 497-2023</t>
+          <t>A 8924-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7418,10 +7418,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44930</v>
+        <v>44974</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.8</v>
+        <v>6.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7477,7 +7477,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 5184-2024</t>
+          <t>A 62201-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7491,10 +7491,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45330</v>
+        <v>46006</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.2</v>
+        <v>22.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7550,7 +7550,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 44107-2023</t>
+          <t>A 497-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7564,10 +7564,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45188</v>
+        <v>44930</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7623,7 +7623,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 10196-2025</t>
+          <t>A 11633-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7637,10 +7637,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45719</v>
+        <v>45373</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.5</v>
+        <v>4.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7696,7 +7696,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 4149-2022</t>
+          <t>A 11922-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7706,14 +7706,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44588</v>
+        <v>44993</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7769,7 +7769,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 13245-2024</t>
+          <t>A 5068-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45386</v>
+        <v>46049</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>13</v>
+        <v>3.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7842,7 +7842,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 13791-2026</t>
+          <t>A 59266-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7856,10 +7856,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46097</v>
+        <v>45988</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7915,7 +7915,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 13787-2026</t>
+          <t>A 6365-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7929,10 +7929,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46097</v>
+        <v>46051</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7988,7 +7988,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 21814-2025</t>
+          <t>A 18438-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8002,10 +8002,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45783</v>
+        <v>46127</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8061,7 +8061,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 21541-2025</t>
+          <t>A 24286-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8075,10 +8075,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45782</v>
+        <v>46169</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8134,7 +8134,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 21556-2025</t>
+          <t>A 58970-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45782</v>
+        <v>45987</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8207,7 +8207,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 20047-2024</t>
+          <t>A 25522-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8221,10 +8221,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45434</v>
+        <v>46177</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.3</v>
+        <v>8.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8280,7 +8280,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 34808-2024</t>
+          <t>A 25832-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8294,10 +8294,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45526</v>
+        <v>46178</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.6</v>
+        <v>7.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8353,7 +8353,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 5167-2024</t>
+          <t>A 29337-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8367,10 +8367,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45330</v>
+        <v>46202</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>6.5</v>
+        <v>2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 23747-2025</t>
+          <t>A 30535-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45793</v>
+        <v>46210</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8499,7 +8499,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 24513-2025</t>
+          <t>A 30202-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45798</v>
+        <v>46206</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.4</v>
+        <v>5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8572,7 +8572,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 27310-2023</t>
+          <t>A 13791-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45096</v>
+        <v>46097</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8645,7 +8645,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 22063-2025</t>
+          <t>A 13787-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8659,10 +8659,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45785</v>
+        <v>46097</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8718,7 +8718,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 40917-2026</t>
+          <t>A 40882-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8735,7 +8735,7 @@
         <v>46297</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>8.1</v>
+        <v>2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8791,7 +8791,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 40895-2026</t>
+          <t>A 40917-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8808,7 +8808,7 @@
         <v>46297</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.7</v>
+        <v>8.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8864,7 +8864,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 40882-2026</t>
+          <t>A 40910-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8881,7 +8881,7 @@
         <v>46297</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8937,7 +8937,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 40910-2026</t>
+          <t>A 40895-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8954,7 +8954,7 @@
         <v>46297</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
         <v>46189</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>45854</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>

--- a/Översikt SVALÖV.xlsx
+++ b/Översikt SVALÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45910</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>45401</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45884</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45645</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>45401</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>45306</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>45434</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>45351</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>45373</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>45225</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>44987</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>45964</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>45218</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>44763</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44598</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44483</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44847</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44501</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>44831</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>44854</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>45394</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>45111</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>45761</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>45442</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>45386</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>45306</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>44588</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>45747</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45448</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>44986</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>45330</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>45386</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>45531</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>45573</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>45908</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>44600</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>45911</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>45782</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>45782</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>45783</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>45030</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>45434</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>45526</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>45330</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>45719</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>45929</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>45188</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>45793</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>45148</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>45798</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>45708</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>45096</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>45394</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>45176</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>45671</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>45671</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>45182</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         <v>45434</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         <v>44617</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>44923</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>45016</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>45785</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>44991</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>45910</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         <v>45761</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>45769</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>44986</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>44806</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>45330</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>45758</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>45188</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>45880</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>45895</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>46100</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>45070</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>46107</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>45448</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>44860</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>46042</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>45911</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>45909</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>44593</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         <v>44987</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>44670</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>44910</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         <v>45141</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>44974</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>46006</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>44930</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>45373</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         <v>44993</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         <v>46049</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>45988</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         <v>46051</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>46127</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>46169</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>45987</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         <v>46177</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>46178</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>46202</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>46210</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>46206</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8589,7 +8589,7 @@
         <v>46097</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>46097</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>46297</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>46297</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>46297</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>46297</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         <v>46189</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>45854</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>

--- a/Översikt SVALÖV.xlsx
+++ b/Översikt SVALÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45910</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>45401</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45884</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45645</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>45401</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>45306</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>45434</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>45351</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>45373</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>45225</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>44987</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>45964</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>45218</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>44763</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44598</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44483</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44847</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44501</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>44831</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>44854</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>45394</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>45111</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>45761</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>45442</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>45386</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>45306</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>44588</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>45747</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45448</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>44986</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>45330</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>45386</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>45531</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>45573</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>45908</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>44600</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>45911</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>45782</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>45782</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>45783</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>45030</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>45434</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>45526</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>45330</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>45719</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>45929</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>45188</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>45793</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>45148</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>45798</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>45708</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>45096</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>45394</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>45176</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>45671</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>45671</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>45182</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         <v>45434</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         <v>44617</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>44923</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>45016</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>45785</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>44991</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>45910</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         <v>45761</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>45769</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>44986</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>44806</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>45330</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>45758</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>45188</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>45880</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>45895</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>46100</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>45070</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>46107</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>45448</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>44860</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>46042</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>45911</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>45909</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>44593</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         <v>44987</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>44670</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>44910</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         <v>45141</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>44974</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>46006</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>44930</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>45373</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         <v>44993</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         <v>46049</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>45988</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         <v>46051</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>46127</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>46169</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>45987</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         <v>46177</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>46178</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>46202</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>46210</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>46206</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8589,7 +8589,7 @@
         <v>46097</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>46097</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>46297</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>46297</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>46297</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>46297</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         <v>46189</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>45854</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>

--- a/Översikt SVALÖV.xlsx
+++ b/Översikt SVALÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45910</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 15475-2024</t>
+          <t>A 38522-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45401</v>
+        <v>45884</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.7</v>
+        <v>2.6</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -848,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -857,10 +857,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -869,259 +869,259 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Skogsknipprot
+Stor häxört</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 38522-2025 artfynd.xlsx", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 38522-2025 karta.png", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 38522-2025 georefererad karta.tif", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 38522-2025 FSC-klagomål.docx", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 38522-2025 FSC-klagomål mail.docx", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 38522-2025 tillsynsbegäran.docx", "A 38522-2025")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 38522-2025 tillsynsbegäran mail.docx", "A 38522-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 61064-2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45645</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SVALÖV</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 61064-2024 artfynd.xlsx", "A 61064-2024")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 61064-2024 karta.png", "A 61064-2024")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 61064-2024 georefererad karta.tif", "A 61064-2024")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 61064-2024 FSC-klagomål.docx", "A 61064-2024")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 61064-2024 FSC-klagomål mail.docx", "A 61064-2024")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 61064-2024 tillsynsbegäran.docx", "A 61064-2024")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 61064-2024 tillsynsbegäran mail.docx", "A 61064-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 15475-2024</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45401</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>SVALÖV</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Ask
 Strutbräken</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15475-2024 artfynd.xlsx", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15475-2024 karta.png", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15475-2024 georefererad karta.tif", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15475-2024 FSC-klagomål.docx", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15475-2024 FSC-klagomål mail.docx", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15475-2024 tillsynsbegäran.docx", "A 15475-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15475-2024 tillsynsbegäran mail.docx", "A 15475-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 38522-2025</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45884</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SVALÖV</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Skogsknipprot
-Stor häxört</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 38522-2025 artfynd.xlsx", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 38522-2025 karta.png", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 38522-2025 georefererad karta.tif", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 38522-2025 FSC-klagomål.docx", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 38522-2025 FSC-klagomål mail.docx", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 38522-2025 tillsynsbegäran.docx", "A 38522-2025")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 38522-2025 tillsynsbegäran mail.docx", "A 38522-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 61064-2024</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45645</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>SVALÖV</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 61064-2024 artfynd.xlsx", "A 61064-2024")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 61064-2024 karta.png", "A 61064-2024")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 61064-2024 georefererad karta.tif", "A 61064-2024")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 61064-2024 FSC-klagomål.docx", "A 61064-2024")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 61064-2024 FSC-klagomål mail.docx", "A 61064-2024")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 61064-2024 tillsynsbegäran.docx", "A 61064-2024")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 61064-2024 tillsynsbegäran mail.docx", "A 61064-2024")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 15456-2024</t>
+          <t>A 1577-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45401</v>
+        <v>45306</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.5</v>
+        <v>21.2</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1163,7 +1163,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1191,42 +1191,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Lundticka</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15456-2024 artfynd.xlsx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15456-2024 karta.png", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15456-2024 georefererad karta.tif", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15456-2024 FSC-klagomål.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15456-2024 FSC-klagomål mail.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15456-2024 tillsynsbegäran.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15456-2024 tillsynsbegäran mail.docx", "A 15456-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 1577-2024</t>
+          <t>A 8169-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45306</v>
+        <v>45351</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1256,17 +1256,17 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>21.2</v>
+        <v>3.1</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
@@ -1280,7 +1280,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1296,42 +1296,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Mjukdån</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 1577-2024 artfynd.xlsx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 8169-2024 artfynd.xlsx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 1577-2024 karta.png", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 8169-2024 karta.png", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 1577-2024 georefererad karta.tif", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 8169-2024 georefererad karta.tif", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 1577-2024 FSC-klagomål.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 8169-2024 FSC-klagomål.docx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 1577-2024 FSC-klagomål mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 8169-2024 FSC-klagomål mail.docx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 1577-2024 tillsynsbegäran.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 8169-2024 tillsynsbegäran.docx", "A 8169-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 1577-2024 tillsynsbegäran mail.docx", "A 1577-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 8169-2024 tillsynsbegäran mail.docx", "A 8169-2024")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 20125-2024</t>
+          <t>A 54127-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45434</v>
+        <v>45964</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1361,17 +1361,17 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.7</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
@@ -1385,7 +1385,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1397,46 +1397,50 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 20125-2024 artfynd.xlsx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 54127-2025 artfynd.xlsx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 20125-2024 karta.png", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 54127-2025 karta.png", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 20125-2024 georefererad karta.tif", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 54127-2025 georefererad karta.tif", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 20125-2024 FSC-klagomål.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 54127-2025 FSC-klagomål.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 20125-2024 FSC-klagomål mail.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 54127-2025 FSC-klagomål mail.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 20125-2024 tillsynsbegäran.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 54127-2025 tillsynsbegäran.docx", "A 54127-2025")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 20125-2024 tillsynsbegäran mail.docx", "A 20125-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 54127-2025 tillsynsbegäran mail.docx", "A 54127-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/fåglar/A 54127-2025 prioriterade fågelarter.docx", "A 54127-2025")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 8169-2024</t>
+          <t>A 11170-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1450,10 +1454,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45351</v>
+        <v>44987</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1466,7 +1470,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1475,13 +1479,13 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
         <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1493,7 +1497,7 @@
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1502,46 +1506,46 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Mjukdån</t>
+          <t>Korndådra</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 8169-2024 artfynd.xlsx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11170-2023 artfynd.xlsx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 8169-2024 karta.png", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11170-2023 karta.png", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 8169-2024 georefererad karta.tif", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11170-2023 georefererad karta.tif", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 8169-2024 FSC-klagomål.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11170-2023 FSC-klagomål.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 8169-2024 FSC-klagomål mail.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11170-2023 FSC-klagomål mail.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 8169-2024 tillsynsbegäran.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11170-2023 tillsynsbegäran.docx", "A 11170-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 8169-2024 tillsynsbegäran mail.docx", "A 8169-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11170-2023 tillsynsbegäran mail.docx", "A 11170-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 11672-2024</t>
+          <t>A 15456-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1555,10 +1559,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45373</v>
+        <v>45401</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1571,7 +1575,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>13.9</v>
+        <v>2.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1580,10 +1584,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1598,7 +1602,7 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1607,46 +1611,46 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Lundticka</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11672-2024 artfynd.xlsx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15456-2024 artfynd.xlsx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11672-2024 karta.png", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15456-2024 karta.png", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11672-2024 georefererad karta.tif", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15456-2024 georefererad karta.tif", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11672-2024 FSC-klagomål.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15456-2024 FSC-klagomål.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11672-2024 FSC-klagomål mail.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15456-2024 FSC-klagomål mail.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11672-2024 tillsynsbegäran.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15456-2024 tillsynsbegäran.docx", "A 15456-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11672-2024 tillsynsbegäran mail.docx", "A 11672-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15456-2024 tillsynsbegäran mail.docx", "A 15456-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 52664-2023</t>
+          <t>A 20125-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1660,10 +1664,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45225</v>
+        <v>45434</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1676,10 +1680,10 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -1716,42 +1720,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 52664-2023 artfynd.xlsx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 20125-2024 artfynd.xlsx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 52664-2023 karta.png", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 20125-2024 karta.png", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 52664-2023 georefererad karta.tif", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 20125-2024 georefererad karta.tif", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 52664-2023 FSC-klagomål.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 20125-2024 FSC-klagomål.docx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 52664-2023 FSC-klagomål mail.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 20125-2024 FSC-klagomål mail.docx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 52664-2023 tillsynsbegäran.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 20125-2024 tillsynsbegäran.docx", "A 20125-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 52664-2023 tillsynsbegäran mail.docx", "A 52664-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 20125-2024 tillsynsbegäran mail.docx", "A 20125-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 11170-2023</t>
+          <t>A 52664-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1765,10 +1769,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44987</v>
+        <v>45225</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1781,13 +1785,13 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>6.4</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1796,7 +1800,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1805,10 +1809,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1817,46 +1821,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Korndådra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11170-2023 artfynd.xlsx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 52664-2023 artfynd.xlsx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11170-2023 karta.png", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 52664-2023 karta.png", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11170-2023 georefererad karta.tif", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 52664-2023 georefererad karta.tif", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11170-2023 FSC-klagomål.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 52664-2023 FSC-klagomål.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11170-2023 FSC-klagomål mail.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 52664-2023 FSC-klagomål mail.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11170-2023 tillsynsbegäran.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 52664-2023 tillsynsbegäran.docx", "A 52664-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11170-2023 tillsynsbegäran mail.docx", "A 11170-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 52664-2023 tillsynsbegäran mail.docx", "A 52664-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 54127-2025</t>
+          <t>A 11672-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1870,10 +1874,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45964</v>
+        <v>45373</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1886,10 +1890,10 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.3</v>
+        <v>13.9</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1926,39 +1930,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 54127-2025 artfynd.xlsx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 11672-2024 artfynd.xlsx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 54127-2025 karta.png", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 11672-2024 karta.png", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 54127-2025 georefererad karta.tif", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 11672-2024 georefererad karta.tif", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 54127-2025 FSC-klagomål.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 11672-2024 FSC-klagomål.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 54127-2025 FSC-klagomål mail.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 11672-2024 FSC-klagomål mail.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 54127-2025 tillsynsbegäran.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 11672-2024 tillsynsbegäran.docx", "A 11672-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 54127-2025 tillsynsbegäran mail.docx", "A 54127-2025")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/fåglar/A 54127-2025 prioriterade fågelarter.docx", "A 54127-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 11672-2024 tillsynsbegäran mail.docx", "A 11672-2024")</f>
         <v/>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         <v>45218</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>44763</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44598</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44483</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44847</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44501</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>44831</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>44854</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 14546-2024</t>
+          <t>A 497-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2595,10 +2595,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45394</v>
+        <v>44930</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32620-2023</t>
+          <t>A 42706-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45111</v>
+        <v>45908</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 18121-2025</t>
+          <t>A 43425-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45761</v>
+        <v>45911</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2800,7 +2800,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 21774-2024</t>
+          <t>A 5184-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2814,10 +2814,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45442</v>
+        <v>45330</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 13245-2024</t>
+          <t>A 58970-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45386</v>
+        <v>45987</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 1592-2024</t>
+          <t>A 44107-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45306</v>
+        <v>45188</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3019,7 +3019,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 4149-2022</t>
+          <t>A 49032-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3029,14 +3029,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44588</v>
+        <v>44860</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3092,7 +3092,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 15487-2025</t>
+          <t>A 25522-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3106,10 +3106,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45747</v>
+        <v>46177</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>8.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3165,7 +3165,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 22794-2024</t>
+          <t>A 47139-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45448</v>
+        <v>45929</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3238,7 +3238,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 11101-2023</t>
+          <t>A 10196-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44986</v>
+        <v>45719</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3311,7 +3311,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 5184-2024</t>
+          <t>A 4149-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3321,14 +3321,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45330</v>
+        <v>44588</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3384,7 +3384,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 13273-2024</t>
+          <t>A 13245-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3401,7 +3401,7 @@
         <v>45386</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>12.4</v>
+        <v>13</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 35587-2024</t>
+          <t>A 29337-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45531</v>
+        <v>46202</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 44196-2024</t>
+          <t>A 43294-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45573</v>
+        <v>45910</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3603,7 +3603,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 42706-2025</t>
+          <t>A 35911-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45908</v>
+        <v>45148</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3676,7 +3676,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 6335-2022</t>
+          <t>A 25832-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44600</v>
+        <v>46178</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4</v>
+        <v>7.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 43425-2025</t>
+          <t>A 21814-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45911</v>
+        <v>45783</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 21556-2025</t>
+          <t>A 21541-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3839,7 +3839,7 @@
         <v>45782</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3895,7 +3895,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 21541-2025</t>
+          <t>A 21556-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3912,7 +3912,7 @@
         <v>45782</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3968,7 +3968,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 21814-2025</t>
+          <t>A 30202-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3982,10 +3982,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45783</v>
+        <v>46206</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4041,7 +4041,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 16667-2023</t>
+          <t>A 30535-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45030</v>
+        <v>46210</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4131,7 +4131,7 @@
         <v>45434</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>45526</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>45330</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 10196-2025</t>
+          <t>A 23747-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4347,10 +4347,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45719</v>
+        <v>45793</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4406,7 +4406,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 47139-2025</t>
+          <t>A 24513-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45929</v>
+        <v>45798</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4479,7 +4479,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 44112-2023</t>
+          <t>A 9716-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4493,10 +4493,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45188</v>
+        <v>44617</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4552,7 +4552,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 23747-2025</t>
+          <t>A 43466-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4566,10 +4566,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45793</v>
+        <v>45911</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4625,7 +4625,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 35911-2023</t>
+          <t>A 27310-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45148</v>
+        <v>45096</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4698,7 +4698,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 24513-2025</t>
+          <t>A 43004-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45798</v>
+        <v>45909</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4771,7 +4771,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 8332-2025</t>
+          <t>A 11101-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4785,10 +4785,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45708</v>
+        <v>44986</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4844,7 +4844,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 27310-2023</t>
+          <t>A 11177-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4858,10 +4858,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45096</v>
+        <v>44987</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4917,7 +4917,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 14543-2024</t>
+          <t>A 13791-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4931,10 +4931,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45394</v>
+        <v>46097</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4990,7 +4990,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 42588-2023</t>
+          <t>A 13787-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5004,10 +5004,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45176</v>
+        <v>46097</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5063,7 +5063,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 1901-2025</t>
+          <t>A 22063-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5077,10 +5077,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45671</v>
+        <v>45785</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5136,7 +5136,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 1920-2025</t>
+          <t>A 17980-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5150,10 +5150,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45671</v>
+        <v>45761</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5209,7 +5209,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 43736-2023</t>
+          <t>A 1592-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45182</v>
+        <v>45306</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5282,7 +5282,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 20170-2024</t>
+          <t>A 19282-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5292,14 +5292,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45434</v>
+        <v>45769</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5355,7 +5355,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 9716-2022</t>
+          <t>A 5068-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5369,10 +5369,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44617</v>
+        <v>46049</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5428,7 +5428,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 62403-2022</t>
+          <t>A 59266-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5442,10 +5442,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44923</v>
+        <v>45988</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5501,7 +5501,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 15157-2023</t>
+          <t>A 6365-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5515,10 +5515,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45016</v>
+        <v>46051</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5574,7 +5574,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 22063-2025</t>
+          <t>A 37907-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5588,10 +5588,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45785</v>
+        <v>45880</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5603,8 +5603,13 @@
           <t>SVALÖV</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>5.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5647,7 +5652,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 11491-2023</t>
+          <t>A 40470-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5657,14 +5662,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44991</v>
+        <v>45895</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5677,7 +5682,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.8</v>
+        <v>0.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5720,7 +5725,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 43294-2025</t>
+          <t>A 40917-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5734,10 +5739,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45910</v>
+        <v>46297</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5750,7 +5755,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.6</v>
+        <v>8.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5793,7 +5798,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 17980-2025</t>
+          <t>A 40895-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5807,10 +5812,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45761</v>
+        <v>46297</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5823,7 +5828,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5866,7 +5871,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 19282-2025</t>
+          <t>A 40882-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5876,14 +5881,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45769</v>
+        <v>46297</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5896,7 +5901,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5939,7 +5944,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 10209-2023</t>
+          <t>A 40910-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5953,10 +5958,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44986</v>
+        <v>46297</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5969,7 +5974,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6012,7 +6017,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 37354-2022</t>
+          <t>A 10209-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6026,10 +6031,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44806</v>
+        <v>44986</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6042,7 +6047,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6085,7 +6090,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 5190-2024</t>
+          <t>A 14533-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6099,10 +6104,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45330</v>
+        <v>46100</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6115,7 +6120,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6158,7 +6163,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 17731-2025</t>
+          <t>A 15747-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6168,14 +6173,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45758</v>
+        <v>46107</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6188,7 +6193,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6231,7 +6236,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 44107-2023</t>
+          <t>A 3430-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6245,10 +6250,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45188</v>
+        <v>46042</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6261,7 +6266,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.3</v>
+        <v>5.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6304,7 +6309,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 37907-2025</t>
+          <t>A 27380-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6318,10 +6323,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45880</v>
+        <v>46189</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6333,13 +6338,8 @@
           <t>SVALÖV</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>5.7</v>
+        <v>1.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6382,7 +6382,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 40470-2025</t>
+          <t>A 22262-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6392,14 +6392,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45895</v>
+        <v>45070</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6455,7 +6455,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 14533-2026</t>
+          <t>A 34810-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6469,10 +6469,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46100</v>
+        <v>45141</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6528,7 +6528,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 22262-2023</t>
+          <t>A 6335-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45070</v>
+        <v>44600</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6601,7 +6601,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 15747-2026</t>
+          <t>A 62201-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46107</v>
+        <v>46006</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.4</v>
+        <v>22.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6674,7 +6674,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 22792-2024</t>
+          <t>A 16667-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6688,10 +6688,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45448</v>
+        <v>45030</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6747,7 +6747,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 49032-2022</t>
+          <t>A 1920-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6761,10 +6761,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44860</v>
+        <v>45671</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6820,7 +6820,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 3430-2026</t>
+          <t>A 8332-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6834,10 +6834,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46042</v>
+        <v>45708</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>5.7</v>
+        <v>0.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6893,7 +6893,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 43466-2025</t>
+          <t>A 44112-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45911</v>
+        <v>45188</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6966,7 +6966,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 43004-2025</t>
+          <t>A 11491-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6980,10 +6980,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45909</v>
+        <v>44991</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 4964-2022</t>
+          <t>A 11922-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44593</v>
+        <v>44993</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7112,7 +7112,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 11177-2023</t>
+          <t>A 18438-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44987</v>
+        <v>46127</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7185,7 +7185,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 16215-2022</t>
+          <t>A 24286-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7199,10 +7199,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44670</v>
+        <v>46169</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7258,7 +7258,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 61620-2022</t>
+          <t>A 35587-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44910</v>
+        <v>45531</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7331,7 +7331,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 34810-2023</t>
+          <t>A 8924-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7345,10 +7345,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45141</v>
+        <v>44974</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7404,7 +7404,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 8924-2023</t>
+          <t>A 1901-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7418,10 +7418,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44974</v>
+        <v>45671</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7477,7 +7477,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 62201-2025</t>
+          <t>A 22794-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7491,10 +7491,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46006</v>
+        <v>45448</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>22.1</v>
+        <v>3.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7550,7 +7550,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 497-2023</t>
+          <t>A 32620-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7564,10 +7564,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44930</v>
+        <v>45111</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7623,7 +7623,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 11633-2024</t>
+          <t>A 44196-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7637,10 +7637,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45373</v>
+        <v>45573</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4.9</v>
+        <v>1.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7696,7 +7696,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 11922-2023</t>
+          <t>A 17731-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7706,14 +7706,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44993</v>
+        <v>45758</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7769,7 +7769,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 5068-2026</t>
+          <t>A 14543-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46049</v>
+        <v>45394</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7842,7 +7842,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 59266-2025</t>
+          <t>A 13273-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7856,10 +7856,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45988</v>
+        <v>45386</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.8</v>
+        <v>12.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7915,7 +7915,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 6365-2026</t>
+          <t>A 22792-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7929,10 +7929,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46051</v>
+        <v>45448</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7988,7 +7988,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 18438-2026</t>
+          <t>A 14546-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8002,10 +8002,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46127</v>
+        <v>45394</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8061,7 +8061,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 24286-2026</t>
+          <t>A 18121-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8075,10 +8075,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46169</v>
+        <v>45761</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8134,7 +8134,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 58970-2025</t>
+          <t>A 16215-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45987</v>
+        <v>44670</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8207,7 +8207,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 25522-2026</t>
+          <t>A 15487-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8221,10 +8221,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46177</v>
+        <v>45747</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>8.5</v>
+        <v>0.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8280,7 +8280,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 25832-2026</t>
+          <t>A 4964-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8294,10 +8294,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46178</v>
+        <v>44593</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>7.8</v>
+        <v>1.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8353,7 +8353,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 29337-2026</t>
+          <t>A 37354-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8367,10 +8367,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46202</v>
+        <v>44806</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 30535-2026</t>
+          <t>A 11633-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46210</v>
+        <v>45373</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.8</v>
+        <v>4.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8499,7 +8499,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 30202-2026</t>
+          <t>A 20170-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46206</v>
+        <v>45434</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8572,7 +8572,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 13791-2026</t>
+          <t>A 61620-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46097</v>
+        <v>44910</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8645,7 +8645,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 13787-2026</t>
+          <t>A 5190-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8659,10 +8659,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46097</v>
+        <v>45330</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8718,7 +8718,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 40882-2026</t>
+          <t>A 21774-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8732,10 +8732,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46297</v>
+        <v>45442</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8791,7 +8791,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 40917-2026</t>
+          <t>A 62403-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46297</v>
+        <v>44923</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>8.1</v>
+        <v>2.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8864,7 +8864,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 40910-2026</t>
+          <t>A 43736-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8878,10 +8878,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46297</v>
+        <v>45182</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8937,7 +8937,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 40895-2026</t>
+          <t>A 42588-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8951,10 +8951,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46297</v>
+        <v>45176</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9010,7 +9010,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 27380-2026</t>
+          <t>A 15157-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9024,10 +9024,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46189</v>
+        <v>45016</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9040,7 +9040,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9100,7 +9100,7 @@
         <v>45854</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>

--- a/Översikt SVALÖV.xlsx
+++ b/Översikt SVALÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45910</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 38522-2025</t>
+          <t>A 15475-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45884</v>
+        <v>45401</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -833,14 +833,14 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
@@ -848,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -857,10 +857,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -869,259 +869,259 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15475-2024 artfynd.xlsx", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15475-2024 karta.png", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15475-2024 georefererad karta.tif", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15475-2024 FSC-klagomål.docx", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15475-2024 FSC-klagomål mail.docx", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15475-2024 tillsynsbegäran.docx", "A 15475-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15475-2024 tillsynsbegäran mail.docx", "A 15475-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 38522-2025</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SVALÖV</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Skogsknipprot
 Stor häxört</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 38522-2025 artfynd.xlsx", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 38522-2025 karta.png", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 38522-2025 georefererad karta.tif", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 38522-2025 FSC-klagomål.docx", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 38522-2025 FSC-klagomål mail.docx", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 38522-2025 tillsynsbegäran.docx", "A 38522-2025")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 38522-2025 tillsynsbegäran mail.docx", "A 38522-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>A 61064-2024</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
         <v>45645</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SVALÖV</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
+      <c r="E6" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>SVALÖV</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>5.6</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K6" t="n">
         <v>1</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>1</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R6" t="n">
         <v>1</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S6" t="n">
         <v>2</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T6" t="n">
         <v>2</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Ask
 Skogsknipprot</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 61064-2024 artfynd.xlsx", "A 61064-2024")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 61064-2024 karta.png", "A 61064-2024")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 61064-2024 georefererad karta.tif", "A 61064-2024")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 61064-2024 FSC-klagomål.docx", "A 61064-2024")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 61064-2024 FSC-klagomål mail.docx", "A 61064-2024")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 61064-2024 tillsynsbegäran.docx", "A 61064-2024")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 61064-2024 tillsynsbegäran mail.docx", "A 61064-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 15475-2024</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45401</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>SVALÖV</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/artfynd/A 15475-2024 artfynd.xlsx", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor/A 15475-2024 karta.png", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/kartor_geotiff/A 15475-2024 georefererad karta.tif", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomål/A 15475-2024 FSC-klagomål.docx", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/klagomålsmail/A 15475-2024 FSC-klagomål mail.docx", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsyn/A 15475-2024 tillsynsbegäran.docx", "A 15475-2024")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1214/tillsynsmail/A 15475-2024 tillsynsbegäran mail.docx", "A 15475-2024")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 1577-2024</t>
+          <t>A 15456-2024</t>
         </is>
       </c>
     